--- a/mistral_translate_work/split_by_prompt/excel/skill_description/lang_multi_text/lang_multi_text__skill_description__part_0029.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/skill_description/lang_multi_text/lang_multi_text__skill_description__part_0029.xlsx
@@ -576,9 +576,9 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[&lt;te href=800028&gt;Beam Weapon&lt;/te&gt;]&lt;/color&gt;
-Cảm nhận sức mạnh của sóng ngân. Tầm tấn công và hệ số sát thương của &lt;color=#2c9366&gt;&lt;te href=800014&gt;Zenith Windblades&lt;/te&gt;&lt;/color&gt; được tăng thêm.
-Loại: &lt;color=#c49e55&gt;[&lt;te href=800028&gt;Beam Weapon&lt;/te&gt;]&lt;/color&gt;</t>
+          <t>&lt;color=#c49e55&gt;[&lt;te href=800028&gt;Vũ Khí Tia&lt;/te&gt;]&lt;/color&gt;
+Cảm nhận sức mạnh của sóng ngân. Tầm tấn công và hệ số DMG của &lt;color=#2c9366&gt;&lt;te href=800014&gt;Zenith Windblades&lt;/te&gt;&lt;/color&gt; được tăng thêm.
+Loại: &lt;color=#c49e55&gt;[&lt;te href=800028&gt;Vũ Khí Tia&lt;/te&gt;]&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       <c r="M3" t="inlineStr">
         <is>
           <t>&lt;color=#2c9366&gt;&lt;te href=800014&gt;Zenith Windblade&lt;/te&gt;&lt;/color&gt; hấp thụ &lt;color=#9c5884&gt;&lt;te href=800023&gt;Rampant Fire&lt;/te&gt;&lt;/color&gt; và giờ phóng năm lưỡi kiếm cùng lúc, tấn công kẻ địch trong phạm vi hình quạt rộng.
-Phân loại: &lt;color=#c49e55&gt;[&lt;te href=800028&gt;Beam Weapon&lt;/te&gt;]&lt;/color&gt;</t>
+Phân loại: &lt;color=#c49e55&gt;[&lt;te href=800028&gt;Vũ Khí Tia&lt;/te&gt;]&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -712,7 +712,7 @@
       <c r="M4" t="inlineStr">
         <is>
           <t>&lt;color=#2c9366&gt;&lt;te href=800014&gt;Zenith Windblade&lt;/te&gt;&lt;/color&gt; hấp thụ &lt;color=#917701&gt;&lt;te href=800016&gt;Glittering Ray&lt;/te&gt;&lt;/color&gt; và giờ phóng năm lưỡi kiếm đan chéo, xuyên qua kẻ địch trên đường đi.
-Phân loại: &lt;color=#c49e55&gt;[&lt;te href=800028&gt;Beam Weapon&lt;/te&gt;]&lt;/color&gt;</t>
+Phân loại: &lt;color=#c49e55&gt;[&lt;te href=800028&gt;Vũ Khí Tia&lt;/te&gt;]&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -778,8 +778,8 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Summon &lt;color=#9c5884&gt;&lt;te href=800015&gt;Sanguine Wheel&lt;/te&gt;&lt;/color&gt; để liên tục tấn công kẻ địch xung quanh.
-Loại: &lt;color=#c49e55&gt;[&lt;te href=800027&gt;Summon Weapon&lt;/te&gt;]&lt;/color&gt;</t>
+          <t>Triệu hồi &lt;color=#9c5884&gt;&lt;te href=800015&gt;Bánh Xe Huyết Nhục&lt;/te&gt;&lt;/color&gt; để liên tục tấn công kẻ địch xung quanh.
+Loại: &lt;color=#c49e55&gt;[&lt;te href=800027&gt;Vũ Khí Triệu Hồi&lt;/te&gt;]&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -845,8 +845,8 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Summon thêm một &lt;color=#9c5884&gt;&lt;te href=800015&gt;Sanguine Wheel&lt;/te&gt;&lt;/color&gt; tấn công kẻ địch xung quanh.
-Loại: &lt;color=#c49e55&gt;[&lt;te href=800027&gt;Summon Weapon&lt;/te&gt;]&lt;/color&gt;</t>
+          <t>Triệu hồi thêm một &lt;color=#9c5884&gt;&lt;te href=800015&gt;Bánh Xe Huyết&lt;/te&gt;&lt;/color&gt; tấn công kẻ địch xung quanh.
+Loại: &lt;color=#c49e55&gt;[&lt;te href=800027&gt;Vũ Khí Triệu Hồi&lt;/te&gt;]&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -912,8 +912,8 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Giải phóng sức mạnh nguyên thủy. Summon tổng cộng ba &lt;color=#9c5884&gt;&lt;te href=800015&gt;Sanguine Wheels&lt;/te&gt;&lt;/color&gt; tấn công kẻ địch xung quanh.
-Loại: &lt;color=#c49e55&gt;[&lt;te href=800027&gt;Summon Weapon&lt;/te&gt;]&lt;/color&gt;</t>
+          <t>Giải phóng sức mạnh nguyên thủy. Triệu hồi tổng cộng ba &lt;color=#9c5884&gt;&lt;te href=800015&gt;Bánh Xe Huyết Tộc&lt;/te&gt;&lt;/color&gt; tấn công kẻ địch xung quanh.
+Loại: &lt;color=#c49e55&gt;[&lt;te href=800027&gt;Vũ Khí Triệu Hồi&lt;/te&gt;]&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -980,7 +980,7 @@
       <c r="M8" t="inlineStr">
         <is>
           <t>Số lượng và Hệ Số Sát Thương của &lt;color=#917701&gt;&lt;te href=800016&gt;Glittering Rays&lt;/te&gt;&lt;/color&gt; đã tăng lên.
-Loại: &lt;color=#c49e55&gt;[&lt;te href=800028&gt;Beam Weapon&lt;/te&gt;]&lt;/color&gt;</t>
+Loại: &lt;color=#c49e55&gt;[&lt;te href=800028&gt;Vũ Khí Tia&lt;/te&gt;]&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -1047,7 +1047,7 @@
       <c r="M9" t="inlineStr">
         <is>
           <t>Quá Tải kích hoạt. Số lượng và Hệ Số Sát Thương của &lt;color=#917701&gt;&lt;te href=800016&gt;Glittering Rays&lt;/te&gt;&lt;/color&gt; được tăng cường thêm.
-Loại: &lt;color=#c49e55&gt;[&lt;te href=800028&gt;Beam Weapon&lt;/te&gt;]&lt;/color&gt;</t>
+Loại: &lt;color=#c49e55&gt;[&lt;te href=800028&gt;Vũ Khí Tia&lt;/te&gt;]&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       <c r="M10" t="inlineStr">
         <is>
           <t>Tầm ảnh hưởng và Hệ Số Sát Thương của &lt;color=#9c5884&gt;&lt;te href=800023&gt;Rampant Fire&lt;/te&gt;&lt;/color&gt; được tăng lên.
-Phân loại: &lt;color=#c49e55&gt;[&lt;te href=800029&gt;Morph Weapon&lt;/te&gt;]&lt;/color&gt;</t>
+Phân loại: &lt;color=#c49e55&gt;[&lt;te href=800029&gt;Vũ Khí Biến Hình&lt;/te&gt;]&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -1180,8 +1180,8 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Phun &lt;color=#9c5884&gt;&lt;te href=800023&gt;Rampant Fire&lt;/te&gt;&lt;/color&gt; từ hai bên với hệ số sát thương tăng.
-Phân loại: &lt;color=#c49e55&gt;[&lt;te href=800029&gt;Morph Weapon&lt;/te&gt;]&lt;/color&gt;</t>
+          <t>Phun &lt;color=#9c5884&gt;&lt;te href=800023&gt;Rampant Fire&lt;/te&gt;&lt;/color&gt; từ hai bên với hệ số DMG tăng.
+Phân loại: &lt;color=#c49e55&gt;[&lt;te href=800029&gt;Biến Hình Vũ Khí&lt;/te&gt;]&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -1247,8 +1247,8 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Trở thành bậc thầy bẫy gài. Tầm ảnh hưởng và hệ số sát thương của &lt;color=#be6245&gt;&lt;te href=800025&gt;Explosive Omens&lt;/te&gt;&lt;/color&gt; được tăng cường thêm.
-Phân loại: &lt;color=#c49e55&gt;[&lt;te href=800029&gt;Morph Weapon&lt;/te&gt;]&lt;/color&gt;</t>
+          <t>Trở thành bậc thầy bẫy gài. Tầm ảnh hưởng và hệ số DMG của &lt;color=#be6245&gt;&lt;te href=800025&gt;Điềm Báo Nổ&lt;/te&gt;&lt;/color&gt; được tăng cường thêm.
+Phân loại: &lt;color=#c49e55&gt;[&lt;te href=800029&gt;Biến Hình Vũ Khí&lt;/te&gt;]&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -1313,7 +1313,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Echo DMG</t>
+          <t>Sát Thương Tiếng Vọng</t>
         </is>
       </c>
     </row>
@@ -1384,12 +1384,12 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Bút ký linh tinh của Bộ Trưởng Bộ Sự Vụ Cảm Tử &lt;te href=260009&gt;Mingting&lt;/te&gt;: Tuyển tập thư từ
+          <t>Bút ký linh tinh của Bộ Trưởng Bộ Sự Vụ Cảm Tử &lt;te href=260009&gt;Minh Đình&lt;/te&gt;: Tuyển tập thư từ
 Bạn thân mến Đông Nguyên à,
-Vài ngày trước, &lt;te href=260001&gt;Internal Security Agency&lt;/te&gt; đã chuyển tiếp tài liệu từ Ủy Ban Tư Pháp và Học Viện Hoa Hư đến &lt;te href=260002&gt;Ministry of Sentinel Affairs&lt;/te&gt;. Ngay lập tức, ta đã chỉ thị quan viên Trùng Châu hỗ trợ điều tra và test kỹ lưỡng sổ đăng ký Resonator địa phương. Đến nay đã xác nhận, cá nhân này không hề có liên hệ với &lt;te href=850083&gt;Sentinel&lt;/te&gt; hay &lt;te href=850074&gt;Threnodian&lt;/te&gt; ở Trùng Châu.
-Theo hồ sơ của Bộ, cá nhân này đã là Resonator hơn mười lăm năm. Được miêu tả là "nhìn thế giới qua lũy tre, giấu kiếm trong tre", dù mù lòa nhưng hắn sở hữu khả năng đặc biệt mang tên &lt;te href=260003&gt;Mindsight&lt;/te&gt;. Nhờ sức mạnh này, hắn cảm nhận môi trường xung quanh qua "khu rừng tre" trong tâm trí, từ đó nhìn thấu ý đồ và điểm yếu của đối thủ. Thậm chí, hắn còn có thể biến Thị Giác Tâm Linh thành ảo ảnh hữu hình. Đây không phải là kẻ có thể xem thường.
-Hơn nữa, kiếm pháp của hắn dường như chủ yếu dựa vào kỹ năng cá nhân chứ không phải năng lực Resonance. Theo quan sát, hắn luôn kiềm chế sử dụng sức mạnh Resonance. Hắn cho biết chiếc bình tre mang theo chứa một loại thuốc—do một lang y lưu lạc ở Trùng Châu bào chế—có tác dụng kích thích Thị Giác Tâm Linh và Forte của hắn, và chỉ sử dụng khi cần thiết. Vấn đề này có thể chuyển đến Học Viện để phân tích thêm.
-Còn về dữ liệu test chi tiết, xin chờ báo cáo chính thức từ Học Viện...
+Vài ngày trước, &lt;te href=260001&gt;Cơ Quan An Ninh Nội Bộ&lt;/te&gt; đã chuyển tiếp tài liệu từ Ủy Ban Tư Pháp và Học Viện Hoa Hư đến &lt;te href=260002&gt;Bộ Sự Vụ Cảm Tử&lt;/te&gt;. Ngay lập tức, ta đã chỉ thị quan viên Trùng Châu hỗ trợ điều tra và kiểm tra kỹ lưỡng sổ đăng ký Resonator địa phương. Đến nay đã xác nhận, cá nhân này không hề có liên hệ với &lt;te href=850083&gt;Cảm Tử&lt;/te&gt; hay &lt;te href=850074&gt;Threnody&lt;/te&gt; ở Trùng Châu.
+Theo hồ sơ của Bộ, cá nhân này đã là Resonator hơn mười lăm năm. Được miêu tả là "nhìn thế giới qua lũy tre, giấu kiếm trong tre", dù mù lòa nhưng hắn sở hữu khả năng đặc biệt mang tên &lt;te href=260003&gt;Thị Giác Tâm Linh&lt;/te&gt;. Nhờ sức mạnh này, hắn cảm nhận môi trường xung quanh qua "khu rừng tre" trong tâm trí, từ đó nhìn thấu ý đồ và điểm yếu của đối thủ. Thậm chí, hắn còn có thể biến Thị Giác Tâm Linh thành ảo ảnh hữu hình. Đây không phải là kẻ có thể xem thường.
+Hơn nữa, kiếm pháp của hắn dường như chủ yếu dựa vào kỹ năng cá nhân chứ không phải năng lực Cộng Hưởng. Theo quan sát, hắn luôn kiềm chế sử dụng sức mạnh Cộng Hưởng. Hắn cho biết chiếc bình tre mang theo chứa một loại thuốc—do một lang y lưu lạc ở Trùng Châu bào chế—có tác dụng kích thích Thị Giác Tâm Linh và Forte của hắn, và chỉ sử dụng khi cần thiết. Vấn đề này có thể chuyển đến Học Viện để phân tích thêm.
+Còn về dữ liệu kiểm tra chi tiết, xin chờ báo cáo chính thức từ Học Viện...
 Chú thích của Đông Nguyên: Chỉ cần ghi chép rõ ràng là được. Chúng ta sẽ theo phán quyết của Bộ Sự Vụ Cảm Tử… Trời ơi, Lâm vẫn viết văn kiểu cách như thế này đấy.</t>
         </is>
       </c>
@@ -1462,13 +1462,13 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Ghi Chép Lặt Vặt Của &lt;te href=260009&gt;Mingting&lt;/te&gt; - &lt;te href=260002&gt;Ministry of Sentinel Affairs&lt;/te&gt;: Tuyển Tập Thư Tín
+          <t>Ghi Chép Lặt Vặt Của &lt;te href=260009&gt;Minh Đình&lt;/te&gt; - &lt;te href=260002&gt;Bộ Sự Vụ Cảnh Vệ&lt;/te&gt;: Tuyển Tập Thư Tín
 …Qua quan sát mấy ngày gần đây, ta thấy hắn không phải là không thể sử dụng Forte của mình, mà là cố tình kiềm chế không dùng. Về bản chất khả năng đó, hắn vẫn giữ kín như bưng. Chỉ từ báo cáo của Học Viện mới có thể rút ra vài chi tiết:
 &lt;i&gt;Phân tích dạng sóng đối tượng cho thấy dao động hình elip. Dữ liệu miền thời gian ổn định, không phát hiện bất thường.
-Độ Tới Hạn Cộng Hưởng: High. Độ ổn định cao, không có nguy cơ &lt;te href=850073&gt;Overclocking&lt;/te&gt;.
+Độ Tới Hạn Cộng Hưởng: Cao. Độ ổn định cao, không có nguy cơ &lt;te href=850073&gt;Quá Tải&lt;/te&gt;.
 Chưa từng có tiền sử Quá Tải. Can thiệp tâm lý được đánh giá là không cần thiết.
 Ghi chú: Đối tượng thừa nhận đã nhiều lần vi phạm pháp luật với hành vi bạo lực, nhưng thái độ lại bình thản đến đáng ngờ. Đề nghị Bộ Tư Pháp và chính quyền địa phương Trùng Châu xác minh lại những cáo buộc này.&lt;/i&gt;
-…Nhưng theo đánh giá của ta, gã này không hề có ý đồ sát hại. Thái độ của hắn điềm tĩnh đến mức đáng kinh ngạc, phong thái vững vàng. Kỹ năng kiếm thuật của hắn thuộc hàng xuất sắc, ít người ở Mingting có thể sánh bằng. Hắn đáng lẽ đã có thể trở thành một tài sản quý giá cho &lt;te href=260001&gt;Internal Security Agency&lt;/te&gt;. Thật khó tin khi một cá nhân như vậy lại bị Ủy Ban Tư Pháp liệt vào danh sách tội phạm bạo lực. Ta đã liên lạc với Bộ Lễ Nghĩa, trình bày rõ lợi ích và ý nghĩa của việc chiêu mộ hắn. Nếu ngài muốn sử dụng người này, ta tin sẽ không gặp trở ngại nào.
+…Nhưng theo đánh giá của ta, gã này không hề có ý đồ sát hại. Thái độ của hắn điềm tĩnh đến mức đáng kinh ngạc, phong thái vững vàng. Kỹ năng kiếm thuật của hắn thuộc hàng xuất sắc, ít người ở Minh Đình có thể sánh bằng. Hắn đáng lẽ đã có thể trở thành một tài sản quý giá cho &lt;te href=260001&gt;Cơ Quan An Ninh Nội Bộ&lt;/te&gt;. Thật khó tin khi một cá nhân như vậy lại bị Ủy Ban Tư Pháp liệt vào danh sách tội phạm bạo lực. Ta đã liên lạc với Bộ Lễ Nghĩa, trình bày rõ lợi ích và ý nghĩa của việc chiêu mộ hắn. Nếu ngài muốn sử dụng người này, ta tin sẽ không gặp trở ngại nào.
 Chú thích của Đông Nguyên: Tất nhiên, càng điềm tĩnh càng tốt. Nhưng đọc báo cáo này... thằng nhóc này chẳng có chút cảm xúc nào à?</t>
         </is>
       </c>
@@ -1544,16 +1544,16 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>[Biên Bản Đánh Giá Rủi Ro Chứa Chấp Special – X666]
-"...Năng lực Resonance của đối tượng cho thấy đã bị nhiễm độc trước đó bởi &lt;te href=851023&gt;Dark Tide&lt;/te&gt;. Phổ tần số bị che khuất nghiêm trọng, không thể phân tích bằng Phương Pháp Rabelle. Dựa trên lời khai của đối tượng, được xác nhận bởi các nguồn bên ngoài, cô được phân loại là &lt;te href=850068&gt;Congenital Resonator&lt;/te&gt;."
-"...Phát hiện Discord cấp Overlord trong cơ thể đối tượng. Thí nghiệm sẽ được chuyển đến &lt;te href=850110&gt;Tethys Hệ thống&lt;/te&gt;. Tất cả nhân sự không thiết yếu phải sơ tán đến khu vực an toàn được chỉ định ngay lập tức!"
+          <t>[Biên Bản Đánh Giá Rủi Ro Chứa Chấp Đặc Biệt – X666]
+"...Năng lực Cộng Hưởng của đối tượng cho thấy đã bị nhiễm độc trước đó bởi &lt;te href=851023&gt;Thủy Triều Hắc Ám&lt;/te&gt;. Phổ tần số bị che khuất nghiêm trọng, không thể phân tích bằng Phương Pháp Rabelle. Dựa trên lời khai của đối tượng, được xác nhận bởi các nguồn bên ngoài, cô được phân loại là &lt;te href=850068&gt;Resonator Bẩm Sinh&lt;/te&gt;."
+"...Phát hiện Tacet Discord cấp Overlord trong cơ thể đối tượng. Thí nghiệm sẽ được chuyển đến &lt;te href=850110&gt;Hệ Thống Tethys&lt;/te&gt;. Tất cả nhân sự không thiết yếu phải sơ tán đến khu vực an toàn được chỉ định ngay lập tức!"
 "...Cơ sở dữ liệu mẫu đã liên kết. Bắt đầu phân tích so sánh."
-"...Xác nhận tần số nội tại của đối tượng. Phát hiện khớp một phần với các &lt;te href=850081&gt;Tacet Discords&lt;/te&gt; đã biết: &lt;te href=260005&gt;Chimera&lt;/te&gt;, Galbrena, Harpyia, Dullahan, Balor, và Ác Mộng Vô Danh. Các mối tương quan còn lại đang chờ xác minh."
-"Tất cả các Discord đã xác định không có hành vi thù địch khi bị ức chế bởi tần số của đối tượng. Ổn định hành vi được xác nhận trong điều kiện căng thẳng cao. Đánh giá cuối cùng: không khuyến nghị cách ly. Đề xuất: kiểm tra định kỳ.
+"...Xác nhận tần số nội tại của đối tượng. Phát hiện khớp một phần với các &lt;te href=850081&gt;Tacet Discord&lt;/te&gt; đã biết: &lt;te href=260005&gt;Chimera&lt;/te&gt;, Galbrena, Harpyia, Dullahan, Balor, và Ác Mộng Vô Danh. Các mối tương quan còn lại đang chờ xác minh."
+"Tất cả các Tacet Discord đã xác định không có hành vi thù địch khi bị ức chế bởi tần số của đối tượng. Ổn định hành vi được xác nhận trong điều kiện căng thẳng cao. Đánh giá cuối cùng: không khuyến nghị cách ly. Đề xuất: kiểm tra định kỳ.
 Nguyên nhân Khai Sáng của đối tượng không thể xác định. Ngọn lửa bẩm sinh của cô, từng bị Thủy Triều Hắc Ám ăn mòn, đã suy tàn nhưng không bao giờ tắt hẳn. Sau đó, nó hòa nhập với Sinh Vật Thủy Triều mang tên Chimera, thay đổi bản chất ngọn lửa và ban cho cô khả năng tiêu thụ các tần số khác.
-Thông qua quá trình này, đối tượng chủ động săn lùng Discord, hấp thụ và chuyển hóa tần số của chúng thành sức mạnh của riêng mình. Hiện tại, cô có thể sử dụng nhiều năng lực của Discord trong chiến đấu.
+Thông qua quá trình này, đối tượng chủ động săn lùng Tacet Discord, hấp thụ và chuyển hóa tần số của chúng thành sức mạnh của riêng mình. Hiện tại, cô có thể sử dụng nhiều năng lực của Tacet Discord trong chiến đấu.
 Với những 'con quỷ' bị ngọn lửa của cô nuốt chửng, chỉ có hai kết cục: được thanh tẩy và chuyển hóa thành sức mạnh của cô, hoặc bị hủy diệt hoàn toàn.
-&lt;i&gt;"Một bảo tàng sống của Discord… Liệu sức mạnh như vậy có thực sự thuộc về con người? Tệ hơn nữa, nó còn tiến hóa."&lt;/i&gt;
+&lt;i&gt;"Một bảo tàng sống của Tacet Discord… Liệu sức mạnh như vậy có thực sự thuộc về con người? Tệ hơn nữa, nó còn tiến hóa."&lt;/i&gt;
 &lt;i&gt;"Không… đó là một đế chế nội tại. Ta đã thấy… một đế chế đang trỗi dậy bên trong cô."&lt;/i&gt;</t>
         </is>
       </c>
@@ -1624,11 +1624,11 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Resonators Galbrena có tiền sử Quá Tải trước đây. Mức độ nghiêm trọng tối đa: Nhẹ.
-&lt;i&gt;Report Nghiên cứu Người Mang Hoa Vùng Bờ Đen&lt;/i&gt;
-&lt;i&gt;Dù sau khi &lt;te href=850073&gt;Overclocking&lt;/te&gt;, bà Galbrena thể hiện sức mạnh khủng khiếp—bao gồm cả sự biến đổi rõ rệt về ngoại hình và sinh lý—chúng tôi vẫn xếp mức độ nghiêm trọng Quá Tải trong lịch sử của bà là Nhẹ.&lt;/i&gt;
-&lt;i&gt;Đánh giá này cần được hiểu trong bối cảnh: Resonance Ability của bà từng bị &lt;te href=851023&gt;Dark Tide&lt;/te&gt; làm hư hại, khiến bà gần như cạn kiệt Resonance Ability. Với một Resonators suy yếu như vậy mà vẫn đạt được Quá Tải—từ thiếu hụt đến dư thừa, từ không có gì đến hiện hữu—quả là một điều kỳ diệu.&lt;/i&gt;
-&lt;i&gt;Theo truyền thống, Quá Tải được định nghĩa là trạng thái vắt kiệt tâm trí và thể xác, biểu thị sự áp đảo của xu hướng hủy diệt so với tái tạo trong Resonators. Tuy nhiên, trường hợp của Galbrena buộc chúng ta phải xem xét lại định nghĩa này. Ở bà, Quá Tải không biểu hiện như sự suy thoái, mà như tín hiệu của sự tái sinh. Điều này cho thấy hiện tượng này có thể gắn liền với ý chí của Resonators và nếu được dẫn dắt đúng cách, Quá Tải có khả năng mang lại kết quả tích cực, trở thành sức mạnh mà một ngày nào đó Resonators có thể học cách kiểm soát theo ý muốn.&lt;/i&gt;
+          <t>Resonator Galbrena có tiền sử Quá Tải trước đây. Mức độ nghiêm trọng tối đa: Nhẹ.
+&lt;i&gt;Báo cáo Nghiên cứu Người Mang Hoa Vùng Bờ Đen&lt;/i&gt;
+&lt;i&gt;Dù sau khi &lt;te href=850073&gt;Quá Tải&lt;/te&gt;, bà Galbrena thể hiện sức mạnh khủng khiếp—bao gồm cả sự biến đổi rõ rệt về ngoại hình và sinh lý—chúng tôi vẫn xếp mức độ nghiêm trọng Quá Tải trong lịch sử của bà là Nhẹ.&lt;/i&gt;
+&lt;i&gt;Đánh giá này cần được hiểu trong bối cảnh: Khả Năng Cộng Hưởng của bà từng bị &lt;te href=851023&gt;Thủy Triều Bóng Tối&lt;/te&gt; làm hư hại, khiến bà gần như cạn kiệt Khả Năng Cộng Hưởng. Với một Resonator suy yếu như vậy mà vẫn đạt được Quá Tải—từ thiếu hụt đến dư thừa, từ không có gì đến hiện hữu—quả là một điều kỳ diệu.&lt;/i&gt;
+&lt;i&gt;Theo truyền thống, Quá Tải được định nghĩa là trạng thái vắt kiệt tâm trí và thể xác, biểu thị sự áp đảo của xu hướng hủy diệt so với tái tạo trong Resonator. Tuy nhiên, trường hợp của Galbrena buộc chúng ta phải xem xét lại định nghĩa này. Ở bà, Quá Tải không biểu hiện như sự suy thoái, mà như tín hiệu của sự tái sinh. Điều này cho thấy hiện tượng này có thể gắn liền với ý chí của Resonator và nếu được dẫn dắt đúng cách, Quá Tải có khả năng mang lại kết quả tích cực, trở thành sức mạnh mà một ngày nào đó Resonator có thể học cách kiểm soát theo ý muốn.&lt;/i&gt;
 &lt;i&gt;Lưu ý quan trọng: Tất cả nhân viên nghiên cứu nghiêm cấm tuyệt đối thử tái tạo phương pháp Quá Tải của bà Galbrena bằng bất kỳ cách nào. Nếu phát hiện, sẽ áp dụng ngay biện pháp cách ly.&lt;/i&gt;</t>
         </is>
       </c>
@@ -1765,9 +1765,9 @@
       <c r="M19" t="inlineStr">
         <is>
           <t>"Viên đạn đầu tiên" được cô đặc từ chính máu của Galbrena. Món quà cô dành cho ngươi.
-Trong chuyến du hành qua Vùng Pháp Luật Mất Kiểm Soát của New Federation, Galbrena đã chạm trán một tổ chức bí mật và học được một kỹ thuật tàn khốc mang tên Huyết Ước. Những kẻ thực hành nó đều là những kẻ đào tẩu không đường quay đầu, hoặc như cô, những kẻ đã bị bóng tối trói buộc từ lâu. Mỗi người chọn Con Đường Sát Thủ vì lý do riêng, chỉ để giáng một đòn chí mạng vào khoảnh khắc bất ngờ nhất. Galbrena lĩnh hội nghệ thuật này nhanh chóng. Kết quả của cô phi thường hơn hầu hết—máu cô từ lâu đã cháy như lửa. Cô đã quá quen thuộc với con đường này.
+Trong chuyến du hành qua Vùng Pháp Luật Mất Kiểm Soát của Liên Bang Mới, Galbrena đã chạm trán một tổ chức bí mật và học được một kỹ thuật tàn khốc mang tên Huyết Ước. Những kẻ thực hành nó đều là những kẻ đào tẩu không đường quay đầu, hoặc như cô, những kẻ đã bị bóng tối trói buộc từ lâu. Mỗi người chọn Con Đường Sát Thủ vì lý do riêng, chỉ để giáng một đòn chí mạng vào khoảnh khắc bất ngờ nhất. Galbrena lĩnh hội nghệ thuật này nhanh chóng. Kết quả của cô phi thường hơn hầu hết—máu cô từ lâu đã cháy như lửa. Cô đã quá quen thuộc với con đường này.
 Mỗi sát thủ thề Huyết Ước đều mang theo một viên đạn như thế, gọi là "Huyết Ước Đầu Tiên". Một câu châm ngôn cũ của họ là: "Viên đạn mang tên ngươi." Đó là dấu hiệu của quyết tâm săn đuổi con mồi đến cùng. Nhưng ở Vùng Pháp Luật Mất Kiểm Soát, nơi đồng minh có thể trở mặt thành kẻ thù trong nháy mắt, những mối ràng buộc tin tưởng chân thật trở nên quý giá. Từ đó, Nghi Lễ Giao Ước ra đời. Dù Galbrena chưa từng thực hiện nó, cô vẫn nhớ rõ sức nặng và ý nghĩa của nghi lễ.
-Khi một sát thủ trao Huyết Ước Đầu Tiên cho ai đó, họ sẽ khắc tên người nhận lên viên đạn. Hợp đồng đơn giản nhưng ràng buộc và cổ xưa nhất: trở thành viên đạn của {Male=hắn;Female=cô ta}. Không phản bội. Không trốn chạy. Cho đến khi máu cạn, lửa tàn thành tro.</t>
+Khi một sát thủ trao Huyết Ước Đầu Tiên cho ai đó, họ sẽ khắc tên người nhận lên viên đạn. Hợp đồng đơn giản nhưng ràng buộc và cổ xưa nhất: trở thành viên đạn của {Male=his;Female=her}. Không phản bội. Không trốn chạy. Cho đến khi máu cạn, lửa tàn thành tro.</t>
         </is>
       </c>
     </row>
@@ -1873,11 +1873,11 @@
 "Đây, cầm lấy bình này. Và cả công thức nữa. Một bát thuốc thì cần ba bát nước. Nhớ kỹ đấy."
 "…Cái này là gì?"
 "Phương thuốc mạnh ngày ấy đã kéo ngươi từ cửa tử về, nhưng Tần số của ngươi đã bị tổn thương nặng.
-Loại thuốc này khôi phục &lt;te href=260003&gt;Mindsight&lt;/te&gt; của ngươi, ít nhất là tạm thời. Sẽ có ích vào ngày ngươi lại vung kiếm."
+Loại thuốc này khôi phục &lt;te href=260003&gt;Thị Lực Tâm Linh&lt;/te&gt; của ngươi, ít nhất là tạm thời. Sẽ có ích vào ngày ngươi lại vung kiếm."
 "Ta sẽ không. Ngài đã cứu ta, Lương y. Ít nhất ta có thể ở lại và làm mấy việc lặt vặt cho ngài."
 "Ta không nghĩ thế. Vết máu vẫn vương trên mặt ngươi. Đường sinh mệnh trên tay ngươi đã đứt đoạn. Theo sau là nỗi sợ, ám ảnh bởi đau khổ… Ngươi chắc chắn sẽ chết trên chiến trường, chứ không phải già đi trong túp lều này."
-"Theo sau là nỗi sợ, ám ảnh bởi đau khổ… Master ta cũng từng nói thế."
-"Master à? Có một đệ tử như ngươi… Ông ta hẳn là một người cứng rắn lắm."
+"Theo sau là nỗi sợ, ám ảnh bởi đau khổ… Sư phụ ta cũng từng nói thế."
+"Sư phụ à? Có một đệ tử như ngươi… Ông ta hẳn là một người cứng rắn lắm."
 "…Dù vậy, Lương y, ta sẽ không cầm kiếm nữa. Nhưng ta sẽ nhận công thức của ngài. Cho ta ở lại đây. Nếu có rắc rối vì ta mà tìm đến túp lều này, ta sẽ rời đi."
 "Thôi… thuốc cũng như kiếm. Tất cả đều phụ thuộc vào cách dùng và liều lượng. Nó có thể giết người, nhưng cũng có thể cứu mạng."
 "Giờ thì đi mở cửa đi, Qiuyuan. Nhóm lửa lên. Ta không dám nhận mình giỏi hơn ngươi, nhưng dưới mái nhà này, không ai dám gây chuyện đâu. Ta đảm bảo."</t>
@@ -1963,19 +1963,19 @@
         <is>
           <t>"Ác quỷ đã gục ngã. Lũ trẻ có thể hát lại rồi."
 Kẻ Diệt Tacet gập đôi đôi cánh bốc cháy, từ từ hạ xuống giữa đám đông đang chờ đợi. Sức nóng vẫn tỏa ra từ khẩu súng bên hông cô cho thấy cuộc săn vừa kết thúc.
-&lt;te href=850081&gt;Tacet Discords&lt;/te&gt;—những sinh vật siêu nhiên sinh ra từ tàn dư hỗn loạn của tần số và năng lượng con người—là hiện thân của độc ác và hủy diệt trong thế giới này. Dù khoa học đã phân loại chúng từ lâu, nhiều nơi vẫn gọi chúng là ác quỷ hay linh hồn báo thù, với những cái tên bắt nguồn từ truyền thuyết và chuyện ma quái xưa cũ. Và trên khắp thế giới, vẫn có những kẻ săn đuổi chúng. Vì tiền thưởng, vì nghiên cứu, hay đơn giản là để thử thách sức mạnh bản thân. Để đối mặt với những kẻ thù đáng sợ như vậy với cả sự tôn trọng lẫn thách thức, những thợ săn này mang một danh hiệu được truyền lại qua nhiều thế hệ—Kẻ Diệt Tacet.
-Hầu hết Kẻ Diệt Tacet chứng minh chiến tích của mình bằng cách trích xuất tần số của quái vật qua Terminal, hoặc mang về Core Tacet của nó. Nhưng không phải cô. Cô luôn trở về tay không, chỉ đưa ra lời khẳng định công việc đã hoàn thành. Cô bình tĩnh thuật lại điểm yếu của từng con quái vật và cách tiêu diệt chúng hiệu quả nhất. Nhưng lời nói không đủ để tạo dựng niềm tin. Vì vậy, cô giơ tay phải lên và thì thầm tên gọi… Shrieking Legion, Discord mà cô chứa chấp, hiện ra. Đám đông không còn lựa chọn nào khác ngoài việc tin tưởng. Fear hãi lan tỏa trong không khí. Sự im lặng như lưỡi dao buông xuống.
+&lt;te href=850081&gt;Tacet Discord&lt;/te&gt;—những sinh vật siêu nhiên sinh ra từ tàn dư hỗn loạn của tần số và năng lượng con người—là hiện thân của độc ác và hủy diệt trong thế giới này. Dù khoa học đã phân loại chúng từ lâu, nhiều nơi vẫn gọi chúng là ác quỷ hay linh hồn báo thù, với những cái tên bắt nguồn từ truyền thuyết và chuyện ma quái xưa cũ. Và trên khắp thế giới, vẫn có những kẻ săn đuổi chúng. Vì tiền thưởng, vì nghiên cứu, hay đơn giản là để thử thách sức mạnh bản thân. Để đối mặt với những kẻ thù đáng sợ như vậy với cả sự tôn trọng lẫn thách thức, những thợ săn này mang một danh hiệu được truyền lại qua nhiều thế hệ—Kẻ Diệt Tacet.
+Hầu hết Kẻ Diệt Tacet chứng minh chiến tích của mình bằng cách trích xuất tần số của quái vật qua Thiết bị đầu cuối, hoặc mang về Lõi Tacet của nó. Nhưng không phải cô. Cô luôn trở về tay không, chỉ đưa ra lời khẳng định công việc đã hoàn thành. Cô bình tĩnh thuật lại điểm yếu của từng con quái vật và cách tiêu diệt chúng hiệu quả nhất. Nhưng lời nói không đủ để tạo dựng niềm tin. Vì vậy, cô giơ tay phải lên và thì thầm tên gọi… Shrieking Legion, Tacet Discord mà cô chứa chấp, hiện ra. Đám đông không còn lựa chọn nào khác ngoài việc tin tưởng. Nỗi sợ hãi lan tỏa trong không khí. Sự im lặng như lưỡi dao buông xuống.
 Cô nghe thấy những lời thì thầm, những nghi ngờ, những hoài nghi. Cô cảm nhận được sự thù địch của họ, nhưng chưa bao giờ cố giải thích. Người thì thì thầm rằng cô là sản phẩm của thí nghiệm lai giữa con người và TD, được tạo ra chỉ để giết chóc. Kẻ khác tin rằng cô được rèn từ tần số TD bị biến đổi, một sinh vật sinh ra từ tội lỗi. Còn nhiều người nữa lại tin rằng cô đã lập giao ước với ác quỷ và đánh đổi cảm xúc của mình. Cô luôn gật đầu đồng ý với điều đó. Với cô, đó là một tấm khiên tiện lợi, một cái cớ để bịt miệng những câu hỏi không muốn trả lời.
 Hầu hết ngày, cô sẽ quay lưng trước những ánh nhìn. Nhưng đôi khi, cô cho phép bản thân những thú vui nhỏ. Cô phớt lờ những ánh mắt cảnh giác và ngồi xuống quầy bar mở cửa, lặng lẽ gọi vài ly sinh tố kem việt quất. Chỉ những thợ săn từng chiến đấu bên cạnh cô mới biết sự thật. Dưới lớp mặt nạ lạnh lùng, xa cách ấy là ngọn lửa mãnh liệt của niềm khao khát săn đuổi. Và khi đối mặt với con mồi, cô không hề khoan nhượng.
-Shrieking Legion là một Discord thuộc hệ thú của rừng. Sinh ra từ lòng đố kỵ, nó bắt chước giọng người để dụ trẻ em đến gần trước khi cướp đi tiếng nói của chúng. Cô đã cảnh báo đội không được giao chiến với nó trên lãnh địa của nó. Nhưng ngoại hình trẻ con của cô không mang lại sự tin tưởng. Họ phớt lờ cô và sa vào bẫy. Những bức tường thung lũng khuếch đại tiếng thét của con quái vật thành một cơn bão âm thanh suýt nữa nghiền nát cả đội. Nhưng cô không hề do dự. Với quyết tâm lạnh lùng, cô tự làm vỡ màng nhĩ mình, máu chảy theo sau khi cô lao tới. Trong nháy mắt, ngọn lửa bùng lên quanh cô. Cô dí súng vào ngực con quái vật và bóp cò. Trong sự im lặng đầy khói sau đó, cô chỉ để lại lời phán quyết:
+Shrieking Legion là một Tacet Discord thuộc hệ thú của rừng. Sinh ra từ lòng đố kỵ, nó bắt chước giọng người để dụ trẻ em đến gần trước khi cướp đi tiếng nói của chúng. Cô đã cảnh báo đội không được giao chiến với nó trên lãnh địa của nó. Nhưng ngoại hình trẻ con của cô không mang lại sự tin tưởng. Họ phớt lờ cô và sa vào bẫy. Những bức tường thung lũng khuếch đại tiếng thét của con quái vật thành một cơn bão âm thanh suýt nữa nghiền nát cả đội. Nhưng cô không hề do dự. Với quyết tâm lạnh lùng, cô tự làm vỡ màng nhĩ mình, máu chảy theo sau khi cô lao tới. Trong nháy mắt, ngọn lửa bùng lên quanh cô. Cô dí súng vào ngực con quái vật và bóp cò. Trong sự im lặng đầy khói sau đó, cô chỉ để lại lời phán quyết:
 "Sự chuộc tội của ngươi bắt đầu từ đây."
 Đám đông chứng kiến sự trừng phạt của con quái vật. Bằng tay phải, cô túm lấy cổ họng nó, và ngọn lửa hình rắn nuốt chửng nó hoàn toàn. Legion thét lên tiếng kêu cuối cùng méo mó trước khi tan biến thành một mảnh tinh chất—bị cô hấp thụ như một khoản trả công xứng đáng. Cơ thể cháy sém, đẫm máu của cô bắt đầu tái sinh với tốc độ đáng sợ. Trong khoảnh khắc, thật khó để phân biệt… ai mới là ác quỷ thực sự.
 Nhưng một sự thật không thể phủ nhận. Cô có thể bỏ trốn một mình. Thay vào đó, cô ở lại. Và vì cô đã làm vậy, họ sống sót.
 Cô phủi tro khỏi vai, biến ra một nắm kem que như từ hư không và đưa cho những người sống sót đang run rẩy với nụ cười thoải mái.
-"Want one?"
+"Muốn không?"
 Với cô, cuộc săn chết chóc này chẳng khác gì một việc vặt thường ngày.
 Khi vị ngọt của kem làm dịu đi ngọn lửa vẫn âm ỉ trong lồng ngực, cô xòe rộng đôi cánh và biến mất vào bầu trời.
-Không ai biết cô đến từ đâu, hay sẽ đi về đâu. Lũ trẻ gọi cô là "Ác Quỷ Kem" sau khi thấy cô ăn hết ba ly kem cao ngất. Những người uyên bác hơn nhìn thấy ngọn lửa tai họa bám trên người cô và nghĩ ngay đến Ác Quỷ Lửa trong truyền thuyết. Nhưng nếu ai dám nhặt những chiếc lông vũ rơi của cô, họ sẽ phát hiện ra điều khác. Những chiếc lông sắc như dao đủ để cắt đôi Discord lại mang một sự dịu dàng kỳ lạ, và… một chút đắng cay đã trải qua thời gian. Có lẽ điều đó cũng tự nhiên thôi. Sự tự do, tinh thần hoang dã như vậy chỉ có thể sinh ra từ sự lưu lạc.
+Không ai biết cô đến từ đâu, hay sẽ đi về đâu. Lũ trẻ gọi cô là "Ác Quỷ Kem" sau khi thấy cô ăn hết ba ly kem cao ngất. Những người uyên bác hơn nhìn thấy ngọn lửa tai họa bám trên người cô và nghĩ ngay đến Ác Quỷ Lửa trong truyền thuyết. Nhưng nếu ai dám nhặt những chiếc lông vũ rơi của cô, họ sẽ phát hiện ra điều khác. Những chiếc lông sắc như dao đủ để cắt đôi Tacet Discord lại mang một sự dịu dàng kỳ lạ, và… một chút đắng cay đã trải qua thời gian. Có lẽ điều đó cũng tự nhiên thôi. Sự tự do, tinh thần hoang dã như vậy chỉ có thể sinh ra từ sự lưu lạc.
 Cô hiếm khi nói về quá khứ của mình. Khi bị ép, câu trả lời của cô luôn ngắn gọn, lảng tránh.
 Muốn biết câu chuyện của cô, người ta phải quay ngược thời gian rất xa. Quay về thời điểm tóc cô vẫn óng ánh màu vàng nhạt và đôi mắt vẫn rực sáng ánh hào quang. Quay về trước khi thế giới gọi cô là… "Galbrena."</t>
         </is>
@@ -2061,24 +2061,24 @@
       <c r="M22" t="inlineStr">
         <is>
           <t>Người ta vẫn nói Angel sinh ra "trong vòng tay của ánh sáng và ngọn lửa." Nàng chào đời vào bình minh vàng rực, được bao bọc bởi ngọn lửa huy hoàng.
-Khả năng Resonance của cha mẹ nàng chỉ ở mức khiêm tốn. Ở &lt;te href=850097&gt;Ragunna&lt;/te&gt;, sự ra đời của nàng hẳn đã được tôn vinh như một phép màu. Nhưng ở Septimont, thần tính không có chỗ đứng. Nơi đây, chỉ có sức mạnh mới khiến người ta kính nể.
-Với một đứa trẻ, khả năng Resonance mạnh mẽ từ sớm không phải lúc nào cũng là món quà. Nó đi kèm với nguy cơ mất kiểm soát thường trực. Angel nhỏ tuổi luôn bám lấy lời dạy của cha mẹ, cẩn thận điều tiết cảm xúc để ngọn lửa của mình không bao giờ làm hại người khác. Ở cái tuổi đáng lẽ chỉ có tiếng cười, nàng lại đứng tách biệt khỏi lũ trẻ khác—dè dặt, xa cách, lạnh lùng. Một số gọi đó là kiêu ngạo. Những đứa nhút nhát tránh xa nàng, còn những đứa táo bạo thì tìm cách khiêu khích, háo hức thử sức với một đứa trẻ khác biệt đến vậy. Có lẽ chúng không có ý hại nàng. Nhưng với chúng, bản chất, tài năng, thậm chí cả con người nàng... đơn giản là quá khác biệt.
+Khả năng Cộng Hưởng của cha mẹ nàng chỉ ở mức khiêm tốn. Ở &lt;te href=850097&gt;Ragunna&lt;/te&gt;, sự ra đời của nàng hẳn đã được tôn vinh như một phép màu. Nhưng ở Septimont, thần tính không có chỗ đứng. Nơi đây, chỉ có sức mạnh mới khiến người ta kính nể.
+Với một đứa trẻ, khả năng Cộng Hưởng mạnh mẽ từ sớm không phải lúc nào cũng là món quà. Nó đi kèm với nguy cơ mất kiểm soát thường trực. Angel nhỏ tuổi luôn bám lấy lời dạy của cha mẹ, cẩn thận điều tiết cảm xúc để ngọn lửa của mình không bao giờ làm hại người khác. Ở cái tuổi đáng lẽ chỉ có tiếng cười, nàng lại đứng tách biệt khỏi lũ trẻ khác—dè dặt, xa cách, lạnh lùng. Một số gọi đó là kiêu ngạo. Những đứa nhút nhát tránh xa nàng, còn những đứa táo bạo thì tìm cách khiêu khích, háo hức thử sức với một đứa trẻ khác biệt đến vậy. Có lẽ chúng không có ý hại nàng. Nhưng với chúng, bản chất, tài năng, thậm chí cả con người nàng... đơn giản là quá khác biệt.
 Cha mẹ nàng là những kẻ lưu vong từ Ragunna, đi xa rồi mới định cư ở Septimont. Cha nàng đã đứng ra chiến đấu khi quái vật tấn công. Mẹ nàng, dù chẳng có gì dư dả, vẫn chia sẻ thức ăn cho những người thiếu thốn hơn. Vào thời điểm mà định kiến giữa hai thành bang vẫn còn, những hành động tử tế ấy đã giúp họ có được chỗ đứng trong thị trấn.
 Mẹ nàng dạy nàng theo Giáo Lý: hãy tử tế, nhân ái, khoan dung và tha thứ. Angel khắc cốt ghi tâm những lời dạy ấy. Nhưng ở Septimont, lòng tốt thôi chưa đủ để đổi lấy sự tôn trọng. Được hun đúc bởi hai nền văn hóa khác biệt, Angel đã tự xây dựng cho mình một nguyên tắc riêng: Hãy đối xử tốt với người khác. Đừng bao giờ gây sự trước. Nhưng nếu ai đó đánh con, hãy đánh lại mạnh hơn.
 May mắn thay, vết bầm tím là chuyện thường tình ở lũ trẻ Septimont. Dù vậy, Angel vẫn cố tránh gây rắc rối cho cha mẹ. Theo thời gian, nàng học cách thích nghi với sự cô độc. Nàng tìm thấy nơi trú ẩn trong lò rèn của người bạn của cha mình, bác Filo. Ít đứa trẻ nào đến đó, nhưng bản năng nào đó trong nàng lại bị thu hút bởi ngọn lửa rực cháy, những tia lửa bắn tung tóe và âm thanh vang dội của búa đập vào sắt. Chính tại đó, nàng gặp một cô bé tóc đỏ. Với bản tính bộc trực, thẳng thắn, cô bé ấy có rất nhiều bạn. Cô bé đã mang đến cho Angel tiếng cười mà tuổi thơ nàng từ lâu thiếu vắng. Họ thường ngồi bên lò rèn, trò chuyện đến tận đêm khuya về những nỗi buồn và ước mơ của mình. Cô bé, Augusta, quan tâm nhất đến những câu chuyện đằng sau mỗi vũ khí, còn Angel thì bị mê hoặc bởi nghi lễ bí ẩn gọi là "tôi luyện." Bác Filo từng giải thích: "Dù là lưỡi kiếm sắc bén nhất cũng chỉ là kim loại thô, nếu không được tôi luyện và tôi rèn."
-Nhiều điều khiến Angel băn khoăn, như tại sao gió ở Septimont luôn mang theo mùi gỉ sét. Nàng nghĩ đó chỉ là hơi thở của những lò rèn và ống thổi. Chỉ đến sau này, khi lớn lên, nàng mới hiểu được điều mà gió thực sự mang theo. Gió đến từ High Nguyên: từ những đầu giáo gãy, những lưỡi kiếm vỡ, và... máu tươi của những chiến binh vừa ngã xuống.
-Mười sáu năm trước, &lt;te href=850159&gt;High Tide&lt;/te&gt; đã tràn qua High Nguyên. Ở &lt;te href=260006&gt;Fabianum&lt;/te&gt;, những cuộc săn lùng không bao giờ kết thúc. Angel chứng kiến cha mẹ mình trở về trong mệt mỏi, thấy những người khác trở về với máu me và thương tích, nghe những lời lặp đi lặp lại về "sức mạnh." Chính lúc đó, một lời thề đã nảy mầm trong lòng nàng.
+Nhiều điều khiến Angel băn khoăn, như tại sao gió ở Septimont luôn mang theo mùi gỉ sét. Nàng nghĩ đó chỉ là hơi thở của những lò rèn và ống thổi. Chỉ đến sau này, khi lớn lên, nàng mới hiểu được điều mà gió thực sự mang theo. Gió đến từ Cao Nguyên: từ những đầu giáo gãy, những lưỡi kiếm vỡ, và... máu tươi của những chiến binh vừa ngã xuống.
+Mười sáu năm trước, &lt;te href=850159&gt;Triều Cường&lt;/te&gt; đã tràn qua Cao Nguyên. Ở &lt;te href=260006&gt;Fabianum&lt;/te&gt;, những cuộc săn lùng không bao giờ kết thúc. Angel chứng kiến cha mẹ mình trở về trong mệt mỏi, thấy những người khác trở về với máu me và thương tích, nghe những lời lặp đi lặp lại về "sức mạnh." Chính lúc đó, một lời thề đã nảy mầm trong lòng nàng.
 Từ ngày ấy, nàng rèn luyện không ngừng nghỉ. Nàng tìm đến người lớn để học võ, theo chân các thợ săn để học cách săn bắt, và giao đấu với bất kỳ ai sẵn sàng. Như một con thú khát nước bên bờ suối, nàng uống cạn mọi nguồn tri thức. Tất cả chỉ vì một mục tiêu: Đấu Trường Khởi Đầu. Kẻ chiến thắng sẽ được đào tạo &lt;te href=850164&gt;Gladiator&lt;/te&gt; ưu tú, và từ đó, con đường trở thành một thợ săn thực thụ sẽ nhanh hơn.
-Nỗ lực đã đơm hoa kết trái. Trong đấu trường, Angel hạ gục hàng chục đối thủ cho đến khi đối mặt với đối thủ được yêu thích: Arkyria, nổi tiếng vì từng một mình đẩy lùi bọn sinh vật của &lt;te href=851023&gt;Dark Tide&lt;/te&gt;. Ý chí của Arkyria, được tôi luyện trong những thử thách sinh tử, buộc Angel phải lùi bước hết lần này đến lần khác. Nàng không thể để cơ hội này vuột mất... Vì vậy, lần đầu tiên, nàng giải phóng Resonance Ability của mình.
-Ánh sáng bùng lên từ Angel như ngọn lửa. Rực cháy, nhưng không thiêu đốt. Chói lọi, nhưng không làm chói mắt. Trong khoảnh khắc đó, tình thế đảo ngược. Chiến thắng thuộc về nàng. Nàng tiến đến test đối thủ đã ngã xuống, chỉ để nghe những lời cay đắng: "Tại sao lại là cô? Tại sao cô lại được ban cho sức mạnh như vậy?"
-Đó là câu hỏi mà Angel đã mang theo từ thuở ấu thơ: Why me?
+Nỗ lực đã đơm hoa kết trái. Trong đấu trường, Angel hạ gục hàng chục đối thủ cho đến khi đối mặt với đối thủ được yêu thích: Arkyria, nổi tiếng vì từng một mình đẩy lùi bọn sinh vật của &lt;te href=851023&gt;Triều Hắc Ám&lt;/te&gt;. Ý chí của Arkyria, được tôi luyện trong những thử thách sinh tử, buộc Angel phải lùi bước hết lần này đến lần khác. Nàng không thể để cơ hội này vuột mất... Vì vậy, lần đầu tiên, nàng giải phóng Khả Năng Cộng Hưởng của mình.
+Ánh sáng bùng lên từ Angel như ngọn lửa. Rực cháy, nhưng không thiêu đốt. Chói lọi, nhưng không làm chói mắt. Trong khoảnh khắc đó, tình thế đảo ngược. Chiến thắng thuộc về nàng. Nàng tiến đến kiểm tra đối thủ đã ngã xuống, chỉ để nghe những lời cay đắng: "Tại sao lại là cô? Tại sao cô lại được ban cho sức mạnh như vậy?"
+Đó là câu hỏi mà Angel đã mang theo từ thuở ấu thơ: Tại sao lại là ta?
 Có biết bao người khác chăm chỉ hơn, tài năng hơn. Tại sao họ không được ban cho món quà này?
 Nếu họ có cùng sức mạnh, liệu họ có tránh được đau khổ?
 Nếu nàng có thể làm chủ sức mạnh này, liệu nàng có thể giúp đỡ họ? Nếu như...
-Những suy nghĩ của nàng bị ngắt quãng bởi tiếng kêu của bầy Griffrex trên bầu trời. Chúng bay về phía High Nguyên—nơi mọi cuộc săn bắt đầu.
-Yes. Ít nhất, nàng đã chứng minh được mình có thể kiểm soát sức mạnh của mình. Sớm thôi, nàng cũng sẽ cưỡi một con Griffrex ra chiến trường, tiêu diệt lũ Tidespawn độc ác để bảo vệ nhiều người hơn. Đó là lời thề của nàng. "Cuộc săn" của nàng sắp bắt đầu.
+Những suy nghĩ của nàng bị ngắt quãng bởi tiếng kêu của bầy Griffrex trên bầu trời. Chúng bay về phía Cao Nguyên—nơi mọi cuộc săn bắt đầu.
+Đúng vậy. Ít nhất, nàng đã chứng minh được mình có thể kiểm soát sức mạnh của mình. Sớm thôi, nàng cũng sẽ cưỡi một con Griffrex ra chiến trường, tiêu diệt lũ Tidespawn độc ác để bảo vệ nhiều người hơn. Đó là lời thề của nàng. "Cuộc săn" của nàng sắp bắt đầu.
 Mọi thứ lẽ ra phải diễn ra như vậy. Mọi thứ đã diễn ra như vậy. Nhưng số phận, dù qua một sự trớ trêu cay nghiệt hay một âm mưu được lên kế hoạch từ lâu, cuối cùng cũng lộ diện: Những gì nó ban tặng, nó sẽ lấy đi. Những gì nhân từ, nó sẽ dạy cách gây hại. Những gì không biết sợ, nó sẽ bẻ gãy—cho đến khi quỳ gối và không bao giờ đứng dậy được nữa.
-Nhưng Angel chưa từng đặt chân đến Tetragon Temple. Nàng không tìm hiểu số phận. Nàng cũng không muốn. Nàng chỉ biết một điều: nếu ai đó đánh nàng, nàng sẽ đánh trả mạnh hơn. Dù đó là con người, thần linh, hay... chính số phận.</t>
+Nhưng Angel chưa từng đặt chân đến Đền Tetragon. Nàng không tìm hiểu số phận. Nàng cũng không muốn. Nàng chỉ biết một điều: nếu ai đó đánh nàng, nàng sẽ đánh trả mạnh hơn. Dù đó là con người, thần linh, hay... chính số phận.</t>
         </is>
       </c>
     </row>
@@ -2163,7 +2163,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cô sẽ không bao giờ quên lần đầu tiên mình "nuốt chửng" một &lt;te href=850081&gt;Discord&lt;/te&gt;. Cơ thể cô phản kháng dữ dội, cơn đau thiêu đốt nội tạng như thể linh hồn sắp bị hóa tro. Nhưng đau đớn còn có thể chịu đựng được—điều không thể chịu nổi là sự yếu đuối mà nó phơi bày.
+          <t xml:space="preserve">Cô sẽ không bao giờ quên lần đầu tiên mình "nuốt chửng" một &lt;te href=850081&gt;Tacet Discord&lt;/te&gt;. Cơ thể cô phản kháng dữ dội, cơn đau thiêu đốt nội tạng như thể linh hồn sắp bị hóa tro. Nhưng đau đớn còn có thể chịu đựng được—điều không thể chịu nổi là sự yếu đuối mà nó phơi bày.
 </t>
         </is>
       </c>
@@ -2426,7 +2426,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Kích hoạt hoàn toàn Chuỗi Resonance Spectro của Rover ({0}/{1} đã kích hoạt)</t>
+          <t>Kích hoạt hoàn toàn Resonance Chain Spectro của Rover ({0}/{1} đã kích hoạt)</t>
         </is>
       </c>
     </row>
@@ -2491,7 +2491,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Kích hoạt hoàn toàn Chuỗi Resonance của Yangyang ({0}/{1} đã kích hoạt)</t>
+          <t>Kích hoạt hoàn toàn Resonance Chain của Yangyang ({0}/{1} đã kích hoạt)</t>
         </is>
       </c>
     </row>
@@ -2556,7 +2556,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Fully activate Chixia's Resonance Chain ({0}/{1} đã kích hoạt)</t>
+          <t>Kích hoạt hoàn toàn Resonance Chain của Chixia ({0}/{1} đã kích hoạt)</t>
         </is>
       </c>
     </row>
@@ -2621,7 +2621,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Fully activate Baizhi's Resonance Chain ({0}/{1} đã kích hoạt)</t>
+          <t>Kích hoạt hoàn toàn Resonance Chain của Baizhi ({0}/{1} đã kích hoạt)</t>
         </is>
       </c>
     </row>
@@ -2686,7 +2686,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Fully activate Danjin's Resonance Chain ({0}/{1} đã kích hoạt)</t>
+          <t>Kích hoạt hoàn toàn Resonance Chain của Danjin ({0}/{1} đã kích hoạt)</t>
         </is>
       </c>
     </row>
@@ -2751,7 +2751,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Kích hoạt hoàn toàn Chuỗi Resonance của San'hua ({0}/{1} đã kích hoạt)</t>
+          <t>Kích hoạt hoàn toàn Resonance Chain của San'hua ({0}/{1} đã kích hoạt)</t>
         </is>
       </c>
     </row>
@@ -2816,7 +2816,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Fully activate Taoqi's Resonance Chain ({0}/{1} đã kích hoạt)</t>
+          <t>Kích hoạt toàn bộ Resonance Chain của Taoqi ({0}/{1} đã kích hoạt)</t>
         </is>
       </c>
     </row>
@@ -2881,7 +2881,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Kích hoạt hoàn toàn Chuỗi Resonance của Mortefi ({0}/{1} đã kích hoạt)</t>
+          <t>Kích hoạt hoàn toàn Resonance Chain của Mortefi ({0}/{1} đã kích hoạt)</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Fully activate Yuanwu's Resonance Chain ({0}/{1} đã kích hoạt)</t>
+          <t>Kích hoạt hoàn toàn Resonance Chain của Yuanwu ({0}/{1} đã kích hoạt)</t>
         </is>
       </c>
     </row>
@@ -3011,7 +3011,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Fully activate Aalto's Resonance Chain ({0}/{1} đã kích hoạt)</t>
+          <t>Kích Hoạt Hoàn Toàn Resonance Chain Aalto ({0}/{1} đã kích hoạt)</t>
         </is>
       </c>
     </row>
@@ -3076,7 +3076,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Fully activate Verina's Resonance Chain ({0}/{1} đã kích hoạt)</t>
+          <t>Kích hoạt toàn bộ Resonance Chain của Verina ({0}/{1} đã kích hoạt)</t>
         </is>
       </c>
     </row>
@@ -3141,7 +3141,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Fully activate Encore's Resonance Chain ({0}/{1} đã kích hoạt)</t>
+          <t>Kích hoạt hoàn toàn Resonance Chain của Encore ({0}/{1} đã kích hoạt)</t>
         </is>
       </c>
     </row>
@@ -3206,7 +3206,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Kích hoạt hoàn toàn Chuỗi Resonance của Calcharo ({0}/{1} đã kích hoạt)</t>
+          <t>Kích hoạt hoàn toàn Resonance Chain của Calcharo ({0}/{1} đã kích hoạt)</t>
         </is>
       </c>
     </row>
@@ -3271,7 +3271,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Kích hoạt toàn bộ Chuỗi Resonance của Lingyang ({0}/{1} đã kích hoạt)</t>
+          <t>Kích hoạt toàn bộ Resonance Chain của Lingyang ({0}/{1} đã kích hoạt)</t>
         </is>
       </c>
     </row>
@@ -3336,7 +3336,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Kích hoạt toàn bộ Chuỗi Resonance của Jianxin ({0}/{1} đã kích hoạt)</t>
+          <t>Kích hoạt toàn bộ Resonance Chain của Jianxin ({0}/{1} đã kích hoạt)</t>
         </is>
       </c>
     </row>
@@ -3401,7 +3401,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Fully activate Jiyan's Resonance Chain ({0}/{1} đã kích hoạt)</t>
+          <t>Kích hoạt toàn bộ Resonance Chain của Jiyan ({0}/{1} đã kích hoạt)</t>
         </is>
       </c>
     </row>
@@ -3466,7 +3466,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Fully activate Yinlin's Resonance Chain ({0}/{1} đã kích hoạt)</t>
+          <t>Kích hoạt hoàn toàn Resonance Chain của Yinlin ({0}/{1} đã kích hoạt)</t>
         </is>
       </c>
     </row>
@@ -3531,7 +3531,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Fully activate Jinhsi's Resonance Chain ({0}/{1} đã kích hoạt)</t>
+          <t>Kích hoạt toàn bộ Resonance Chain của Jinhsi ({0}/{1} đã kích hoạt)</t>
         </is>
       </c>
     </row>
@@ -3596,7 +3596,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Kích hoạt hoàn toàn Chuỗi Resonance của Changli ({0}/{1} đã kích hoạt)</t>
+          <t>Kích hoạt hoàn toàn Resonance Chain của Changli ({0}/{1} đã kích hoạt)</t>
         </is>
       </c>
     </row>
@@ -3661,7 +3661,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Kích hoạt toàn bộ Chuỗi Resonance của Xiangli Yao ({0}/{1} đã kích hoạt)</t>
+          <t>Kích hoạt toàn bộ Resonance Chain của Xiangli Yao ({0}/{1} đã kích hoạt)</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Fully activate Zhezhi's Resonance Chain ({0}/{1} đã kích hoạt)</t>
+          <t>Kích hoạt hoàn toàn Resonance Chain của Zhezhi ({0}/{1} đã kích hoạt)</t>
         </is>
       </c>
     </row>
@@ -3791,7 +3791,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Kích hoạt toàn bộ Chuỗi Resonance của Shorekeeper ({0}/{1} đã kích hoạt)</t>
+          <t>Kích hoạt toàn bộ Resonance Chain của Shorekeeper ({0}/{1} đã kích hoạt)</t>
         </is>
       </c>
     </row>
@@ -3856,7 +3856,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Fully activate Youhu's Resonance Chain ({0}/{1} đã kích hoạt)</t>
+          <t>Kích hoạt hoàn toàn Resonance Chain của Youhu ({0}/{1} đã kích hoạt)</t>
         </is>
       </c>
     </row>
@@ -3921,7 +3921,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Kích hoạt hoàn toàn Chuỗi Resonance của Camellya ({0}/{1} đã kích hoạt)</t>
+          <t>Kích hoạt hoàn toàn Resonance Chain của Camellya ({0}/{1} đã kích hoạt)</t>
         </is>
       </c>
     </row>
@@ -3986,7 +3986,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Fully activate Lumi's Resonance Chain ({0}/{1} đã kích hoạt)</t>
+          <t>Kích hoạt toàn bộ Resonance Chain của Lumi ({0}/{1} đã kích hoạt)</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Kích hoạt hoàn toàn Chuỗi Resonance của Carlotta ({0}/{1} đã kích hoạt)</t>
+          <t>Kích hoạt hoàn toàn Resonance Chain của Carlotta ({0}/{1} đã kích hoạt)</t>
         </is>
       </c>
     </row>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Fully activate Roccia's Resonance Chain ({0}/{1} đã kích hoạt)</t>
+          <t>Kích hoạt hoàn toàn Resonance Chain của Roccia ({0}/{1} đã kích hoạt)</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Fully activate Brant's Resonance Chain ({0}/{1} đã kích hoạt)</t>
+          <t>Kích hoạt hoàn toàn Resonance Chain của Brant ({0}/{1} đã kích hoạt)</t>
         </is>
       </c>
     </row>
@@ -4246,7 +4246,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Fully activate Phoebe's Resonance Chain ({0}/{1} đã kích hoạt)</t>
+          <t>Kích hoạt hoàn toàn Resonance Chain của Phoebe ({0}/{1} đã kích hoạt)</t>
         </is>
       </c>
     </row>
@@ -4311,7 +4311,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Kích hoạt hoàn toàn Chuỗi Resonance của Cantarella ({0}/{1} đã kích hoạt)</t>
+          <t>Kích hoạt hoàn toàn Resonance Chain của Cantarella ({0}/{1} đã kích hoạt)</t>
         </is>
       </c>
     </row>
@@ -4376,7 +4376,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Kích hoạt hoàn toàn Chuỗi Resonance của Ciaccona ({0}/{1} đã kích hoạt)</t>
+          <t>Kích hoạt hoàn toàn Resonance Chain của Ciaccona ({0}/{1} đã kích hoạt)</t>
         </is>
       </c>
     </row>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Fully activate Zani's Resonance Chain ({0}/{1} đã kích hoạt)</t>
+          <t>Kích hoạt hoàn toàn Resonance Chain của Zani ({0}/{1} đã kích hoạt)</t>
         </is>
       </c>
     </row>
@@ -4506,7 +4506,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Kích hoạt hoàn toàn Chuỗi Resonance Havoc của Rover ({0}/{1} đã kích hoạt)</t>
+          <t>Kích hoạt hoàn toàn Resonance Chain Havoc của Rover ({0}/{1} đã kích hoạt)</t>
         </is>
       </c>
     </row>
@@ -4571,7 +4571,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Kích hoạt hoàn toàn Chuỗi Resonance Aero của Rover ({0}/{1} đã kích hoạt)</t>
+          <t>Kích hoạt hoàn toàn Resonance Chain Aero của Rover ({0}/{1} đã kích hoạt)</t>
         </is>
       </c>
     </row>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Kích hoạt hoàn toàn Chuỗi Resonance của Cartethyia ({0}/{1} đã kích hoạt)</t>
+          <t>Kích hoạt hoàn toàn Resonance Chain của Cartethyia ({0}/{1} đã kích hoạt)</t>
         </is>
       </c>
     </row>
@@ -4701,7 +4701,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Kích hoạt hoàn toàn Chuỗi Resonance của Lupa ({0}/{1} đã kích hoạt)</t>
+          <t>Kích hoạt hoàn toàn Resonance Chain của Lupa ({0}/{1} đã kích hoạt)</t>
         </is>
       </c>
     </row>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Kích hoạt hoàn toàn Chuỗi Resonance của Phrolova ({0}/{1} đã kích hoạt)</t>
+          <t>Kích hoạt hoàn toàn Resonance Chain của Phrolova ({0}/{1} đã kích hoạt)</t>
         </is>
       </c>
     </row>
@@ -4831,7 +4831,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Kích hoạt hoàn toàn Chuỗi Resonance của Augusta ({0}/{1} đã kích hoạt)</t>
+          <t>Kích hoạt hoàn toàn Resonance Chain của Augusta ({0}/{1} đã kích hoạt)</t>
         </is>
       </c>
     </row>
@@ -4896,7 +4896,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Kích hoạt toàn bộ Chuỗi Resonance của Iuno ({0}/{1} đã kích hoạt)</t>
+          <t>Kích hoạt toàn bộ Resonance Chain của Iuno ({0}/{1} đã kích hoạt)</t>
         </is>
       </c>
     </row>
@@ -4961,7 +4961,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Kích hoạt hoàn toàn Chuỗi Resonance của Galbrena</t>
+          <t>Kích hoạt hoàn toàn Resonance Chain của Galbrena</t>
         </is>
       </c>
     </row>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Kích hoạt hoàn toàn Chuỗi Resonance của Qiuyuan</t>
+          <t>Kích hoạt hoàn toàn Resonance Chain của Qiuyuan</t>
         </is>
       </c>
     </row>
@@ -5091,7 +5091,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Kích hoạt hoàn toàn Chuỗi Resonance của Galbrena ({0}/{1} đã kích hoạt)</t>
+          <t>Kích hoạt hoàn toàn Resonance Chain của Galbrena ({0}/{1} đã kích hoạt)</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Kích hoạt hoàn toàn Chuỗi Resonance của Qiuyuan ({0}/{1} đã kích hoạt)</t>
+          <t>Kích hoạt hoàn toàn Resonance Chain của Qiuyuan ({0}/{1} đã kích hoạt)</t>
         </is>
       </c>
     </row>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Tăng DMG III</t>
+          <t>Tăng Sát Thương III</t>
         </is>
       </c>
     </row>
@@ -5611,7 +5611,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Gây Sát Thương Basic Attack &lt;color=Highlight&gt;{0}&lt;/color&gt; lần sẽ triệu hồi &lt;color=Highlight&gt;{1}&lt;/color&gt; &lt;color=Highlight&gt;&lt;te href=851100&gt;Combo - Rice Dango Missile&lt;/te&gt;&lt;/color&gt;.</t>
+          <t>Gây Sát Thương Basic Attack &lt;color=Highlight&gt;{0}&lt;/color&gt; lần sẽ triệu hồi &lt;color=Highlight&gt;{1}&lt;/color&gt; &lt;color=Highlight&gt;&lt;te href=851100&gt;Combo - Tên Lửa Bánh Dango&lt;/te&gt;&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -5676,7 +5676,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Khi &lt;color=Highlight&gt;&lt;te href=851100&gt;Combo - Rice Dango Missile&lt;/te&gt;&lt;/color&gt; hoặc &lt;color=Highlight&gt;&lt;te href=851101&gt;Combo - Rice Dango Missile: Enhanced&lt;/te&gt;&lt;/color&gt; trúng mục tiêu, các tên lửa tiếp theo của &lt;color=Highlight&gt;&lt;te href=851100&gt;Combo - Rice Dango Missile&lt;/te&gt;&lt;/color&gt; và &lt;color=Highlight&gt;&lt;te href=851101&gt;Combo - Rice Dango Missile: Enhanced&lt;/te&gt;&lt;/color&gt; sẽ nhận thêm &lt;color=Highlight&gt;{0}&lt;/color&gt; Tấn Công trong &lt;color=Highlight&gt;{2}s&lt;/color&gt;, có thể tích lũy tối đa &lt;color=Highlight&gt;{1}&lt;/color&gt; lần.</t>
+          <t>Khi &lt;color=Highlight&gt;&lt;te href=851100&gt;Hợp Kỹ - Tên Lửa Bánh Dango&lt;/te&gt;&lt;/color&gt; hoặc &lt;color=Highlight&gt;&lt;te href=851101&gt;Hợp Kỹ - Tên Lửa Bánh Dango: Cường Hóa&lt;/te&gt;&lt;/color&gt; trúng mục tiêu, các tên lửa tiếp theo của &lt;color=Highlight&gt;&lt;te href=851100&gt;Hợp Kỹ - Tên Lửa Bánh Dango&lt;/te&gt;&lt;/color&gt; và &lt;color=Highlight&gt;&lt;te href=851101&gt;Hợp Kỹ - Tên Lửa Bánh Dango: Cường Hóa&lt;/te&gt;&lt;/color&gt; sẽ nhận thêm &lt;color=Highlight&gt;{0}&lt;/color&gt; Tấn Công trong &lt;color=Highlight&gt;{2} giây&lt;/color&gt;, có thể tích lũy tối đa &lt;color=Highlight&gt;{1}&lt;/color&gt; lần.</t>
         </is>
       </c>
     </row>
@@ -5741,7 +5741,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Crit. DMG của &lt;color=Highlight&gt;&lt;te href=851100&gt;Combo - Rice Dango Missile&lt;/te&gt;&lt;/color&gt; và &lt;color=Highlight&gt;&lt;te href=851101&gt;Combo - Rice Dango Missile: Enhanced&lt;/te&gt;&lt;/color&gt; tăng thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;.</t>
+          <t>Crit. DMG của &lt;color=Highlight&gt;&lt;te href=851100&gt;Combo - Tên Lửa Bánh Dango&lt;/te&gt;&lt;/color&gt; và &lt;color=Highlight&gt;&lt;te href=851101&gt;Combo - Tên Lửa Bánh Dango: Cường Hóa&lt;/te&gt;&lt;/color&gt; tăng thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -5806,7 +5806,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Kích hoạt Skill Kết thúc triệu hồi &lt;color=Highlight&gt;&lt;te href=851102&gt;Burst - Blazing Pillar&lt;/te&gt;&lt;/color&gt;.</t>
+          <t>Kích hoạt Kỹ năng Kết thúc triệu hồi &lt;color=Highlight&gt;&lt;te href=851102&gt;Đòn Phát Lửa - Trụ Lửa Bùng Cháy&lt;/te&gt;&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -5936,7 +5936,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Khi &lt;color=Highlight&gt;&lt;te href=851103&gt;Burst - Scorching Impact&lt;/te&gt;&lt;/color&gt; hoặc &lt;color=Highlight&gt;&lt;te href=851102&gt;Burst - Blazing Pillar&lt;/te&gt;&lt;/color&gt; trúng kẻ địch, tất cả Resonators trong đội sẽ hồi HP mỗi giây trong &lt;color=Highlight&gt;{1}s&lt;/color&gt;, với tốc độ hồi bằng &lt;color=Highlight&gt;{0}&lt;/color&gt; Tấn Công của Resonators. Hiệu ứng này chỉ có thể kích hoạt &lt;color=Highlight&gt;&lt;SapTag=3&gt;{3}&lt;/color&gt;&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=3} mỗi &lt;color=Highlight&gt;{2} giây&lt;/color&gt;.</t>
+          <t>Khi &lt;color=Highlight&gt;&lt;te href=851103&gt;Kỹ Năng Q - Va Chạm Nảy Lửa&lt;/te&gt;&lt;/color&gt; hoặc &lt;color=Highlight&gt;&lt;te href=851102&gt;Kỹ Năng Q - Trụ Lửa Bừng Cháy&lt;/te&gt;&lt;/color&gt; trúng kẻ địch, tất cả Resonator trong đội sẽ hồi HP mỗi giây trong &lt;color=Highlight&gt;{1} giây&lt;/color&gt;, với tốc độ hồi bằng &lt;color=Highlight&gt;{0}&lt;/color&gt; ATK của Resonator. Hiệu ứng này chỉ có thể kích hoạt &lt;color=Highlight&gt;&lt;SapTag=3&gt;{3}&lt;/color&gt;&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=3} mỗi &lt;color=Highlight&gt;{2} giây&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -6001,7 +6001,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Trong &lt;color=Highlight&gt;&lt;te href=851104&gt;Boost - Namipon Aid&lt;/te&gt;&lt;/color&gt;, nhận sát thương sẽ phục hồi &lt;color=Highlight&gt;{0}&lt;/color&gt; Độ Stability.</t>
+          <t>Trong &lt;color=Highlight&gt;&lt;te href=851104&gt;Tăng Cường - Hỗ Trợ Namipon&lt;/te&gt;&lt;/color&gt;, nhận sát thương sẽ phục hồi &lt;color=Highlight&gt;{0}&lt;/color&gt; Độ Ổn Định.</t>
         </is>
       </c>
     </row>
@@ -6066,7 +6066,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Khi rời khỏi &lt;color=Highlight&gt;&lt;te href=851104&gt;Boost - Namipon Aid&lt;/te&gt;&lt;/color&gt;, tất cả Resonators trong đội sẽ được hồi phục HP bằng &lt;color=Highlight&gt;{0}&lt;/color&gt; HP tối đa của người sử dụng.</t>
+          <t>Khi rời khỏi &lt;color=Highlight&gt;&lt;te href=851104&gt;Tăng Cường - Namipon Hỗ Trợ&lt;/te&gt;&lt;/color&gt;, tất cả Resonator trong đội sẽ được hồi phục HP bằng &lt;color=Highlight&gt;{0}&lt;/color&gt; HP tối đa của người sử dụng.</t>
         </is>
       </c>
     </row>
@@ -6131,7 +6131,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Khi kích hoạt &lt;color=Highlight&gt;&lt;te href=851104&gt;Boost - Namipon Aid&lt;/te&gt;&lt;/color&gt;, toàn bộ Resonators trong đội tăng &lt;color=Highlight&gt;{0}&lt;/color&gt; Tấn Công trong &lt;color=Highlight&gt;{1}s&lt;/color&gt;.</t>
+          <t>Khi kích hoạt &lt;color=Highlight&gt;&lt;te href=851104&gt;Boost - Namipon Aid&lt;/te&gt;&lt;/color&gt;, toàn bộ Resonator trong đội tăng &lt;color=Highlight&gt;{0}&lt;/color&gt; ATK trong &lt;color=Highlight&gt;{1} giây&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -6196,7 +6196,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Khi kích hoạt &lt;color=Highlight&gt;&lt;te href=851105&gt;Boost - Sprint&lt;/te&gt;&lt;/color&gt;, sẽ triệu hồi thêm &lt;color=Highlight&gt;&lt;te href=851116&gt;Burst - Shock Impact&lt;/te&gt;&lt;/color&gt;, gây Sát Thương lên mục tiêu bằng &lt;color=Highlight&gt;{0}&lt;/color&gt; HP tối đa của Resonator.</t>
+          <t>Khi kích hoạt &lt;color=Highlight&gt;&lt;te href=851105&gt;Tăng Cường - Bứt Tốc&lt;/te&gt;&lt;/color&gt;, sẽ triệu hồi thêm &lt;color=Highlight&gt;&lt;te href=851116&gt;Kích Nổ - Xung Kích Sét&lt;/te&gt;&lt;/color&gt;, gây Sát Thương lên mục tiêu bằng &lt;color=Highlight&gt;{0}&lt;/color&gt; HP tối đa của Cộng Hưởng Giả.</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;&lt;te href=851116&gt;Burst - Shock Impact&lt;/te&gt;&lt;/color&gt; ngoài ra còn gây sát thương bằng &lt;color=Highlight&gt;{1}&lt;/color&gt; HP tối đa của người sử dụng &lt;color=Highlight&gt;{0}&lt;/color&gt; lần khi trúng mục tiêu.</t>
+          <t>&lt;color=Highlight&gt;&lt;te href=851116&gt;Kỹ Năng Bùng Nổ - Sốc Tác Động&lt;/te&gt;&lt;/color&gt; ngoài ra còn gây DMG bằng &lt;color=Highlight&gt;{1}&lt;/color&gt; HP tối đa của người sử dụng &lt;color=Highlight&gt;{0}&lt;/color&gt; lần khi trúng mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -6326,7 +6326,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Trong &lt;color=Highlight&gt;&lt;te href=851105&gt;Boost - Sprint&lt;/te&gt;&lt;/color&gt;, Resonator nhận được &lt;color=Highlight&gt;{0}&lt;/color&gt; Giảm Sát Thương.</t>
+          <t>Trong &lt;color=Highlight&gt;&lt;te href=851105&gt;Tăng Cường - Tăng Tốc&lt;/te&gt;&lt;/color&gt;, Resonator nhận được &lt;color=Highlight&gt;{0}&lt;/color&gt; Giảm Sát Thương.</t>
         </is>
       </c>
     </row>
@@ -6391,7 +6391,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;&lt;te href=851107&gt;Combo - Hỗ Trợ Missile&lt;/te&gt;&lt;/color&gt; ngoài ra còn gây sát thương bằng &lt;color=Highlight&gt;{1}&lt;/color&gt; Tấn Công của Resonator &lt;color=Highlight&gt;&lt;SapTag=0&gt;{0}&lt;/SapTag&gt;&lt;/color&gt; {Cus:Sap,S=lần P=lần SapTag=0} và áp &lt;color=Highlight&gt;{2}&lt;/color&gt; tầng &lt;color=Highlight&gt;&lt;te href=851108&gt;Status - Waveworn Bane&lt;/te&gt;&lt;/color&gt; khi trúng mục tiêu.</t>
+          <t>&lt;color=Highlight&gt;&lt;te href=851107&gt;Combo - Hỏa Tiễn Hỗ Trợ&lt;/te&gt;&lt;/color&gt; ngoài ra còn gây DMG bằng &lt;color=Highlight&gt;{1}&lt;/color&gt; ATK của Resonator &lt;color=Highlight&gt;&lt;SapTag=0&gt;{0}&lt;/SapTag&gt;&lt;/color&gt; {Cus:Sap,S=lần P=lần SapTag=0} và áp &lt;color=Highlight&gt;{2}&lt;/color&gt; tầng &lt;color=Highlight&gt;&lt;te href=851108&gt;Trạng Thái - Ác Nghiệt Sóng Dữ&lt;/te&gt;&lt;/color&gt; khi trúng mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -6456,7 +6456,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Gây &lt;color=Highlight&gt;&lt;te href=851108&gt;Status - Waveworn Bane&lt;/te&gt;&lt;/color&gt; lên mục tiêu sẽ tăng số tầng tối đa của &lt;color=Highlight&gt;&lt;te href=851108&gt;Status - Waveworn Bane&lt;/te&gt;&lt;/color&gt; mà mục tiêu có thể nhận lên &lt;color=Highlight&gt;{0}&lt;/color&gt;.</t>
+          <t>Gây &lt;color=Highlight&gt;&lt;te href=851108&gt;Trạng Thái - Tai Họa Sóng Dữ&lt;/te&gt;&lt;/color&gt; lên mục tiêu sẽ tăng số tầng tối đa của &lt;color=Highlight&gt;&lt;te href=851108&gt;Trạng Thái - Tai Họa Sóng Dữ&lt;/te&gt;&lt;/color&gt; mà mục tiêu có thể nhận lên &lt;color=Highlight&gt;{0}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -6521,7 +6521,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Namipon rung chuyển mặt đất và để lại 2 Vùng Thanh Tẩy. Mục tiêu trong vùng chịu sát thương mỗi giây bằng &lt;color=Highlight&gt;{0}&lt;/color&gt; Tấn Công của Resonator và bị dính &lt;color=Highlight&gt;{1}&lt;/color&gt; tầng &lt;color=Highlight&gt;&lt;te href=851108&gt;Status - Waveworn Bane&lt;/te&gt;&lt;/color&gt; trong &lt;color=Highlight&gt;{2}s&lt;/color&gt;.</t>
+          <t>Namipon rung chuyển mặt đất và để lại 2 Vùng Thanh Tẩy. Mục tiêu trong vùng chịu DMG mỗi giây bằng &lt;color=Highlight&gt;{0}&lt;/color&gt; ATK của Resonator và bị dính &lt;color=Highlight&gt;{1}&lt;/color&gt; tầng &lt;color=Highlight&gt;&lt;te href=851108&gt;Trạng Thái - Tai Họa Sóng Dữ&lt;/te&gt;&lt;/color&gt; trong &lt;color=Highlight&gt;{2} giây&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -6586,7 +6586,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Khi sóng xung kích trúng mục tiêu, &lt;color=Highlight&gt;&lt;te href=851108&gt;Status - Waveworn Bane&lt;/te&gt;&lt;/color&gt; sẽ gây thêm sát thương dựa trên số lượt chồng trên mục tiêu, kích hoạt &lt;color=Highlight&gt;{0}&lt;/color&gt; lần.</t>
+          <t>Khi sóng xung kích trúng mục tiêu, &lt;color=Highlight&gt;&lt;te href=851108&gt;Trạng Thái - Tai Họa Sóng Dữ&lt;/te&gt;&lt;/color&gt; sẽ gây thêm DMG dựa trên số lượt chồng trên mục tiêu, kích hoạt &lt;color=Highlight&gt;{0}&lt;/color&gt; lần.</t>
         </is>
       </c>
     </row>
@@ -6651,7 +6651,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Khi &lt;color=Highlight&gt;&lt;te href=851110&gt;Combo - Dessert Strike&lt;/te&gt;&lt;/color&gt; và &lt;color=Highlight&gt;&lt;te href=851111&gt;Combo - Dessert Strike: Enhanced&lt;/te&gt;&lt;/color&gt; trúng mục tiêu, có thể gây hiệu ứng Havoc Bane, Spectro Frazzle, Aero Erosion hoặc &lt;color=Highlight&gt;&lt;te href=851108&gt;Status - Waveworn Bane&lt;/te&gt;&lt;/color&gt;.</t>
+          <t>Khi &lt;color=Highlight&gt;&lt;te href=851110&gt;Combo - Đòn Đánh Bánh Ngọt&lt;/te&gt;&lt;/color&gt; và &lt;color=Highlight&gt;&lt;te href=851111&gt;Combo - Đòn Đánh Bánh Ngọt: Cường Hóa&lt;/te&gt;&lt;/color&gt; trúng mục tiêu, có thể gây hiệu ứng Havoc Bane, Spectro Frazzle, Aero Erosion hoặc &lt;color=Highlight&gt;&lt;te href=851108&gt;Trạng Thái - Waveworn Bane&lt;/te&gt;&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -6716,7 +6716,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;&lt;te href=851110&gt;Combo - Dessert Strike&lt;/te&gt;&lt;/color&gt; và &lt;color=Highlight&gt;&lt;te href=851111&gt;Combo - Dessert Strike: Enhanced&lt;/te&gt;&lt;/color&gt; nhận &lt;color=Highlight&gt;{0}&lt;/color&gt; Tăng Sát Thương.</t>
+          <t>&lt;color=Highlight&gt;&lt;te href=851110&gt;Combo - Đòn Đánh Sa Mạc&lt;/te&gt;&lt;/color&gt; và &lt;color=Highlight&gt;&lt;te href=851111&gt;Combo - Đòn Đánh Sa Mạc: Cường Hóa&lt;/te&gt;&lt;/color&gt; nhận &lt;color=Highlight&gt;{0}&lt;/color&gt; Tăng Sát Thương.</t>
         </is>
       </c>
     </row>
@@ -6781,7 +6781,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Khi kích hoạt &lt;color=Highlight&gt;&lt;te href=851112&gt;Boost - Satisfaction&lt;/te&gt;&lt;/color&gt;, nhận thêm &lt;color=Highlight&gt;{0}&lt;/color&gt; Tăng Sát Thương Toàn Bộ trong &lt;color=Highlight&gt;{1}s&lt;/color&gt;.</t>
+          <t>Khi kích hoạt &lt;color=Highlight&gt;&lt;te href=851112&gt;Tăng Cường - Thỏa Mãn&lt;/te&gt;&lt;/color&gt;, nhận thêm &lt;color=Highlight&gt;{0}&lt;/color&gt; Tăng Sát Thương Toàn Bộ trong &lt;color=Highlight&gt;{1} giây&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -6846,7 +6846,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Khi kích hoạt &lt;color=Highlight&gt;&lt;te href=851114&gt;Boost - Coffee's Shelter&lt;/te&gt;&lt;/color&gt;, sẽ nhận thêm Shield tương đương &lt;color=Highlight&gt;{0}&lt;/color&gt; Tấn Công của Resonator trong &lt;color=Highlight&gt;{1}s&lt;/color&gt;.</t>
+          <t>Khi kích hoạt &lt;color=Highlight&gt;&lt;te href=851114&gt;Tăng Cường - Nơi Trú Ẩn Của Cà Phê&lt;/te&gt;&lt;/color&gt;, sẽ nhận thêm Khiên tương đương &lt;color=Highlight&gt;{0}&lt;/color&gt; ATK của Resonator trong &lt;color=Highlight&gt;{1} giây&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -6911,7 +6911,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Resonator nhận một Lớp Shield tương đương &lt;color=Highlight&gt;{1}&lt;/color&gt; Tấn Công của bản thân, kéo dài &lt;color=Highlight&gt;{2}s&lt;/color&gt;, mỗi &lt;color=Highlight&gt;{0}s&lt;/color&gt;.</t>
+          <t>Resonator nhận một Lớp Khiên tương đương &lt;color=Highlight&gt;{1}&lt;/color&gt; ATK của bản thân, kéo dài &lt;color=Highlight&gt;{2} giây&lt;/color&gt;, mỗi &lt;color=Highlight&gt;{0} giây&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -6976,7 +6976,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Khi Độ Stability ở mức &lt;color=Highlight&gt;{0}&lt;/color&gt; hoặc thấp hơn, Tấn Công của Resonator tăng thêm &lt;color=Highlight&gt;{1}&lt;/color&gt;.</t>
+          <t>Khi Độ Ổn Định ở mức &lt;color=Highlight&gt;{0}&lt;/color&gt; hoặc thấp hơn, ATK của Resonator tăng thêm &lt;color=Highlight&gt;{1}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -7041,7 +7041,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Khi HP ở mức &lt;color=Highlight&gt;{0}&lt;/color&gt;, nhận sát thương không làm giảm Độ Stability.</t>
+          <t>Khi HP ở mức &lt;color=Highlight&gt;{0}&lt;/color&gt;, nhận sát thương không làm giảm Độ Ổn Định.</t>
         </is>
       </c>
     </row>
@@ -7106,7 +7106,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Khi Độ Stability đạt Trạng Thái Nguy Kịch, Dodge Counter còn gây thêm &lt;color=Highlight&gt;{0}&lt;/color&gt; lần sát thương, mỗi lần tương đương &lt;color=Highlight&gt;{1}&lt;/color&gt; Tấn Công của Resonator. Hiệu ứng này có thể kích hoạt &lt;color=Highlight&gt;&lt;SapTag=2&gt;{3}&lt;/SapTag&gt;&lt;/color&gt; {Cus:Sap,S=lần P=lần SapTag=2} mỗi &lt;color=Highlight&gt;{2}s&lt;/color&gt;.</t>
+          <t>Khi Độ Ổn Định đạt Trạng Thái Nguy Kịch, Dodge Counter còn gây thêm &lt;color=Highlight&gt;{0}&lt;/color&gt; lần sát thương, mỗi lần tương đương &lt;color=Highlight&gt;{1}&lt;/color&gt; ATK của Resonator. Hiệu ứng này có thể kích hoạt &lt;color=Highlight&gt;&lt;SapTag=2&gt;{3}&lt;/SapTag&gt;&lt;/color&gt; {Cus:Sap,S=lần P=lần SapTag=2} mỗi &lt;color=Highlight&gt;{2} giây&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -7171,7 +7171,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Tăng Tấn Công của Resonators trong Sự Kiện Lạ ở Honami lên 30%.</t>
+          <t>Tăng ATK của Resonator trong Sự Kiện Lạ ở Honami lên 30%.</t>
         </is>
       </c>
     </row>
@@ -7236,7 +7236,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Tăng HP của Resonators trong Sự Kiện Lạ ở Honami lên 10%.</t>
+          <t>Tăng HP của Resonator trong Sự Kiện Lạ ở Honami lên 10%.</t>
         </is>
       </c>
     </row>
@@ -7301,7 +7301,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Mỗi 60 giây khi khám phá Honami City, hồi phục 5 điểm Stability.</t>
+          <t>Mỗi 60 giây khi khám phá Thành phố Honami, hồi phục 5 điểm Ổn Định.</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Tăng Tấn Công của Resonators trong Sự Kiện Lạ ở Honami lên 30%.</t>
+          <t>Tăng ATK của Resonator trong Sự Kiện Lạ ở Honami lên 30%.</t>
         </is>
       </c>
     </row>
@@ -7431,7 +7431,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Tăng HP của Resonators trong Sự Kiện Lạ ở Honami lên 10%.</t>
+          <t>Tăng HP của Resonator trong Sự Kiện Lạ ở Honami lên 10%.</t>
         </is>
       </c>
     </row>
@@ -7496,7 +7496,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Mỗi 60 giây khi khám phá Honami City, hồi phục 5 điểm Stability.</t>
+          <t>Mỗi 60 giây khi khám phá Thành phố Honami, hồi phục 5 điểm Ổn Định.</t>
         </is>
       </c>
     </row>
@@ -7561,7 +7561,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Restore 10 điểm Stability mỗi 60 giây khi khám phá Honami City.</t>
+          <t>Hồi phục 10 điểm Ổn Định mỗi 60 giây khi khám phá Thành phố Honami.</t>
         </is>
       </c>
     </row>
@@ -7626,7 +7626,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Tăng Tấn Công của Resonators trong Sự Kiện Lạ ở Honami lên 45%.</t>
+          <t>Tăng ATK của Resonator trong Sự Kiện Lạ ở Honami lên 45%.</t>
         </is>
       </c>
     </row>
@@ -7691,7 +7691,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Giảm 20% Sát Thương nhận vào của Resonators trong Sự Vật Lạ tại Honami.</t>
+          <t>Giảm 20% Sát Thương nhận vào của Resonator trong Sự Vật Lạ tại Honami.</t>
         </is>
       </c>
     </row>
@@ -7756,7 +7756,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Tiêu hao &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=Điểm P=Điểm} Stability để khởi động Máy Capsule này?</t>
+          <t>Tiêu hao &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=Điểm P=Điểm} Ổn Định để khởi động Máy Capsule này?</t>
         </is>
       </c>
     </row>
@@ -7821,7 +7821,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Skill Nâng cấp Required Amount {0}/{1}</t>
+          <t>Số Lượng Cần Nâng Cấp {0}/{1}</t>
         </is>
       </c>
     </row>
@@ -8081,7 +8081,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>Fully activate Chisa's Resonance Chain ({0}/{1} đã kích hoạt)</t>
+          <t>Kích hoạt hoàn toàn Resonance Chain của Chisa ({0}/{1} đã kích hoạt)</t>
         </is>
       </c>
     </row>
@@ -8146,7 +8146,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Fully activate Buling's Resonance Chain ({0}/{1} đã kích hoạt)</t>
+          <t>Kích hoạt hoàn toàn Resonance Chain của Buling ({0}/{1} đã kích hoạt)</t>
         </is>
       </c>
     </row>
@@ -8276,7 +8276,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Fully activate Lynae's Resonance Chain ({0}/{1} đã kích hoạt)</t>
+          <t>Kích hoạt hoàn toàn Resonance Chain của Lynae ({0}/{1} đã kích hoạt)</t>
         </is>
       </c>
     </row>
@@ -8406,7 +8406,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Fully activate Mornye's Resonance Chain ({0}/{1} đã kích hoạt)</t>
+          <t>Kích hoạt hoàn toàn Resonance Chain của Mornye ({0}/{1} đã kích hoạt)</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Kích Hoạt Hoàn Toàn Chuỗi Resonance Aemeath</t>
+          <t>Kích Hoạt Hoàn Toàn Resonance Chain Aemeath</t>
         </is>
       </c>
     </row>
@@ -8536,7 +8536,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Kích Hoạt Hoàn Toàn Chuỗi Resonance Aemeath ({0}/{1} đã kích hoạt)</t>
+          <t>Kích Hoạt Hoàn Toàn Resonance Chain Aemeath ({0}/{1} đã kích hoạt)</t>
         </is>
       </c>
     </row>
@@ -8601,7 +8601,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Kích hoạt hoàn toàn Chuỗi Resonance của Luuk Herssen</t>
+          <t>Kích hoạt hoàn toàn Resonance Chain của Luuk Herssen</t>
         </is>
       </c>
     </row>
@@ -8666,7 +8666,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>Kích hoạt hoàn toàn Chuỗi Resonance của Luuk Herssen ({0}/{1} đã kích hoạt)</t>
+          <t>Kích hoạt hoàn toàn Resonance Chain của Luuk Herssen ({0}/{1} đã kích hoạt)</t>
         </is>
       </c>
     </row>
@@ -8731,7 +8731,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Kích hoạt toàn bộ Chuỗi Resonance của Sigrika</t>
+          <t>Kích hoạt toàn bộ Resonance Chain của Sigrika</t>
         </is>
       </c>
     </row>
@@ -8796,7 +8796,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Kích hoạt toàn bộ Chuỗi Resonance của Sigrika ({0}/{1} đã kích hoạt)</t>
+          <t>Kích hoạt toàn bộ Resonance Chain của Sigrika ({0}/{1} đã kích hoạt)</t>
         </is>
       </c>
     </row>
@@ -8861,7 +8861,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Trong Giai đoạn Triển khai và Giai đoạn Chiến đấu, mỗi lần mất HP, Resonator chỉ mất ít hơn 1 HP.</t>
+          <t>Trong Giai đoạn Triển khai và Giai đoạn Chiến đấu, mỗi lần mất HP, Cộng Hưởng Giả chỉ mất ít hơn 1 HP.</t>
         </is>
       </c>
     </row>
@@ -8926,7 +8926,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Mỗi lần Resonator chịu sát thương sẽ được giảm đi 5.</t>
+          <t>Mỗi lần Cộng Hưởng Giả chịu DMG sẽ được giảm đi 5.</t>
         </is>
       </c>
     </row>
@@ -9058,9 +9058,9 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Mỗi khi đấu thủ triển khai Echoes, Echoes đó sẽ nhận được Kháng Phá và Resilience.
-Đấu thủ sẽ mất ít hơn 1 HP mỗi khi bị trừ HP trong Giai Đoạn Triển Khai và Battle Stage.
-Cuối mỗi hiệp đấu, các Echoes của đấu thủ sẽ nhận được X điểm Sức Mạnh và Thể Chất, với X là số hiệp hiện tại.</t>
+          <t>Mỗi khi đấu thủ triển khai Echo, Echo đó sẽ nhận được Kháng Phá và Kiên Cường.
+Đấu thủ sẽ mất ít hơn 1 HP mỗi khi bị trừ HP trong Giai Đoạn Triển Khai và Giai Đoạn Chiến Đấu.
+Cuối mỗi hiệp đấu, các Echo của đấu thủ sẽ nhận được X điểm Sức Mạnh và Thể Chất, với X là số hiệp hiện tại.</t>
         </is>
       </c>
     </row>
@@ -9136,7 +9136,7 @@
 Báo Cáo Kiểm Tra Tần Số: NHA-Mắt Giải Cấu-017
 Đối tượng: Chisa Kuchiba
 Loại Resonator: Đột Biến
-Vị trí Echo: Cánh tay phải phía trên
+Vị trí Tổ Tacet: Cánh tay phải phía trên
 Cơ quan Kiểm tra: &lt;te href=851074&gt;Ashinohara&lt;/te&gt; - Neo Honami - Trung Tâm Giám Sát Resonator
 Kiểm tra cho thấy đối tượng sở hữu khả năng nhận thức đặc biệt, có thể trực giác phân biệt cấu trúc, hình dạng và chuyển động của vật thể quan sát. Khi sử dụng Tần số, cô ta có thể phân tích điểm yếu của vật thể qua thị giác và can thiệp chính xác để gây phá hủy cấu trúc.
 Ghi chú: Đối tượng mô tả cảm nhận về "sợi dây" khiến vật thể tan rã. Phân tích sơ bộ cho thấy những "sợi dây" này không phải thực thể mà chỉ là biểu hiện thị giác riêng của cô ta.</t>
@@ -9214,10 +9214,10 @@
           <t>&gt;&gt;&gt;Nâng Cấp Quyền Truy Cập: R-III&gt;&gt;&gt;
 Tần số của đối tượng thể hiện khả năng mở rộng và tiềm năng phát triển vượt ngưỡng an toàn. Trong điều kiện cực đoan, cô ta có thể phân tích cấu trúc không gian trừu tượng, xác định "sợi dây" dị thường trong các không gian bất thường, và kích hoạt các sự kiện bóp méo thực tại, bao gồm cả không gian ██.
 Các Chỉ Số Dị Thường Hiện Tại:
-- Nhiều biến động đột ngột được phát hiện trên &lt;te href=850067&gt;Rabelle's Curve&lt;/te&gt;, với giá trị đỉnh gần chạm ngưỡng giới hạn.
-- Độ ổn định Tần số vẫn yếu, tiềm ẩn rủi ro đáng kể về &lt;te href=850073&gt;Overclocking&lt;/te&gt;.
+- Nhiều biến động đột ngột được phát hiện trên &lt;te href=850067&gt;Đường Cong Rabelle&lt;/te&gt;, với giá trị đỉnh gần chạm ngưỡng giới hạn.
+- Độ ổn định Tần số vẫn yếu, tiềm ẩn rủi ro đáng kể về &lt;te href=850073&gt;Quá Tải&lt;/te&gt;.
 Biện Pháp Giám Sát Sơ Bộ:
-Đối tượng buộc phải đeo vòng cổ kiềm chế Resonators để điều chỉnh Tần số và được đưa vào danh sách theo dõi Resonators nguy cơ cao.
+Đối tượng buộc phải đeo vòng cổ kiềm chế Resonator để điều chỉnh Tần số và được đưa vào danh sách theo dõi các Resonator nguy cơ cao.
 Các cơ quan giám sát liên quan được chỉ thị cập nhật hồ sơ với cơ quan trung ương về những thay đổi Tần số và vị trí thời gian thực của đối tượng. Nếu cần thiết, các biện pháp cưỡng chế sẽ được áp dụng theo quy định pháp luật.</t>
         </is>
       </c>
@@ -9288,12 +9288,12 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Cơ sở đánh giá: [Report Khảo sát Phổ RA1556-G]
-Thời gian Resonance không xác định. Tacet Mark nằm ở bên phải cổ. &lt;te href=850067&gt;Rabelle's Curve&lt;/te&gt; cho thấy sự hội tụ ổn định: được phân loại là &lt;te href=850070&gt;Natural Resonator&lt;/te&gt;.
+          <t>Cơ sở đánh giá: [Báo cáo Khảo sát Phổ RA1556-G]
+Thời gian Cộng Hưởng không xác định. Dấu Tacet nằm ở bên phải cổ. &lt;te href=850067&gt;Đường Cong Rabelle&lt;/te&gt; cho thấy sự hội tụ ổn định: được phân loại là &lt;te href=850070&gt;Resonator Tự Nhiên&lt;/te&gt;.
 Đối tượng thể hiện độ nhạy cảm đặc biệt với tần số Vang Động và thường bị quấy rối bởi những âm thanh mà người khác không thể cảm nhận. Kiểm tra xác nhận rằng những "ảo giác" mà cô cảm nhận thực chất là kết quả của khả năng cảm nhận Vang Động vượt trội.
 Đối tượng cho biết đã được đào tạo kỹ thuật tu luyện Khí Lôi của môn phái từ nhỏ. Hiện tại, cô có thể dẫn truyền tần số môi trường thông qua các phương tiện và phép thuật để triệu hồi sét.
-So sánh các mô hình Resonance không cho thấy sự trùng khớp đáng kể. Nguồn gốc Resonance vẫn chưa được xác định.
-Ghi chú: Điều khiến tôi bối rối nhất với tư cách một nhà nghiên cứu là những lời tiên đoán của cô luôn chính xác. Mỗi khi cô trở về &lt;te href=850109&gt;the Black Shores&lt;/te&gt; để kiểm tra sức khỏe định kỳ, chúng tôi đều nhân cơ hội nhờ cô bói một quẻ. Đến giờ, một nửa phòng ban đã kính cẩn gọi cô là Đạo Sư.</t>
+So sánh các mô hình Cộng Hưởng không cho thấy sự trùng khớp đáng kể. Nguồn gốc Cộng Hưởng vẫn chưa được xác định.
+Ghi chú: Điều khiến tôi bối rối nhất với tư cách một nhà nghiên cứu là những lời tiên đoán của cô luôn chính xác. Mỗi khi cô trở về &lt;te href=850109&gt;Bờ Biển Đen&lt;/te&gt; để kiểm tra sức khỏe định kỳ, chúng tôi đều nhân cơ hội nhờ cô bói một quẻ. Đến giờ, một nửa phòng ban đã kính cẩn gọi cô là Đạo Sư.</t>
         </is>
       </c>
     </row>
@@ -9496,7 +9496,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Khi Buling lớn lên và Tần số của cô trưởng thành, những âm thanh trong tai ngày càng sắc bén, không thể phớt lờ. Ngoài bức tường tu viện, cô không thể tiếp tục tụng kinh để át đi chúng như trong những buổi luyện tập yên tĩnh. Tiếng ồn ào dai dẳng gặm nhấm tâm trí cô. Rồi một ngày, sau khi mệt lả kéo ai đó ra khỏi bầy Tacet Discord, người đó nhẹ nhàng đặt lên đầu cô một phát minh của Huaxu Academy. Trong khoảnh khắc ấy, thế giới của cô hoàn toàn chìm vào im lặng.</t>
+          <t>Khi Buling lớn lên và Tần số của cô trưởng thành, những âm thanh trong tai ngày càng sắc bén, không thể phớt lờ. Ngoài bức tường tu viện, cô không thể tiếp tục tụng kinh để át đi chúng như trong những buổi luyện tập yên tĩnh. Tiếng ồn ào dai dẳng gặm nhấm tâm trí cô. Rồi một ngày, sau khi mệt lả kéo ai đó ra khỏi bầy Tacet Discord, người đó nhẹ nhàng đặt lên đầu cô một phát minh của Học viện Huaxu. Trong khoảnh khắc ấy, thế giới của cô hoàn toàn chìm vào im lặng.</t>
         </is>
       </c>
     </row>
@@ -9657,12 +9657,12 @@
       <c r="M137" t="inlineStr">
         <is>
           <t>Mùa hè năm mười sáu tuổi của cô, mây đen kéo dài bất tận, mưa như trút nước. Sấm sét đè nặng lên màng nhĩ khi cô đứng trước cửa sổ trần của Trung tâm Giám sát Resonator.
-"Nghe ta nói không?" Giọng nói sắc lạnh, đầy bất mãn. Chisa ngước mắt lên, chỉ thấy khuôn mặt người nói tan biến vào hư không.
+"Nghe tao nói không?" Giọng nói sắc lạnh, đầy bất mãn. Chisa ngước mắt lên, chỉ thấy khuôn mặt người nói tan biến vào hư không.
 "Nghe rõ lắm," cô đáp lại khoảng không.
 Cái vòng cổ kêu lách cách quanh cổ cô, mang theo cái lạnh của thiết bị giám sát.
-Khi cơn bão cuối cùng cũng dịu đi, cô lên đường về nhà. Đi ngang qua công viên, cô bắt gặp một cậu bé đang khóc bên cầu trượt, tay nắm chặt sợi dây diều đứt. Trong tầm mắt cô, con diều mắc trên ngọn cây hiện ra với độ sắc Dodget kỳ lạ: ba cành cây tạo thành một cái khóa tự nhiên, và nếu cành ngoài cùng bên phải bị cắt đứt—
+Khi cơn bão cuối cùng cũng dịu đi, cô lên đường về nhà. Đi ngang qua công viên, cô bắt gặp một cậu bé đang khóc bên cầu trượt, tay nắm chặt sợi dây diều đứt. Trong tầm mắt cô, con diều mắc trên ngọn cây hiện ra với độ sắc nét kỳ lạ: ba cành cây tạo thành một cái khóa tự nhiên, và nếu cành ngoài cùng bên phải bị cắt đứt—
 "Đứng yên nào," cô ngăn cậu bé kéo dây. Đôi mắt cậu mở to. Với một tiếng rắc nhẹ, cành cây gãy rời, con diều từ từ rơi xuống, đáp nhẹ vào vòng tay cậu.
-"Cảm ơn c—" Niềm vui của cậu vụt tắt khi một tiếng thét chói tai vang lên. "Q-quái vật! Tránh xa con ta ra!"
+"Cảm ơn c—" Niềm vui của cậu vụt tắt khi một tiếng thét chói tai vang lên. "Q-quái vật! Tránh xa con tao ra!"
 Theo ánh mắt kinh hãi của người phụ nữ, Chisa mới nhận ra chiếc vòng cổ đang cắn lạnh vào cổ mình.
 Chẳng có gì to tát. Cô tự nhủ mình nên quen với điều này rồi.
 Cô có thể nhìn thấy khung diều, quỹ đạo của những giọt mưa, thậm chí cả dòng electron cuồn cuộn trong đám mây bão với độ rõ ràng đến lạ kỳ, nhưng cô không bao giờ nhìn thấu được khuôn mặt hay trái tim của người khác.
@@ -9670,7 +9670,7 @@
 Giấy gói kẹo sột soạt trong tay cô. Chisa nhìn chằm chằm vào cậu bé. Khuôn mặt cậu vẫn mờ ảo, nhưng lại sáng rực, như đom đóm bay quanh chiếc đèn lồng trong lễ hội xa xưa.
 "Mẹ cháu bảo người đeo vòng cổ này là người xấu," cậu bé nghiêng người, thì thầm. "Nhưng cháu không tin đâu. Cách chị cắt cái cành kia? Ngầu thật đấy."
 Chisa dừng lại, rồi cúi xuống vỗ đầu cậu.
-Thiết bị trên cổ cô vẫn im lặng. Phổ Resonance của cô đang hiển thị một đường cong hiếm hoi, ổn định. Như bầu trời mùa hè sau cơn bão, một tia sáng cuối cùng cũng lóe lên.</t>
+Thiết bị trên cổ cô vẫn im lặng. Phổ Cộng Hưởng của cô đang hiển thị một đường cong hiếm hoi, ổn định. Như bầu trời mùa hè sau cơn bão, một tia sáng cuối cùng cũng lóe lên.</t>
         </is>
       </c>
     </row>
@@ -9759,11 +9759,11 @@
 Bên ngoài, mưa rơi không ngừng.
 Khi Sumika thức dậy, màn đêm đã buông xuống. Cơn bão đã yếu đi. Những vì sao mờ nhạt lốm đốm trên bầu trời xanh thẫm, như những chiếc đinh bạc vương vãi trên đêm lạnh.
 Vẫn còn ngái ngủ, cô theo Chisa vào một cửa hàng tiện lợi. Trong khi Chisa cẩn thận lấy đồ ăn và nhu yếu phẩm từ kệ, cô quay lại thấy Sumika đang chăm chú nhìn biển hiệu nhấp nháy phía trên, tay đã cầm sẵn sổ và bút.
-"Chisa, nhìn này—" cô thì thầm, giọng tràn ngập hứng khởi kìm Dodgen. "Giống hệt lần trước! Thời gian, tần số nhấp nháy... Tất cả đều khớp! Nếu thu thập thêm vài mẫu nữa... dữ liệu này sẽ giúp ta tìm ra quy luật đằng sau vòng lặp!"
+"Chisa, nhìn này—" cô thì thầm, giọng tràn ngập hứng khởi kìm nén. "Giống hệt lần trước! Thời gian, tần số nhấp nháy... Tất cả đều khớp! Nếu thu thập thêm vài mẫu nữa... dữ liệu này sẽ giúp ta tìm ra quy luật đằng sau vòng lặp!"
 Nhìn thấy ánh mắt rực sáng của cô, Chisa vô thức siết chặt tay. Trong lòng bàn tay vẫn còn cảm giác đau rát từ vết cắt hôm qua, khi cô cắt đứt những sợi dây Tacet Discord, một cơn ớn lạnh như tơ bị đứt lìa.
 Mỗi khi rút kéo và sử dụng Forte, những đường đỏ thẫm lại hiện ra trong tầm mắt—những sợi dây sinh mệnh, chỉ có cô nhìn thấy. Không giống như mạch máu ấm áp của con người, những sợi dây này mang mùi thối rữa. Chúng săn đuổi những kẻ Bị Bỏ Lại, xé nát họ và kéo những sinh mệnh mỏng manh ấy vào vòng lặp mới cùng với Lament.
 Chisa nhìn bóng mình trên cửa kính: một gương mặt bình thản, gần như nhợt nhạt, nhưng trong đôi mắt vẫn còn một tia lửa âm ỉ.
-Yesterday, ngay tại cửa hàng này, cô lại gặp cô gái ấy một lần nữa. Người cô gặp mỗi vòng lặp, luôn chia sẻ đồ ăn một cách chân thành, không hề biết mình mang ánh sáng lấp lánh của kẻ Bị Bỏ Lại. Có lẽ chính sự tử tế mỏng manh nhưng không chịu khuất phục ấy đã khiến Chisa không thể chấp nhận rằng thành phố này đã bị giam cầm trong quá khứ mãi mãi.
+Hôm qua, ngay tại cửa hàng này, cô lại gặp cô gái ấy một lần nữa. Người cô gặp mỗi vòng lặp, luôn chia sẻ đồ ăn một cách chân thành, không hề biết mình mang ánh sáng lấp lánh của kẻ Bị Bỏ Lại. Có lẽ chính sự tử tế mỏng manh nhưng không chịu khuất phục ấy đã khiến Chisa không thể chấp nhận rằng thành phố này đã bị giam cầm trong quá khứ mãi mãi.
 Đêm dài đằng đẵng, nhưng bình minh rồi sẽ đến.
 Khi ánh sáng đầu tiên xuyên qua những đám mây chì, cô tưởng như nghe thấy tiếng rung động run rẩy của những sợi dây. Áp tay lên ngực, Chisa biết rằng khi vòng lặp tiếp theo bắt đầu, mọi thứ sẽ lại trở về con số không.
 Nhưng không sao cả.
@@ -10028,7 +10028,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>Trong 30 giây sau khi kích hoạt Phá Vỡ Giai Tune, Resonators trong đội nhận thêm 50% DMG Amplification.</t>
+          <t>Trong 30 giây sau khi kích hoạt Phá Vỡ Giai Điệu, Resonator trong đội nhận thêm 50% Khuếch Đại Sát Thương.</t>
         </is>
       </c>
     </row>
@@ -10093,7 +10093,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>Trong vòng 30 giây sau khi kích hoạt Tune Break, Resonators trong đội nhận tăng 80% Crit. DMG.</t>
+          <t>Trong vòng 30 giây sau khi kích hoạt Tune Break, Resonator trong đội nhận tăng 80% Crit. DMG.</t>
         </is>
       </c>
     </row>
@@ -10158,7 +10158,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>Trong 30 giây sau khi kích hoạt Phá Vỡ Giai Tune, Resonators trong đội được tăng 80% Tấn Công.</t>
+          <t>Trong 30 giây sau khi kích hoạt Phá Vỡ Giai Điệu, Resonator trong đội được tăng 80% ATK.</t>
         </is>
       </c>
     </row>
@@ -10223,7 +10223,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Resonators trong đội tăng 50% Efficiency Cấp Độ Lệch Nhịp.</t>
+          <t>Resonator trong đội tăng 50% Hiệu Suất Cấp Độ Lệch Nhịp.</t>
         </is>
       </c>
     </row>
@@ -10288,7 +10288,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>Kích hoạt Tune Break tạo ra bão sấm sét gây 6000% Electro DMG lên kẻ địch.</t>
+          <t>Kích hoạt Tune Break tạo ra bão sấm sét gây 6000% Sát Thương Electro lên kẻ địch.</t>
         </is>
       </c>
     </row>
@@ -10353,7 +10353,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>Trong vòng 30 giây sau khi kích hoạt Tune Break, mỗi khi Resonators trong đội gây sát thương, tạo ra một tia sét gây 100% Electro DMG lên mục tiêu. Hiệu ứng này có thể kích hoạt mỗi 0.5 giây một lần.</t>
+          <t>Trong vòng 30 giây sau khi kích hoạt Tune Break, mỗi khi Resonator trong đội gây DMG, tạo ra một tia sét gây 100% Sát Thương Electro lên mục tiêu. Hiệu ứng này có thể kích hoạt mỗi 0.5 giây một lần.</t>
         </is>
       </c>
     </row>
@@ -10418,7 +10418,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>Trong vòng 30 giây sau khi kích hoạt Tune Break, Spectro Frazzle gây ra bởi Resonators trong đội sẽ bỏ qua 60% Phòng Ngự của mục tiêu.</t>
+          <t>Trong vòng 30 giây sau khi kích hoạt Tune Break, Spectro Frazzle gây ra bởi Resonator trong đội sẽ bỏ qua 60% Phòng Ngự của mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -10483,7 +10483,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>Trong vòng 30 giây sau khi kích hoạt Tune Break, Spectro DMG Frazzle gây ra bởi Resonators trong đội được Khuếch Đại thêm 150%.</t>
+          <t>Trong vòng 30 giây sau khi kích hoạt Tune Break, Sát Thương Spectro Frazzle gây ra bởi Resonator trong đội được Khuếch Đại thêm 150%.</t>
         </is>
       </c>
     </row>
@@ -10548,7 +10548,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>Trong vòng 30 giây sau khi kích hoạt Tune Break, mỗi khi Resonators trong đội gây hiệu ứng Havoc Bane, tạo ra một hố đen gây tổng cộng 400% Havoc DMG lên mục tiêu.</t>
+          <t>Trong vòng 30 giây sau khi kích hoạt Tune Break, mỗi khi Resonator trong đội gây hiệu ứng Havoc Bane, tạo ra một hố đen gây tổng cộng 400% Sát Thương Havoc lên mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -10613,7 +10613,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>Trong vòng 30 giây sau khi kích hoạt Tune Break, mỗi 3 tầng Aero Erosion gây ra bởi Resonators trong đội sẽ tạo ra một cơn lốc gây tổng cộng 750% Aero DMG lên mục tiêu.</t>
+          <t>Trong vòng 30 giây sau khi kích hoạt Tune Break, mỗi 3 tầng Aero Erosion gây ra bởi Resonator trong đội sẽ tạo ra một cơn lốc gây tổng cộng 750% Sát Thương Aero lên mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -10678,7 +10678,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Trong 30 giây sau khi kích hoạt Phá Vỡ Giai Tune, mỗi lần Resonators trong đội nhận Shield sẽ nhận 1 tầng Flash. Khi đạt 10 tầng Flash, sẽ phóng một chùm tia gây 1500% Spectro DMG lên mục tiêu và xóa toàn bộ tầng Flash.</t>
+          <t>Trong 30 giây sau khi kích hoạt Phá Vỡ Giai Điệu, mỗi lần Resonator trong đội nhận Khiên sẽ nhận 1 tầng Tia Chớp. Khi đạt 10 tầng Tia Chớp, sẽ phóng một chùm tia gây 1500% Sát Thương Spectro lên mục tiêu và xóa toàn bộ tầng Tia Chớp.</t>
         </is>
       </c>
     </row>
@@ -10743,7 +10743,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>Trong vòng 30 giây sau khi kích hoạt Tune Break, mỗi khi Resonators trong đội nhận được Shield, tạo ra một quả cầu lửa gây 120% Fusion DMG lên mục tiêu.</t>
+          <t>Trong vòng 30 giây sau khi kích hoạt Tune Break, mỗi khi Resonator trong đội nhận được Khiên, tạo ra một quả cầu lửa gây 120% Sát Thương Fusion lên mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -10808,7 +10808,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>Trong 30 giây sau khi kích hoạt Phá Vỡ Giai Tune, Resonators trong đội nhận thêm 200% Sát Thương Kỹ Năng Echo.</t>
+          <t>Trong 30 giây sau khi kích hoạt Phá Vỡ Giai Điệu, Resonator trong đội nhận thêm 200% Sát Thương Kỹ Năng Echo.</t>
         </is>
       </c>
     </row>
@@ -10873,7 +10873,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>Trong vòng 30 giây sau khi kích hoạt Tune Break, mỗi khi Resonators trong đội sử dụng Kỹ Năng Echoes, Tấn Công của họ tăng thêm 20%, tối đa 5 tầng. Các Echoes cùng tên chỉ kích hoạt hiệu ứng này một lần. Khi đạt 5 tầng, đòn tấn công của Resonators sẽ bỏ qua 50% Phòng Ngự của mục tiêu. Trigger lại Tune Break sẽ đặt lại hiệu ứng này.</t>
+          <t>Trong vòng 30 giây sau khi kích hoạt Tune Break, mỗi khi Resonator trong đội sử dụng Kỹ Năng Echo, ATK của họ tăng thêm 20%, tối đa 5 tầng. Các Echo cùng tên chỉ kích hoạt hiệu ứng này một lần. Khi đạt 5 tầng, đòn tấn công của Resonator sẽ bỏ qua 50% Phòng Ngự của mục tiêu. Kích hoạt lại Tune Break sẽ đặt lại hiệu ứng này.</t>
         </is>
       </c>
     </row>
@@ -11003,7 +11003,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>Gây Sát Thương Basic Attack sẽ triệu hồi thêm 6 &lt;color=Highlight&gt;&lt;te href=851100&gt;Combo - Rice Dango Missiles&lt;/te&gt;&lt;/color&gt;.</t>
+          <t>Gây Sát Thương Basic Attack sẽ triệu hồi thêm 6 &lt;color=Highlight&gt;&lt;te href=851100&gt;Combo - Tên Lửa Bánh Dango&lt;/te&gt;&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -11068,7 +11068,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>Khi &lt;color=Highlight&gt;&lt;te href=851100&gt;Combo - Rice Dango Missile&lt;/te&gt;&lt;/color&gt; hoặc &lt;color=Highlight&gt;&lt;te href=851101&gt;Combo - Rice Dango Missile: Enhanced&lt;/te&gt;&lt;/color&gt; trúng mục tiêu, các tên lửa tiếp theo sẽ nhận thêm Tấn Công.</t>
+          <t>Khi &lt;color=Highlight&gt;&lt;te href=851100&gt;Hợp Kỹ - Tên Lửa Bánh Dango&lt;/te&gt;&lt;/color&gt; hoặc &lt;color=Highlight&gt;&lt;te href=851101&gt;Hợp Kỹ - Tên Lửa Bánh Dango: Cường Hóa&lt;/te&gt;&lt;/color&gt; trúng mục tiêu, các tên lửa tiếp theo sẽ nhận thêm Tấn Công.</t>
         </is>
       </c>
     </row>
@@ -11133,7 +11133,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>Crit. DMG của &lt;color=Highlight&gt;&lt;te href=851100&gt;Combo - Rice Dango Missile&lt;/te&gt;&lt;/color&gt; và &lt;color=Highlight&gt;&lt;te href=851101&gt;Combo - Rice Dango Missile: Enhanced&lt;/te&gt;&lt;/color&gt; được tăng lên.</t>
+          <t>Crit. DMG của &lt;color=Highlight&gt;&lt;te href=851100&gt;Combo - Tên Lửa Bánh Dango&lt;/te&gt;&lt;/color&gt; và &lt;color=Highlight&gt;&lt;te href=851101&gt;Combo - Tên Lửa Bánh Dango: Cường Hóa&lt;/te&gt;&lt;/color&gt; được tăng lên.</t>
         </is>
       </c>
     </row>
@@ -11198,7 +11198,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>Kích hoạt Skill Kết thúc triệu hồi &lt;color=Highlight&gt;&lt;te href=851102&gt;Burst - Blazing Pillar&lt;/te&gt;&lt;/color&gt;.</t>
+          <t>Kích hoạt Kỹ năng Kết thúc triệu hồi &lt;color=Highlight&gt;&lt;te href=851102&gt;Đòn Phát Lửa - Trụ Lửa Bùng Cháy&lt;/te&gt;&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -11328,7 +11328,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>Khi &lt;color=Highlight&gt;&lt;te href=851103&gt;Burst - Scorching Impact&lt;/te&gt;&lt;/color&gt; hoặc &lt;color=Highlight&gt;&lt;te href=851102&gt;Burst - Blazing Pillar&lt;/te&gt;&lt;/color&gt; trúng kẻ địch, tất cả Resonators trong đội sẽ hồi HP.</t>
+          <t>Khi &lt;color=Highlight&gt;&lt;te href=851103&gt;Kỹ Năng Q - Va Chạm Nảy Lửa&lt;/te&gt;&lt;/color&gt; hoặc &lt;color=Highlight&gt;&lt;te href=851102&gt;Kỹ Năng Q - Trụ Lửa Bừng Cháy&lt;/te&gt;&lt;/color&gt; trúng kẻ địch, tất cả Resonator trong đội sẽ hồi HP.</t>
         </is>
       </c>
     </row>
@@ -11393,7 +11393,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>Trong &lt;color=Highlight&gt;&lt;te href=851104&gt;Boost - Namipon Aid&lt;/te&gt;&lt;/color&gt;, nhận sát thương sẽ phục hồi Độ Stability.</t>
+          <t>Trong &lt;color=Highlight&gt;&lt;te href=851104&gt;Tăng Cường - Hỗ Trợ Namipon&lt;/te&gt;&lt;/color&gt;, nhận sát thương sẽ phục hồi Độ Ổn Định.</t>
         </is>
       </c>
     </row>
@@ -11458,7 +11458,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>Khi kích hoạt &lt;color=Highlight&gt;&lt;te href=851104&gt;Boost - Namipon Aid&lt;/te&gt;&lt;/color&gt;, toàn bộ Resonators trong đội tăng Tấn Công.</t>
+          <t>Khi kích hoạt &lt;color=Highlight&gt;&lt;te href=851104&gt;Boost - Namipon Aid&lt;/te&gt;&lt;/color&gt;, toàn bộ Resonator trong đội tăng ATK.</t>
         </is>
       </c>
     </row>
@@ -11523,7 +11523,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>Khi kích hoạt &lt;color=Highlight&gt;&lt;te href=851105&gt;Boost - Sprint&lt;/te&gt;&lt;/color&gt;, sẽ triệu hồi thêm &lt;color=Highlight&gt;&lt;te href=851116&gt;Burst - Shock Impact&lt;/te&gt;&lt;/color&gt; gây Sát Thương.</t>
+          <t>Khi kích hoạt &lt;color=Highlight&gt;&lt;te href=851105&gt;Tăng Cường - Bứt Tốc&lt;/te&gt;&lt;/color&gt;, sẽ triệu hồi thêm &lt;color=Highlight&gt;&lt;te href=851116&gt;Kích Nổ - Xung Kích Sét&lt;/te&gt;&lt;/color&gt; gây Sát Thương.</t>
         </is>
       </c>
     </row>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;&lt;te href=851116&gt;Burst - Shock Impact&lt;/te&gt;&lt;/color&gt; gây thêm sát thương khi trúng mục tiêu.</t>
+          <t>&lt;color=Highlight&gt;&lt;te href=851116&gt;Kỹ Năng Bùng Nổ - Sốc Tác Động&lt;/te&gt;&lt;/color&gt; gây thêm DMG khi trúng mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -11653,7 +11653,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>Trong &lt;color=Highlight&gt;&lt;te href=851105&gt;Boost - Sprint&lt;/te&gt;&lt;/color&gt;, Resonator nhận được Giảm Sát Thương.</t>
+          <t>Trong &lt;color=Highlight&gt;&lt;te href=851105&gt;Tăng Cường - Tăng Tốc&lt;/te&gt;&lt;/color&gt;, Resonator nhận được Giảm Sát Thương.</t>
         </is>
       </c>
     </row>
@@ -11718,7 +11718,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;&lt;te href=851107&gt;Combo - Hỗ Trợ Missile&lt;/te&gt;&lt;/color&gt; gây thêm sát thương và áp &lt;color=Highlight&gt;&lt;te href=851108&gt;Status - Waveworn Bane&lt;/te&gt;&lt;/color&gt; khi trúng mục tiêu.</t>
+          <t>&lt;color=Highlight&gt;&lt;te href=851107&gt;Combo - Hỏa Tiễn Hỗ Trợ&lt;/te&gt;&lt;/color&gt; gây thêm DMG và áp &lt;color=Highlight&gt;&lt;te href=851108&gt;Trạng Thái - Ác Nghiệt Sóng Dữ&lt;/te&gt;&lt;/color&gt; khi trúng mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -11783,7 +11783,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>Giới hạn lớp chồng của &lt;color=Highlight&gt;&lt;te href=851108&gt;Status - Waveworn Bane&lt;/te&gt;&lt;/color&gt; đã tăng.</t>
+          <t>Giới hạn lớp chồng của &lt;color=Highlight&gt;&lt;te href=851108&gt;Trạng Thái - Lời Nguyền Sóng Dữ&lt;/te&gt;&lt;/color&gt; đã tăng.</t>
         </is>
       </c>
     </row>
@@ -11848,7 +11848,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>Namipon rung chuyển mặt đất và để lại các Vùng Thanh Tẩy, gây sát thương và áp dụng &lt;color=Highlight&gt;&lt;te href=851108&gt;Status - Waveworn Bane&lt;/te&gt;&lt;/color&gt;.</t>
+          <t>Namipon rung chuyển mặt đất và để lại các Vùng Thanh Tẩy, gây DMG và áp dụng &lt;color=Highlight&gt;&lt;te href=851108&gt;Trạng Thái - Tai Họa Sóng Dữ&lt;/te&gt;&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -11913,7 +11913,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>Khi sóng xung kích trúng mục tiêu, nó sẽ kích hoạt thêm sát thương dựa trên số lượt &lt;color=Highlight&gt;&lt;te href=851108&gt;Status - Waveworn Bane&lt;/te&gt;&lt;/color&gt; hiện tại.</t>
+          <t>Khi sóng xung kích trúng mục tiêu, nó sẽ kích hoạt thêm DMG dựa trên số lượt &lt;color=Highlight&gt;&lt;te href=851108&gt;Trạng Thái - Tai Họa Sóng Dữ&lt;/te&gt;&lt;/color&gt; hiện tại.</t>
         </is>
       </c>
     </row>
@@ -11978,7 +11978,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>Khi &lt;color=Highlight&gt;&lt;te href=851110&gt;Combo - Dessert Strike&lt;/te&gt;&lt;/color&gt; hoặc &lt;color=Highlight&gt;&lt;te href=851111&gt;Combo - Dessert Strike: Enhanced&lt;/te&gt;&lt;/color&gt; trúng mục tiêu, có thể gây hiệu ứng Havoc Bane, Spectro Frazzle, Aero Erosion hoặc &lt;color=Highlight&gt;&lt;te href=851108&gt;Status - Waveworn Bane&lt;/te&gt;&lt;/color&gt;.</t>
+          <t>Khi &lt;color=Highlight&gt;&lt;te href=851110&gt;Combo - Đòn Đánh Bánh Ngọt&lt;/te&gt;&lt;/color&gt; hoặc &lt;color=Highlight&gt;&lt;te href=851111&gt;Combo - Đòn Đánh Bánh Ngọt: Cường Hóa&lt;/te&gt;&lt;/color&gt; trúng mục tiêu, có thể gây hiệu ứng Havoc Bane, Spectro Frazzle, Aero Erosion hoặc &lt;color=Highlight&gt;&lt;te href=851108&gt;Trạng Thái - Waveworn Bane&lt;/te&gt;&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -12043,7 +12043,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;&lt;te href=851110&gt;Combo - Dessert Strike&lt;/te&gt;&lt;/color&gt; và &lt;color=Highlight&gt;&lt;te href=851111&gt;Combo - Dessert Strike: Enhanced&lt;/te&gt;&lt;/color&gt; nhận Tăng Sát Thương.</t>
+          <t>&lt;color=Highlight&gt;&lt;te href=851110&gt;Combo - Đòn Đánh Sa Mạc&lt;/te&gt;&lt;/color&gt; và &lt;color=Highlight&gt;&lt;te href=851111&gt;Combo - Đòn Đánh Sa Mạc: Cường Hóa&lt;/te&gt;&lt;/color&gt; nhận Tăng Sát Thương.</t>
         </is>
       </c>
     </row>
@@ -12108,7 +12108,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;&lt;te href=851112&gt;Boost - Satisfaction&lt;/te&gt;&lt;/color&gt; cấp Tăng Sát Thương Toàn Bộ.</t>
+          <t>&lt;color=Highlight&gt;&lt;te href=851112&gt;Tăng Cường - Thỏa Mãn&lt;/te&gt;&lt;/color&gt; cấp Tăng Sát Thương Toàn Bộ.</t>
         </is>
       </c>
     </row>
@@ -12173,7 +12173,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>Khi Độ Stability ở mức 30% hoặc thấp hơn, Resonator nhận tăng Tấn Công.</t>
+          <t>Khi Độ Ổn Định ở mức 30% hoặc thấp hơn, Resonator nhận tăng ATK.</t>
         </is>
       </c>
     </row>
@@ -12238,7 +12238,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>Khi HP ở mức 100%, bị tấn công sẽ không làm giảm Độ Stability.</t>
+          <t>Khi HP ở mức 100%, bị tấn công sẽ không làm giảm Độ Ổn Định.</t>
         </is>
       </c>
     </row>
@@ -12303,7 +12303,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>Trong Trạng Thái Nguy Kịch, Dodge Counter gây thêm sát thương.</t>
+          <t>Trong Trạng Thái Nguy Kịch, Dodge Counter Tránh gây thêm DMG.</t>
         </is>
       </c>
     </row>
@@ -12371,10 +12371,10 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;[Heavy Attack]&lt;/color&gt;
-- Khi Prowess đạt &lt;color=Highlight&gt;{0}&lt;/color&gt; điểm, giữ Basic Attack hoặc {Cus:Ipt,Touch=tap PC=click Gamepad=press} Basic Attack khi đang ở trên không để tiêu hao &lt;color=Highlight&gt;{0}&lt;/color&gt; điểm Prowess và thi triển Heavy Attack - Thét Sấm: Thượng Đoạn.
-- Thi triển Heavy Attack - Thét Sấm: Thượng Đoạn sẽ hồi phục thêm &lt;color=Highlight&gt;{1}&lt;/color&gt; điểm Thăng Hoa và tăng &lt;color=Highlight&gt;{2}&lt;/color&gt; Sát Thương trong &lt;color=Highlight&gt;{4}s&lt;/color&gt;, có thể chồng chất lên đến &lt;color=Highlight&gt;{3}&lt;/color&gt; lần.
-- Khi Prowess đạt &lt;color=Highlight&gt;{0}&lt;/color&gt; điểm, giữ Basic Attack sau khi thi triển Stage 2 của Basic Attack để tiêu hao &lt;color=Highlight&gt;{0}&lt;/color&gt; điểm Prowess và thi triển Heavy Attack - Thét Sấm: Lùi Bước.</t>
+          <t>&lt;color=Highlight&gt;[Đòn Heavy Attack]&lt;/color&gt;
+- Khi Prowess đạt &lt;color=Highlight&gt;{0}&lt;/color&gt; điểm, giữ Basic Attack hoặc {Cus: Ipt,Touch=tap PC=click Gamepad=press} Basic Attack while in mid-air to consume &lt;color=Highlight&gt;{0}&lt;/color&gt; points of Prowess and cast Heavy Attack - Thunderoar: Uppercut.
+- Casting Heavy Attack - Thunderoar: Uppercut additionally restores &lt;color=Highlight&gt;{1}&lt;/color&gt; Ascendancy and grants &lt;color=Highlight&gt;{2}&lt;/color&gt; DMG Bonus for &lt;color=Highlight&gt;{4}s&lt;/color&gt;, stacking up to &lt;color=Highlight&gt;{3}&lt;/color&gt; times.
+- When Prowess reaches &lt;color=Highlight&gt;{0}&lt;/color&gt; points, hold Basic Attack after casting Basic Attack Stage 2 to consume &lt;color=Highlight&gt;{0}&lt;/color&gt; points of Prowess and cast Heavy Attack - Thunderoar: Backstep.</t>
         </is>
       </c>
     </row>
@@ -12445,11 +12445,11 @@
       <c r="M179" t="inlineStr">
         <is>
           <t>&lt;color=Highlight&gt;[Resonance Liberation]&lt;/color&gt;
-- Thi triển Heavy Attack - Thét Sấm: Thượng Đoạn hoặc Heavy Attack - Thét Sấm: Lùi Bước sẽ tạo ra &lt;color=Highlight&gt;&lt;SapTag=0&gt;{0}&lt;/SapTag&gt;&lt;/color&gt; {Cus:Sap,S=điểm P=điểm} Daystar, có thể chồng chất lên đến &lt;color=Highlight&gt;{1}&lt;/color&gt; lần.
+- Thi triển Đòn Heavy Attack - Thét Sấm: Thượng Đoạn hoặc Đòn Heavy Attack - Thét Sấm: Lùi Bước sẽ tạo ra &lt;color=Highlight&gt;&lt;SapTag=0&gt;{0}&lt;/SapTag&gt;&lt;/color&gt; {Cus:Sap,S=điểm P=điểm} Daystar, có thể chồng chất lên đến &lt;color=Highlight&gt;{1}&lt;/color&gt; lần.
 - Khi có ít nhất &lt;color=Highlight&gt;{2}&lt;/color&gt; điểm Daystar, sử dụng Resonance Liberation để tiêu hao &lt;color=Highlight&gt;{2}&lt;/color&gt; điểm Daystar và thi triển Kiếm Bùng Nổ.
-- Sau khi hoàn thành &lt;color=Highlight&gt;{3}&lt;/color&gt; giai đoạn của Kiếm Bùng Nổ với ít nhất &lt;color=Highlight&gt;{4}&lt;/color&gt; điểm Daystar còn lại, sử dụng Resonance Liberation lần nữa để tiêu hao &lt;color=Highlight&gt;{2}&lt;/color&gt; điểm Daystar và thi triển Eclipse.
-- Kiếm Bùng Nổ và Nhật Thực gây Electro DMG tương đương &lt;color=Highlight&gt;{5}&lt;/color&gt; và &lt;color=Highlight&gt;{6}&lt;/color&gt; Attack của Augusta, được tính là Sát Thương Heavy Attack.
-- Thi triển Heavy Attack - Thét Sấm: Thượng Đoạn, Heavy Attack - Thét Sấm: Lùi Bước, Kiếm Bùng Nổ và Nhật Thực sẽ hồi phục thêm &lt;color=Highlight&gt;{7}&lt;/color&gt; điểm Resonance Energy và tăng &lt;color=Highlight&gt;{8}&lt;/color&gt; Sát Thương trong &lt;color=Highlight&gt;{10}s&lt;/color&gt;, có thể chồng chất lên đến &lt;color=Highlight&gt;{9}&lt;/color&gt; lần.</t>
+- Sau khi hoàn thành &lt;color=Highlight&gt;{3}&lt;/color&gt; giai đoạn của Kiếm Bùng Nổ với ít nhất &lt;color=Highlight&gt;{4}&lt;/color&gt; điểm Daystar còn lại, sử dụng Resonance Liberation lần nữa để tiêu hao &lt;color=Highlight&gt;{2}&lt;/color&gt; điểm Daystar và thi triển Nhật Thực.
+- Kiếm Bùng Nổ và Nhật Thực gây Sát Thương Electro tương đương &lt;color=Highlight&gt;{5}&lt;/color&gt; và &lt;color=Highlight&gt;{6}&lt;/color&gt; ATK của Augusta, được tính là Sát Thương Đòn Heavy Attack.
+- Thi triển Đòn Heavy Attack - Thét Sấm: Thượng Đoạn, Đòn Heavy Attack - Thét Sấm: Lùi Bước, Kiếm Bùng Nổ và Nhật Thực sẽ hồi phục thêm &lt;color=Highlight&gt;{7}&lt;/color&gt; điểm Resonance Energy và tăng &lt;color=Highlight&gt;{8}&lt;/color&gt; Sát Thương trong &lt;color=Highlight&gt;{10} giây&lt;/color&gt;, có thể chồng chất lên đến &lt;color=Highlight&gt;{9}&lt;/color&gt; lần.</t>
         </is>
       </c>
     </row>
@@ -12518,7 +12518,7 @@
         <is>
           <t>&lt;color=Highlight&gt;[Resonance Liberation]&lt;/color&gt;
 - Tổng Sát Thương của Resonance Liberation - Kiếm Lời Thề Vĩnh Hằng, Resonance Liberation - Vinh Quang Như Mặt Trời, Vinh Quang Như Mặt Trời - Hạ Sinh Từ Ánh Dương và Vinh Quang Như Mặt Trời - Người Bảo Hộ Vĩnh Cửu tăng thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;.
-- Cooldown chiêu của Resonance Liberation - Kiếm Lời Thề Vĩnh Hằng giảm &lt;color=Highlight&gt;{1}&lt;/color&gt; giây. Khi sử dụng kỹ năng này, phục hồi &lt;color=Highlight&gt;{2}&lt;/color&gt; Năng Lượng Thăng Hoa.</t>
+- Thời gian hồi chiêu của Resonance Liberation - Kiếm Lời Thề Vĩnh Hằng giảm &lt;color=Highlight&gt;{1}&lt;/color&gt; giây. Khi sử dụng kỹ năng này, phục hồi &lt;color=Highlight&gt;{2}&lt;/color&gt; Năng Lượng Thăng Hoa.</t>
         </is>
       </c>
     </row>
@@ -12585,7 +12585,7 @@
       <c r="M181" t="inlineStr">
         <is>
           <t>&lt;color=Highlight&gt;[Forte Circuit]&lt;/color&gt;
-Mỗi khi Chisa gây sát thương &lt;color=Highlight&gt;{0}&lt;/color&gt; lần, Số Mệnh Xé Nát sẽ được kích hoạt, gây Havoc DMG bằng &lt;color=Highlight&gt;{1}&lt;/color&gt; Tấn Công của Chisa (được tính là Sát Thương Resonance Liberation) và áp đặt Havoc Bane. Hiệu ứng này có thể kích hoạt &lt;color=Highlight&gt;&lt;SapTag=2&gt;{2}&lt;/SapTag&gt;&lt;/color&gt; {Cus:Sap,S=lần P=lần SapTag=2} mỗi giây.</t>
+Mỗi khi Chisa gây DMG &lt;color=Highlight&gt;{0}&lt;/color&gt; lần, Số Mệnh Xé Nát sẽ được kích hoạt, gây Sát Thương Havoc bằng &lt;color=Highlight&gt;{1}&lt;/color&gt; ATK của Chisa (được tính là Sát Thương Resonance Liberation) và áp đặt Hiểm Họa Havoc. Hiệu ứng này có thể kích hoạt &lt;color=Highlight&gt;&lt;SapTag=2&gt;{2}&lt;/SapTag&gt;&lt;/color&gt; {Cus:Sap,S=lần P=lần SapTag=2} mỗi giây.</t>
         </is>
       </c>
     </row>
@@ -12652,7 +12652,7 @@
       <c r="M182" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt;
-Khi ở Chế Độ Chainsaw và sau khi sử dụng Chainsaw - Diệt Trừ, dùng Basic Attack để thi triển Chainsaw - Trừng Phạt, gây Havoc DMG bằng &lt;color=Highlight&gt;{0}&lt;/color&gt; Attack của Chisa (được tính là Sát Thương Resonance Liberation) và phục hồi &lt;color=Highlight&gt;{1}&lt;/color&gt; điểm Resonance Energy.</t>
+Khi ở Chế Độ Cưa Xích và sau khi sử dụng Cưa Xích - Diệt Trừ, dùng Đòn Cơ Bản để thi triển Cưa Xích - Trừng Phạt, gây Sát Thương Havoc bằng &lt;color=Highlight&gt;{0}&lt;/color&gt; ATK của Chisa (được tính là Sát Thương Resonance Liberation) và phục hồi &lt;color=Highlight&gt;{1}&lt;/color&gt; điểm Resonance Energy.</t>
         </is>
       </c>
     </row>
@@ -12721,9 +12721,9 @@
       <c r="M183" t="inlineStr">
         <is>
           <t>&lt;color=Highlight&gt;[Forte Circuit]&lt;/color&gt;
-- Cooldown chiêu của Resonance Skill - Mắt Giải Mê giảm &lt;color=Highlight&gt;{0} giây&lt;/color&gt;.
-- Kích hoạt Resonance Skill - Mắt Giải Mê sẽ hồi &lt;color=Highlight&gt;{1}&lt;/color&gt; điểm Resonance Energy và tạo ra &lt;color=Highlight&gt;&lt;SapTag=4&gt;{4}&lt;/SapTag&gt;&lt;/color&gt; điểm Vòng Chainsaw.
-- Kích hoạt Resonance Skill - Vòng Lặp Răng Cưa sẽ tăng &lt;color=Highlight&gt;{2}&lt;/color&gt; Havoc DMG trong &lt;color=Highlight&gt;{3}s&lt;/color&gt;.</t>
+- Thời gian hồi chiêu của Resonance Skill - Mắt Giải Mê giảm &lt;color=Highlight&gt;{0} giây&lt;/color&gt;.
+- Kích hoạt Resonance Skill - Mắt Giải Mê sẽ hồi &lt;color=Highlight&gt;{1}&lt;/color&gt; điểm Resonance Energy và tạo ra &lt;color=Highlight&gt;&lt;SapTag=4&gt;{4}&lt;/SapTag&gt;&lt;/color&gt; điểm Vòng Cưa Xích.
+- Kích hoạt Resonance Skill - Vòng Lặp Răng Cưa sẽ tăng &lt;color=Highlight&gt;{2}&lt;/color&gt; DMG Havoc trong &lt;color=Highlight&gt;{3} giây&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -12861,7 +12861,7 @@
         <is>
           <t>&lt;color=Highlight&gt;[Forte Circuit]&lt;/color&gt;
 - Iuno nhận được &lt;color=Highlight&gt;{1}&lt;/color&gt; tầng Blessing of the Wan Light mỗi &lt;color=Highlight&gt;{0}s&lt;/color&gt;.
-- Sử dụng Heavy Attack - Flux làm tăng Aero DMG thêm &lt;color=Highlight&gt;{2}&lt;/color&gt; trong &lt;color=Highlight&gt;{3}s&lt;/color&gt; và làm chậm kẻ địch xung quanh trong &lt;color=Highlight&gt;{4}s&lt;/color&gt;.</t>
+- Sử dụng Heavy Attack - Flux làm tăng Sát Thương Aero thêm &lt;color=Highlight&gt;{2}&lt;/color&gt; trong &lt;color=Highlight&gt;{3}s&lt;/color&gt; và làm chậm kẻ địch xung quanh trong &lt;color=Highlight&gt;{4}s&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -12928,7 +12928,7 @@
       <c r="M186" t="inlineStr">
         <is>
           <t>&lt;color=Highlight&gt;[Resonance Liberation]&lt;/color&gt;
-Resonance Liberation - Dưới Sóng Trăng có Cooldown chiêu giảm &lt;color=Highlight&gt;{0}s&lt;/color&gt; và giờ đây có thể bắn thêm &lt;color=Highlight&gt;{1}&lt;/color&gt; Mũi Tên Thanh Minh, mỗi mũi tên gây Aero DMG bằng &lt;color=Highlight&gt;{2}&lt;/color&gt; Tấn Công của Iuno, được tính là Sát Thương Resonance Liberation.</t>
+Resonance Liberation - Dưới Sóng Trăng có Thời gian hồi chiêu giảm &lt;color=Highlight&gt;{0} giây&lt;/color&gt; và giờ đây có thể bắn thêm &lt;color=Highlight&gt;{1}&lt;/color&gt; Mũi Tên Thanh Minh, mỗi mũi tên gây Sát Thương Aero bằng &lt;color=Highlight&gt;{2}&lt;/color&gt; ATK của Iuno, được tính là Sát Thương Resonance Liberation.</t>
         </is>
       </c>
     </row>
@@ -12996,8 +12996,8 @@
       <c r="M187" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt;
-- Khi kích hoạt Hellstride trong Threshold State, Galbrena sẽ gây thêm Fusion DMG bằng &lt;color=Highlight&gt;{0}&lt;/color&gt; Attack của bản thân (được tính là sát thương của Heavy Attack) và khiến kẻ địch xung quanh bị trì trệ trong &lt;color=Highlight&gt;{1}s&lt;/color&gt;. Lần tiếp theo sử dụng Basic Attack sẽ kích hoạt Giai Đoạn 3 và 4 của Basic Attack và phục hồi &lt;color=Highlight&gt;{2}&lt;/color&gt; điểm Sinflame.
-- Mỗi lần kích hoạt Hellstride sẽ tăng &lt;color=Highlight&gt;{3}&lt;/color&gt; Fusion DMG trong &lt;color=Highlight&gt;{4}s&lt;/color&gt;, có thể cộng dồn tối đa &lt;color=Highlight&gt;{5}&lt;/color&gt; lần.</t>
+- Khi kích hoạt Hellstride trong Trạng Thái Ngưỡng, Galbrena sẽ gây thêm Sát Thương Fusion bằng &lt;color=Highlight&gt;{0}&lt;/color&gt; ATK của bản thân (được tính là DMG của Đòn Heavy Attack) và khiến kẻ địch xung quanh bị trì trệ trong &lt;color=Highlight&gt;{1} giây&lt;/color&gt;. Lần tiếp theo sử dụng Đòn Basic Attack sẽ kích hoạt Giai Đoạn 3 và 4 của Đòn Basic Attack và phục hồi &lt;color=Highlight&gt;{2}&lt;/color&gt; điểm Sinflame.
+- Mỗi lần kích hoạt Hellstride sẽ tăng &lt;color=Highlight&gt;{3}&lt;/color&gt; Sát Thương Fusion trong &lt;color=Highlight&gt;{4} giây&lt;/color&gt;, có thể cộng dồn tối đa &lt;color=Highlight&gt;{5}&lt;/color&gt; lần.</t>
         </is>
       </c>
     </row>
@@ -13134,8 +13134,8 @@
       <c r="M189" t="inlineStr">
         <is>
           <t>&lt;color=Highlight&gt;[Resonance Liberation]&lt;/color&gt;
-- Cooldown chiêu của Resonance Liberation - Giải Tội Hỏa Ngục giảm &lt;color=Highlight&gt;{0}s&lt;/color&gt;.
-- Khi sử dụng kỹ năng, mỗi &lt;color=Highlight&gt;{1}&lt;/color&gt; điểm Ngọn Sinflame Lỗi hoặc Ngọn Purging Flame sẽ hồi phục thêm &lt;color=Highlight&gt;{2}&lt;/color&gt; điểm Ngọn Lửa Dư Dả. Mỗi điểm Ngọn Sinflame Lỗi hoặc Ngọn Purging Flame sẽ tăng &lt;color=Highlight&gt;{3}&lt;/color&gt; Hệ Số Sát Thương trong &lt;color=Highlight&gt;{4}s&lt;/color&gt;.</t>
+- Thời gian hồi chiêu của Resonance Liberation - Giải Tội Hỏa Ngục giảm &lt;color=Highlight&gt;{0} giây&lt;/color&gt;.
+- Khi sử dụng kỹ năng, mỗi &lt;color=Highlight&gt;{1}&lt;/color&gt; điểm Ngọn Lửa Tội Lỗi hoặc Ngọn Lửa Thanh Tẩy sẽ hồi phục thêm &lt;color=Highlight&gt;{2}&lt;/color&gt; điểm Ngọn Lửa Dư Dả. Mỗi điểm Ngọn Lửa Tội Lỗi hoặc Ngọn Lửa Thanh Tẩy sẽ tăng &lt;color=Highlight&gt;{3}&lt;/color&gt; Hệ Số Sát Thương trong &lt;color=Highlight&gt;{4} giây&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -13203,8 +13203,8 @@
       <c r="M190" t="inlineStr">
         <is>
           <t>&lt;color=Highlight&gt;[Forte Circuit]&lt;/color&gt;
-- Tỷ Lệ Critical Hit tăng thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;. Mỗi &lt;color=Highlight&gt;{1}&lt;/color&gt; Tỷ Lệ Critical Hit vượt quá &lt;color=Highlight&gt;{2}&lt;/color&gt; sẽ được chuyển đổi thành &lt;color=Highlight&gt;{3}&lt;/color&gt; Attack.
-- Gây Critical Hit sẽ tạo ra &lt;color=Highlight&gt;&lt;SapTag=4&gt;{4}&lt;/SapTag&gt;&lt;/color&gt; Lưỡi Gió, gây Aero DMG bằng &lt;color=Highlight&gt;{5}&lt;/color&gt; Attack của Qiuyuan, được tính là sát thương Heavy Attack. Hiệu ứng này có thể kích hoạt &lt;color=Highlight&gt;&lt;SapTag=7&gt;{7}&lt;/SapTag&gt;&lt;/color&gt; lần mỗi &lt;color=Highlight&gt;{6}s&lt;/color&gt;.</t>
+- Crit. Rate tăng thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;. Mỗi &lt;color=Highlight&gt;{1}&lt;/color&gt; Crit. Rate vượt quá &lt;color=Highlight&gt;{2}&lt;/color&gt; sẽ được chuyển đổi thành &lt;color=Highlight&gt;{3}&lt;/color&gt; ATK.
+- Gây Bạo Kích sẽ tạo ra &lt;color=Highlight&gt;&lt;SapTag=4&gt;{4}&lt;/SapTag&gt;&lt;/color&gt; Lưỡi Gió, gây DMG Aero bằng &lt;color=Highlight&gt;{5}&lt;/color&gt; ATK của Qiuyuan, được tính là DMG Đòn Heavy Attack. Hiệu ứng này có thể kích hoạt &lt;color=Highlight&gt;&lt;SapTag=7&gt;{7}&lt;/SapTag&gt;&lt;/color&gt; lần mỗi &lt;color=Highlight&gt;{6} giây&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -13272,8 +13272,8 @@
       <c r="M191" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Basic Attack]&lt;/color&gt;
-- Basic Attack được thay thế bằng Lưỡi Kiếm Lên Tiếng - Mực Tàu, và đòn tấn công Giai Đoạn &lt;color=Highlight&gt;{0}&lt;/color&gt; sẽ hồi phục thêm &lt;color=Highlight&gt;{1}&lt;/color&gt; điểm Swordster's Soliloquy.
-- Khi Heavy Attack hoặc Lưỡi Kiếm Lên Tiếng - Mực Tàu Giai Đoạn &lt;color=Highlight&gt;{2}&lt;/color&gt; trúng mục tiêu, tạo ra Hú Gió hút mục tiêu vào và Aero DMG Bonus của chúng lên &lt;color=Highlight&gt;{3}&lt;/color&gt; trong &lt;color=Highlight&gt;{4}s&lt;/color&gt;. Hiệu ứng này có thể kích hoạt &lt;color=Highlight&gt;&lt;SapTag=6&gt;{6}&lt;/SapTag&gt;&lt;/color&gt; {Cus:Sap,S=lần P=lần SapTag=6} mỗi &lt;color=Highlight&gt;{5}s&lt;/color&gt;.</t>
+- Basic Attack được thay thế bằng Lưỡi Kiếm Lên Tiếng - Mực Tàu, và đòn tấn công Giai Đoạn &lt;color=Highlight&gt;{0}&lt;/color&gt; sẽ hồi phục thêm &lt;color=Highlight&gt;{1}&lt;/color&gt; điểm Độc Thoại Kiếm Khách.
+- Khi Heavy Attack hoặc Lưỡi Kiếm Lên Tiếng - Mực Tàu Giai Đoạn &lt;color=Highlight&gt;{2}&lt;/color&gt; trúng mục tiêu, tạo ra Hú Gió hút mục tiêu vào và Tăng Sát Thương Aero của chúng lên &lt;color=Highlight&gt;{3}&lt;/color&gt; trong &lt;color=Highlight&gt;{4}s&lt;/color&gt;. Hiệu ứng này có thể kích hoạt &lt;color=Highlight&gt;&lt;SapTag=6&gt;{6}&lt;/SapTag&gt;&lt;/color&gt; {Cus:Sap,S=lần P=lần SapTag=6} mỗi &lt;color=Highlight&gt;{5}s&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -13341,8 +13341,8 @@
       <c r="M192" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt;
-- Cooldown chiêu của Resonance Skill - Through the Groves giảm &lt;color=Highlight&gt;{0}s&lt;/color&gt; và tổng Sát Thương tăng thêm &lt;color=Highlight&gt;{1}&lt;/color&gt;. Thi triển kỹ năng này sẽ tăng &lt;color=Highlight&gt;{2}&lt;/color&gt; Aero DMG trong &lt;color=Highlight&gt;{3}s&lt;/color&gt;.
-- Resonance Skill - Through the Groves sẽ tự động thi triển khi Qiuyuan bị tấn công, làm chậm kẻ địch xung quanh trong &lt;color=Highlight&gt;{4}s&lt;/color&gt; và khôi phục &lt;color=Highlight&gt;{5}&lt;/color&gt; điểm Swordster's Soliloquy.</t>
+- Thời gian hồi chiêu của Resonance Skill - Through the Groves giảm &lt;color=Highlight&gt;{0} giây&lt;/color&gt; và tổng Sát Thương tăng thêm &lt;color=Highlight&gt;{1}&lt;/color&gt;. Thi triển kỹ năng này sẽ tăng &lt;color=Highlight&gt;{2}&lt;/color&gt; Sát Thương Aero trong &lt;color=Highlight&gt;{3} giây&lt;/color&gt;.
+- Resonance Skill - Through the Groves sẽ tự động thi triển khi Qiuyuan bị tấn công, làm chậm kẻ địch xung quanh trong &lt;color=Highlight&gt;{4} giây&lt;/color&gt; và khôi phục &lt;color=Highlight&gt;{5}&lt;/color&gt; điểm Swordster's Soliloquy.</t>
         </is>
       </c>
     </row>
@@ -13409,9 +13409,9 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;[Heavy Attack]&lt;/color&gt;
-- Giữ Basic Attack hoặc {Cus:Ipt,Touch=tap PC=click Gamepad=press} Basic Attack khi đang ở trên không để thi triển Heavy Attack - Thét Sấm: Thượng Đoạn, tiêu hao Prowess và nhận hiệu ứng tăng cường.
-- Giữ Basic Attack sau khi thi triển Stage 2 của Basic Attack để thi triển Heavy Attack - Thét Sấm: Lùi Bước, tiêu hao Prowess.</t>
+          <t>&lt;color=Highlight&gt;[Đòn Heavy Attack]&lt;/color&gt;
+- Giữ Basic Attack hoặc {Cus: Ipt,Touch=tap PC=click Gamepad=press} Basic Attack while in mid-air to cast Heavy Attack - Thunderoar: Uppercut at the cost of Prowess and gain enhancements.
+- Hold Basic Attack after casting Basic Attack Stage 2 to cast Heavy Attack - Thunderoar: Backstep at the cost of Prowess.</t>
         </is>
       </c>
     </row>
@@ -13480,9 +13480,9 @@
       <c r="M194" t="inlineStr">
         <is>
           <t>&lt;color=Highlight&gt;[Resonance Liberation]&lt;/color&gt;
-- Thi triển Heavy Attack - Thét Sấm: Thượng Đoạn hoặc Heavy Attack - Thét Sấm: Lùi Bước sẽ tạo ra Daystar.
+- Thi triển Đòn Heavy Attack - Thét Sấm: Thượng Đoạn hoặc Đòn Heavy Attack - Thét Sấm: Lùi Bước sẽ tạo ra Daystar.
 - Sử dụng Resonance Liberation để thi triển Kiếm Bùng Nổ hoặc Nhật Thực, tiêu hao Daystar.
-- Heavy Attack - Thét Sấm: Thượng Đoạn, Heavy Attack - Thét Sấm: Lùi Bước, Kiếm Bùng Nổ và Nhật Thực đều được tăng cường.</t>
+- Đòn Heavy Attack - Thét Sấm: Thượng Đoạn, Đòn Heavy Attack - Thét Sấm: Lùi Bước, Kiếm Bùng Nổ và Nhật Thực đều được tăng cường.</t>
         </is>
       </c>
     </row>
@@ -13549,7 +13549,7 @@
       <c r="M195" t="inlineStr">
         <is>
           <t>&lt;color=Highlight&gt;[Forte Circuit]&lt;/color&gt;
-Mỗi khi Chisa gây sát thương &lt;color=Highlight&gt;{0}&lt;/color&gt; lần, Số Mệnh Xé Nát sẽ được kích hoạt, gây Havoc DMG và áp đặt Havoc Bane.</t>
+Mỗi khi Chisa gây DMG &lt;color=Highlight&gt;{0}&lt;/color&gt; lần, Số Mệnh Xé Nát sẽ được kích hoạt, gây Sát Thương Havoc và áp đặt Hiểm Họa Havoc.</t>
         </is>
       </c>
     </row>
@@ -13616,7 +13616,7 @@
       <c r="M196" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt;
-Khi ở Chế Độ Chainsaw và sau khi sử dụng Chainsaw - Diệt Trừ, dùng Basic Attack để thi triển Chainsaw - Trừng Phạt.</t>
+Khi ở Chế Độ Cưa Xích và sau khi sử dụng Cưa Xích - Diệt Trừ, dùng Đòn Cơ Bản để thi triển Cưa Xích - Trừng Phạt.</t>
         </is>
       </c>
     </row>
@@ -13685,9 +13685,9 @@
       <c r="M197" t="inlineStr">
         <is>
           <t>&lt;color=Highlight&gt;[Forte Circuit]&lt;/color&gt;
-- Cooldown chiêu của Resonance Skill - Mắt Giải Mê được rút ngắn.
-- Kích hoạt Resonance Skill - Mắt Giải Mê sẽ hồi Resonance Energy và tạo ra Vòng Chainsaw.
-- Kích hoạt Resonance Skill - Vòng Lặp Răng Cưa sẽ tăng Havoc DMG.</t>
+- Thời gian hồi chiêu của Resonance Skill - Mắt Giải Mê được rút ngắn.
+- Kích hoạt Resonance Skill - Mắt Giải Mê sẽ hồi Resonance Energy và tạo ra Vòng Cưa Xích.
+- Kích hoạt Resonance Skill - Vòng Lặp Răng Cưa sẽ tăng DMG Havoc.</t>
         </is>
       </c>
     </row>
@@ -13755,8 +13755,8 @@
       <c r="M198" t="inlineStr">
         <is>
           <t>&lt;color=Highlight&gt;[Resonance Skill]&lt;/color&gt;
-- Kỹ Năng "Beyond Biên Giới" được tăng cường.
-- "Closing Refrain" và "Điệp Khúc Bất Tận" hút mục tiêu xung quanh.</t>
+- Kỹ Năng "Vượt Qua Biên Giới" được tăng cường.
+- "Điệp Khúc Kết" và "Điệp Khúc Bất Tận" hút mục tiêu xung quanh.</t>
         </is>
       </c>
     </row>
@@ -13892,7 +13892,7 @@
       <c r="M200" t="inlineStr">
         <is>
           <t>&lt;color=Highlight&gt;[Resonance Liberation]&lt;/color&gt;
-Resonance Liberation có Cooldown chiêu ngắn hơn và giờ đây có thể bắn thêm Mũi Tên Thanh Minh.</t>
+Resonance Liberation có Thời gian hồi chiêu ngắn hơn và giờ đây có thể bắn thêm Mũi Tên Thanh Minh.</t>
         </is>
       </c>
     </row>
@@ -13961,7 +13961,7 @@
         <is>
           <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt;
 - Hellstride được tăng cường.
-- Khi ở Threshold State, sử dụng Basic Attack sau khi thi triển Hellstride sẽ khôi phục Sinflame.</t>
+- Khi ở Trạng Thái Ngưỡng, sử dụng Đòn Basic Attack sau khi thi triển Hellstride sẽ khôi phục Sinflame.</t>
         </is>
       </c>
     </row>
@@ -14098,7 +14098,7 @@
       <c r="M203" t="inlineStr">
         <is>
           <t>&lt;color=Highlight&gt;[Resonance Liberation]&lt;/color&gt;
-- Cooldown chiêu của Resonance Liberation được giảm.
+- Thời gian hồi chiêu của Resonance Liberation được giảm.
 - Khi sử dụng Resonance Liberation, phục hồi thêm Lửa Dư và tăng Sát Thương gây ra.</t>
         </is>
       </c>
@@ -14167,8 +14167,8 @@
       <c r="M204" t="inlineStr">
         <is>
           <t>&lt;color=Highlight&gt;[Forte Circuit]&lt;/color&gt;
-- Tỷ Lệ Critical Hit được tăng lên. Phần Tỷ Lệ Critical Hit vượt quá giá trị nhất định sẽ được chuyển đổi thành Tấn Công.
-- Gây Critical Hit sẽ tạo ra Lưỡi Gió gây Aero DMG.</t>
+- Crit. Rate được tăng lên. Phần Crit. Rate vượt quá giá trị nhất định sẽ được chuyển đổi thành ATK.
+- Gây Bạo Kích sẽ tạo ra Lưỡi Gió gây DMG Aero.</t>
         </is>
       </c>
     </row>
@@ -14237,7 +14237,7 @@
         <is>
           <t>&lt;color=#c49e55&gt;[Basic Attack]&lt;/color&gt;
 - Basic Attack được tăng cường.
-- Heavy Attack hoặc Basic Attack Giai Đoạn &lt;color=Highlight&gt;{2}&lt;/color&gt; tạo ra Hú Gió.</t>
+- Đòn Heavy Attack hoặc Basic Attack Giai Đoạn &lt;color=Highlight&gt;{2}&lt;/color&gt; tạo ra Hú Gió.</t>
         </is>
       </c>
     </row>
@@ -14436,7 +14436,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Ghim trên Bản Đồ ({0}/{1})</t>
+          <t>Đánh dấu trên Bản đồ ({0}/{1})</t>
         </is>
       </c>
     </row>
@@ -14501,7 +14501,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>Sau hiệp 8, Resonator nào còn nhiều HP hơn sẽ thắng cuộc đấu.</t>
+          <t>Sau hiệp 8, Cộng Hưởng Giả nào còn nhiều HP hơn sẽ thắng cuộc đấu.</t>
         </is>
       </c>
     </row>
@@ -14631,7 +14631,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>Kích hoạt Đèn Tín Hiệu Resonance trong khu vực để Dịch Chuyển Tức Thời</t>
+          <t>Kích hoạt Đèn Tín Hiệu Cộng Hưởng trong khu vực để Dịch Chuyển Tức Thời</t>
         </is>
       </c>
     </row>
@@ -14696,7 +14696,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>Đạt Cấp Liên Minh 14 và kích hoạt Resonance Nexus tại Startorch Academy trong Nhiệm Vụ Chính "What Burns Beneath Frostlands" để mở khóa.</t>
+          <t>Đạt Cấp Độ Liên Minh 14 và kích hoạt Mạng Lưới Cộng Hưởng Học viện Startorch trong Nhiệm Vụ Chính "Điều Gì Nung Nấu Dưới Băng Giá" để mở khóa.</t>
         </is>
       </c>
     </row>
@@ -14761,7 +14761,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>Xuống xe và gây Sát Thương bằng 1200% Tấn Công của xe máy lên mục tiêu trong phạm vi, đồng thời tăng nhẹ Off-Tune Level của mục tiêu. Hồi chiêu: 10 giây.</t>
+          <t>Xuống xe và gây Sát Thương bằng 1200% ATK của xe máy lên mục tiêu trong phạm vi, đồng thời tăng nhẹ Mức Lệch Tần của mục tiêu. Thời gian hồi: 10 giây.</t>
         </is>
       </c>
     </row>
@@ -14826,7 +14826,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>Xuống xe và gây Sát Thương bằng 1600% Tấn Công của xe máy lên mục tiêu trong phạm vi, đồng thời tăng vừa Off-Tune Level của mục tiêu. Hồi chiêu: 10 giây.</t>
+          <t>Xuống xe và gây Sát Thương bằng 1600% ATK của xe máy lên mục tiêu trong phạm vi, đồng thời tăng vừa Mức Lệch Tần của mục tiêu. Thời gian hồi: 10 giây.</t>
         </is>
       </c>
     </row>
@@ -14891,7 +14891,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>Xuống xe và gây Sát Thương bằng 2000% Tấn Công của xe máy lên mục tiêu trong phạm vi, đồng thời tăng vừa Off-Tune Level của mục tiêu. Hồi chiêu: 10 giây.</t>
+          <t>Xuống xe và gây Sát Thương bằng 2000% ATK của xe máy lên mục tiêu trong phạm vi, đồng thời tăng vừa Mức Lệch Tần của mục tiêu. Thời gian hồi: 10 giây.</t>
         </is>
       </c>
     </row>
@@ -14956,7 +14956,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>Khi chịu ảnh hưởng của Void Storm, Resonators trong đội nhận ít hơn 20% Sát Thương.</t>
+          <t>Khi chịu ảnh hưởng của Bão Hư Không, Resonator trong đội nhận ít hơn 20% Sát Thương.</t>
         </is>
       </c>
     </row>
@@ -15021,7 +15021,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>Khi chịu ảnh hưởng của Void Storm, Resonators trong đội nhận ít hơn 40% Sát Thương. Resonators trong đội sẽ không bị hạ gục bởi đòn chí mạng, thay vào đó nhận một Lớp Shield tương đương 150% Trường Lực của xe máy. Hiệu ứng này có thể kích hoạt mỗi 3 phút một lần.</t>
+          <t>Khi chịu ảnh hưởng của Bão Hư Không, Resonator trong đội nhận ít hơn 40% Sát Thương. Resonator trong đội sẽ không bị hạ gục bởi đòn chí mạng, thay vào đó nhận một Lớp Khiên tương đương 150% Trường Lực của xe máy. Hiệu ứng này có thể kích hoạt mỗi 3 phút một lần.</t>
         </is>
       </c>
     </row>
@@ -15086,7 +15086,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>Sau khi giải phóng Ram Dynamics, Crit. Rate của Resonators trong đội tăng 20% trong 30 giây.</t>
+          <t>Sau khi giải phóng Ram Dynamics, Crit. Rate của các Resonator trong đội tăng 20% trong 30 giây.</t>
         </is>
       </c>
     </row>
@@ -15281,7 +15281,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>Cấp Độ Kẻ Địch</t>
+          <t>Cấp kẻ địch</t>
         </is>
       </c>
     </row>
@@ -15352,8 +15352,8 @@
         <is>
           <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt;
 - Khi Thanh Nguyện đạt tối đa, Phoebe chỉ có thể tung đòn Heavy Attack - Thánh Ca Giải Oan.
-- Sử dụng Thánh Ca Giải Oan sẽ nhận &lt;color=#c49e55&gt;&lt;SapTag=0&gt;{0}&lt;/SapTag&gt;&lt;/color&gt; {Cus:Sap,S= tầng P= tầng SapTag=0} Gương Light. Khi không có Giọng nói Thần, Đòn Mid-air Attack sẽ tiêu hao &lt;color=#c49e55&gt;&lt;SapTag=1&gt;{1}&lt;/SapTag&gt;&lt;/color&gt; {Cus:Sap,S= tầng P= tầng SapTag=1} Gương Light để hồi phục &lt;color=#c49e55&gt;&lt;SapTag=2&gt;{2}&lt;/SapTag&gt;&lt;/color&gt; {Cus:Sap,S= điểm P= điểm SapTag=2} Giọng nói Thần khi trúng mục tiêu.
-- Khi Phoebe không giữ Giọng nói Thần, lượng STA tiêu hao của Heavy Attack Giữa Không sẽ giảm. Sử dụng Heavy Attack Giữa Không sẽ triệu hồi Prism Light gây Spectro DMG bằng &lt;color=#c49e55&gt;{3}&lt;/color&gt; tổng Attack của Phoebe (được tính là Sát Thương Basic Attack) lên mục tiêu và tung đòn Heavy Attack - Sao Lóe.
+- Sử dụng Thánh Ca Giải Oan sẽ nhận &lt;color=#c49e55&gt;&lt;SapTag=0&gt;{0}&lt;/SapTag&gt;&lt;/color&gt; {Cus:Sap,S= tầng P= tầng SapTag=0} Gương Ánh Sáng. Khi không có Giọng Thần, Đòn ATK Giữa Không sẽ tiêu hao &lt;color=#c49e55&gt;&lt;SapTag=1&gt;{1}&lt;/SapTag&gt;&lt;/color&gt; {Cus:Sap,S= tầng P= tầng SapTag=1} Gương Ánh Sáng để hồi phục &lt;color=#c49e55&gt;&lt;SapTag=2&gt;{2}&lt;/SapTag&gt;&lt;/color&gt; {Cus:Sap,S= điểm P= điểm SapTag=2} Giọng Thần khi trúng mục tiêu.
+- Khi Phoebe không giữ Giọng Thần, lượng STA tiêu hao của Đòn Heavy Attack Giữa Không sẽ giảm. Sử dụng Đòn Heavy Attack Giữa Không sẽ triệu hồi Lăng Kính Ánh Sáng gây Sát Thương Spectro bằng &lt;color=#c49e55&gt;{3}&lt;/color&gt; tổng ATK của Phoebe (được tính là Sát Thương Basic Attack) lên mục tiêu và tung đòn Heavy Attack - Sao Lóe.
 - Đánh trúng mục tiêu bằng Sao Lóe sẽ gây &lt;color=#c49e55&gt;&lt;SapTag=4&gt;{4}&lt;/SapTag&gt;&lt;/color&gt; {Cus:Sap,S= tầng P= tầng SapTag=4} trạng thái Spectro Frazzle.</t>
         </is>
       </c>
@@ -15423,9 +15423,9 @@
       <c r="M223" t="inlineStr">
         <is>
           <t>&lt;color=Highlight&gt;[Basic Attack]&lt;/color&gt;
-- Mục tiêu trong Vòng Gương nhận thêm &lt;color=Highlight&gt;{0}&lt;/color&gt; Spectro DMG.
+- Mục tiêu trong Vòng Gương nhận thêm &lt;color=Highlight&gt;{0}&lt;/color&gt; Sát Thương Spectro.
 - Đánh trúng mục tiêu bằng Basic Attack sẽ nhận &lt;color=Highlight&gt;&lt;SapTag=1&gt;{1}&lt;/SapTag&gt;&lt;/color&gt; {Cus:Sap,S=lớp P=lớp SapTag=1} Hymn, tối đa &lt;color=Highlight&gt;&lt;SapTag=2&gt;{2}&lt;/SapTag&gt;&lt;/color&gt; {Cus:Sap,S=lớp P=lớp SapTag=2}. Hiệu ứng này có thể kích hoạt &lt;color=Highlight&gt;&lt;SapTag=3&gt;{3}&lt;/SapTag&gt;&lt;/color&gt; {Cus:Sap,S=lần P=lần SapTag=3} mỗi giây.
-Khi đạt tối đa lớp Hymn, tất cả lớp sẽ bị loại bỏ để kích nổ một lần, gây Spectro DMG bằng &lt;color=Highlight&gt;{4}&lt;/color&gt; Attack của Phoebe, được tính là Sát Thương Basic Attack.</t>
+Khi đạt tối đa lớp Hymn, tất cả lớp sẽ bị loại bỏ để kích nổ một lần, gây Sát Thương Spectro bằng &lt;color=Highlight&gt;{4}&lt;/color&gt; ATK của Phoebe, được tính là Sát Thương Basic Attack.</t>
         </is>
       </c>
     </row>
@@ -15493,7 +15493,7 @@
       <c r="M224" t="inlineStr">
         <is>
           <t>&lt;color=Highlight&gt;[Resonance Skill]&lt;/color&gt;
-- Khi Thanh Cầu Nguyện đầy, Phoebe chỉ có thể sử dụng Heavy Attack - Khúc Thánh Ca Giải Oan.
+- Khi Thanh Cầu Nguyện đầy, Phoebe chỉ có thể sử dụng Đòn Heavy Attack - Khúc Thánh Ca Giải Oan.
 - Hệ số Sát Thương của Vòng Gương được triệu hồi bởi Resonance Skill tăng thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;, phạm vi tấn công mở rộng thêm &lt;color=Highlight&gt;{1}&lt;/color&gt;. Khi Vòng Gương tồn tại, nó sẽ hút các mục tiêu xung quanh mỗi &lt;color=Highlight&gt;{2}s&lt;/color&gt; và thực hiện Đòn Sóng Xung Kích &lt;color=Highlight&gt;&lt;SapTag=3&gt;{3}&lt;/SapTag&gt;&lt;/color&gt; {Cus:Sap,S=lần P=lần SapTag=3}, gây Sát Thương bằng &lt;color=Highlight&gt;{4}&lt;/color&gt; sức mạnh của Vòng Gương và gây &lt;color=Highlight&gt;&lt;SapTag=5&gt;{5}&lt;/SapTag&gt;&lt;/color&gt; {Cus:Sap,S=lớp P=lớp Hỗn Loạn Quang Phổ SapTag=5} khi trúng mục tiêu. Khi Đòn Sóng Xung Kích trúng mục tiêu, Phoebe sẽ hồi phục thêm &lt;color=Highlight&gt;{6}&lt;/color&gt; điểm Cầu Nguyện.</t>
         </is>
       </c>
@@ -15564,10 +15564,10 @@
       <c r="M225" t="inlineStr">
         <is>
           <t>&lt;color=Highlight&gt;[Resonance Liberation]&lt;/color&gt;
-Glory Ngọn Lửa nhận được các nâng cấp sau:
-- Cooldown chiêu giảm &lt;color=Highlight&gt;{0}&lt;/color&gt;.
-- Khi sử dụng kỹ năng, nhận thêm &lt;color=Highlight&gt;{1}&lt;/color&gt; Tăng Sát Thương Hợp Thể trong &lt;color=Highlight&gt;{2}s&lt;/color&gt;.
-- Ngoài ra, triệu hồi Tiếng Hú Sói hai lần tại vị trí mục tiêu, mỗi lần gây Sát Thương Hợp Thể bằng &lt;color=Highlight&gt;{3}&lt;/color&gt; Tấn Công của Lupa khi trúng đích và phục hồi &lt;color=Highlight&gt;{4}&lt;/color&gt; điểm Resonance Energy.</t>
+Vinh Quang Ngọn Lửa nhận được các nâng cấp sau:
+- Thời gian hồi chiêu giảm &lt;color=Highlight&gt;{0}&lt;/color&gt;.
+- Khi sử dụng kỹ năng, nhận thêm &lt;color=Highlight&gt;{1}&lt;/color&gt; Tăng Sát Thương Hợp Thể trong &lt;color=Highlight&gt;{2} giây&lt;/color&gt;.
+- Ngoài ra, triệu hồi Tiếng Hú Sói hai lần tại vị trí mục tiêu, mỗi lần gây Sát Thương Hợp Thể bằng &lt;color=Highlight&gt;{3}&lt;/color&gt; ATK của Lupa khi trúng đích và phục hồi &lt;color=Highlight&gt;{4}&lt;/color&gt; điểm Resonance Energy.</t>
         </is>
       </c>
     </row>
@@ -15634,7 +15634,7 @@
       <c r="M226" t="inlineStr">
         <is>
           <t>&lt;color=Highlight&gt;[Forte Circuit]&lt;/color&gt;
-Kích hoạt Resonance Skill - Khiêu Vũ Cùng Sói hoặc Resonance Skill - Khiêu Vũ Cùng Sói: Cao Trào sẽ phục hồi &lt;color=Highlight&gt;{0}&lt;/color&gt; HP tối đa của Lupa, hút các mục tiêu xung quanh và triệu hồi Bầy Sói, gây Fusion DMG mỗi giây bằng &lt;color=Highlight&gt;{1}&lt;/color&gt; Attack của cô lên các mục tiêu trong phạm vi. Sát thương gây ra được tính là sát thương từ Basic Attack. Bầy Sói sẽ hồi &lt;color=Highlight&gt;{2}&lt;/color&gt; Resonance Energy khi trúng mục tiêu, hiệu ứng kéo dài &lt;color=Highlight&gt;{3}&lt;/color&gt; giây.</t>
+Kích hoạt Resonance Skill - Khiêu Vũ Cùng Sói hoặc Resonance Skill - Khiêu Vũ Cùng Sói: Cao Trào sẽ phục hồi &lt;color=Highlight&gt;{0}&lt;/color&gt; HP tối đa của Lupa, hút các mục tiêu xung quanh và triệu hồi Bầy Sói, gây DMG Fusion mỗi giây bằng &lt;color=Highlight&gt;{1}&lt;/color&gt; ATK của cô lên các mục tiêu trong phạm vi. DMG gây ra được tính là DMG từ Đòn Basic Attack. Bầy Sói sẽ hồi &lt;color=Highlight&gt;{2}&lt;/color&gt; Resonance Energy khi trúng mục tiêu, hiệu ứng kéo dài &lt;color=Highlight&gt;{3}&lt;/color&gt; giây.</t>
         </is>
       </c>
     </row>
@@ -15704,10 +15704,10 @@
       <c r="M227" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt;
-Inherent Skill - Nhớ Lấy Name Ta nhận được các tăng cường đặc biệt sau:
-- Thời gian cần thiết để vào trạng thái Chạy Nước Rút giảm xuống còn &lt;color=#c49e55&gt;{0}s&lt;/color&gt;.
-- Heavy Attack - Cắn Xé Của Sói, Heavy Attack - Vuốt Sói và Đòn Mid-air Attack - Đòn Lửa gây thêm Fusion DMG bằng &lt;color=#c49e55&gt;{1}&lt;/color&gt; Attack của Lupa.
-- Basic Attack - Sao Rơi và Dodge Counter gây thêm Fusion DMG bằng &lt;color=#c49e55&gt;{2}&lt;/color&gt; Attack của Lupa và hồi phục thêm &lt;color=#c49e55&gt;&lt;SapTag=3&gt;{3}&lt;/SapTag&gt;&lt;/color&gt; {Cus:Sap,S=điểm P=điểm} Ngọn Lửa Sói. Sử dụng Basic Attack ngay sau đó sẽ thi triển lại Basic Attack - Sao Rơi.</t>
+Kỹ Năng Nội Tại - Nhớ Lấy Tên Ta nhận được các tăng cường đặc biệt sau:
+- Thời gian cần thiết để vào trạng thái Chạy Nước Rút giảm xuống còn &lt;color=#c49e55&gt;{0} giây&lt;/color&gt;.
+- Đòn ATK Mạnh - Cắn Xé Của Sói, Đòn ATK Mạnh - Vuốt Sói và Đòn ATK Giữa Không - Đòn Lửa gây thêm Sát Thương Fusion bằng &lt;color=#c49e55&gt;{1}&lt;/color&gt; ATK của Lupa.
+- Đòn Basic Attack - Sao Rơi và Dodge Counter Tránh gây thêm Sát Thương Fusion bằng &lt;color=#c49e55&gt;{2}&lt;/color&gt; ATK của Lupa và hồi phục thêm &lt;color=#c49e55&gt;&lt;SapTag=3&gt;{3}&lt;/SapTag&gt;&lt;/color&gt; {Cus:Sap,S=điểm P=điểm} Ngọn Lửa Sói. Sử dụng Đòn Basic Attack ngay sau đó sẽ thi triển lại Đòn Basic Attack - Sao Rơi.</t>
         </is>
       </c>
     </row>
@@ -15776,9 +15776,9 @@
       <c r="M228" t="inlineStr">
         <is>
           <t>&lt;color=Highlight&gt;[Basic Attack]&lt;/color&gt;
-- Basic Attack giờ bắt đầu từ Stage 3, tăng Hệ Số Sát Thương lên &lt;color=Highlight&gt;{0}&lt;/color&gt;.
+- Basic Attack giờ bắt đầu từ Giai Đoạn 3, tăng Hệ Số Sát Thương lên &lt;color=Highlight&gt;{0}&lt;/color&gt;.
 - Hiệu ứng hút của Basic Attack 3 và phạm vi của Basic Attack 4 được tăng đáng kể.
-- Basic Attack 4 giờ gây Sát Thương &lt;color=Highlight&gt;{1}&lt;/color&gt; lần và hồi phục thêm &lt;color=Highlight&gt;{2}&lt;/color&gt; điểm Forte Gauge khi gây sát thương.</t>
+- Basic Attack 4 giờ gây Sát Thương &lt;color=Highlight&gt;{1}&lt;/color&gt; lần và hồi phục thêm &lt;color=Highlight&gt;{2}&lt;/color&gt; điểm Forte Gauge khi gây DMG.</t>
         </is>
       </c>
     </row>
@@ -15846,9 +15846,9 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;[Dodge]&lt;/color&gt;
-- Dodge thành công kích hoạt Long Chúa Trị Vì, tạo ra Vùng Trì Trệ.
-- Tăng thêm &lt;color=Highlight&gt;{1}&lt;/color&gt; Spectro DMG trong &lt;color=Highlight&gt;{2}s&lt;/color&gt;. Hiệu ứng này có thể kích hoạt mỗi &lt;color=Highlight&gt;{3}s&lt;/color&gt; một lần.
+          <t>&lt;color=Highlight&gt;[Né Tránh]&lt;/color&gt;
+- Né tránh thành công kích hoạt Long Chúa Trị Vì, tạo ra Vùng Trì Trệ.
+- Tăng thêm &lt;color=Highlight&gt;{1}&lt;/color&gt; Sát Thương Spectro trong &lt;color=Highlight&gt;{2}s&lt;/color&gt;. Hiệu ứng này có thể kích hoạt mỗi &lt;color=Highlight&gt;{3}s&lt;/color&gt; một lần.
 - Jinhsi hồi phục &lt;color=Highlight&gt;{0}&lt;/color&gt; điểm Forte Gauge cho mỗi mục tiêu bị ảnh hưởng bởi Vùng Trì Trệ.</t>
         </is>
       </c>
@@ -15919,8 +15919,8 @@
         <is>
           <t>&lt;color=Highlight&gt;[Forte Circuit]&lt;/color&gt;
 Thống Trị Của Loong được tăng cường:
-- Kích hoạt Thống Trị Của Loong khi sử dụng Resonance Liberation, tạo ra Vùng Trì Trệ và tăng &lt;color=Highlight&gt;{0}&lt;/color&gt; Spectro DMG Bonus cho Jinhsi trong &lt;color=Highlight&gt;{1}&lt;/color&gt; giây. Hiệu ứng này có thể kích hoạt mỗi &lt;color=Highlight&gt;{2}&lt;/color&gt; giây một lần.
-- Khi Thống Trị Của Loong đang hoạt động, mỗi &lt;color=Highlight&gt;{3}&lt;/color&gt; giây sẽ giáng sấm sét xuống mục tiêu trong khu vực, gây Spectro DMG bằng &lt;color=Highlight&gt;{4}&lt;/color&gt; Attack của Jinhsi. Khi Thống Trị Của Loong kết thúc, gây Spectro DMG bằng sát thương của Hiện Thân: Kỹ Năng Basic 4, sau đó tấn công khu vực xung quanh với Spectro DMG bằng &lt;color=Highlight&gt;{5}&lt;/color&gt; Attack của Jinhsi.</t>
+- Kích hoạt Thống Trị Của Loong khi sử dụng Resonance Liberation, tạo ra Vùng Trì Trệ và tăng &lt;color=Highlight&gt;{0}&lt;/color&gt; Tăng Sát Thương Spectro cho Jinhsi trong &lt;color=Highlight&gt;{1}&lt;/color&gt; giây. Hiệu ứng này có thể kích hoạt mỗi &lt;color=Highlight&gt;{2}&lt;/color&gt; giây một lần.
+- Khi Thống Trị Của Loong đang hoạt động, mỗi &lt;color=Highlight&gt;{3}&lt;/color&gt; giây sẽ giáng sấm sét xuống mục tiêu trong khu vực, gây Sát Thương Spectro bằng &lt;color=Highlight&gt;{4}&lt;/color&gt; ATK của Jinhsi. Khi Thống Trị Của Loong kết thúc, gây Sát Thương Spectro bằng DMG của Hiện Thân: Kỹ Năng Cơ Bản 4, sau đó tấn công khu vực xung quanh với Sát Thương Spectro bằng &lt;color=Highlight&gt;{5}&lt;/color&gt; ATK của Jinhsi.</t>
         </is>
       </c>
     </row>
@@ -15992,12 +15992,12 @@
       <c r="M231" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt;
-- Skill Chém Nặng - Hoàng Hôn và đòn tấn công cuối của Basic Attack Giai Đoạn &lt;color=#c49e55&gt;{0}&lt;/color&gt; sẽ tạo ra &lt;color=#c49e55&gt;&lt;SapTag=1&gt;{1}&lt;/SapTag&gt;&lt;/color&gt; {Cus:Sap,S=Blaze P=Blazes SapTag=1} và &lt;color=#c49e55&gt;{2}&lt;/color&gt; điểm Resonance Energy.
-- Khi ở Tư Thế Sẵn Sàng, hồi phục &lt;color=#c49e55&gt;&lt;SapTag=3&gt;{3}&lt;/SapTag&gt;&lt;/color&gt; {Cus:Sap,S=Blaze P=Blazes SapTag=3} mỗi giây, và ngay lập tức hồi phục &lt;color=#c49e55&gt;&lt;SapTag=4&gt;{4}&lt;/SapTag&gt;&lt;/color&gt; {Cus:Sap,S=Blaze P=Blazes SapTag=4} khi bị tấn công, đồng thời nhận một lá chắn tương đương &lt;color=#c49e55&gt;{5}&lt;/color&gt; HP tối đa. Hiệu ứng này kéo dài trong &lt;color=#c49e55&gt;{6}s&lt;/color&gt;.
-Khi Blaze đạt tối đa ở Inferno Mode:
-- Tiêu thụ toàn bộ Blazes để thi triển Skill Chém Nặng - Hoàng Hôn: Vô Nhân Sinh Tồn theo các cách sau: {Cus:Ipt,Touch=tap PC=press Gamepad=press} Resonance Skill, thả nút Resonance Skill ở Tư Thế Sẵn Sàng, khi Tư Thế Sẵn Sàng kết thúc, hoặc khi bị tấn công trong Tư Thế Sẵn Sàng.
-- Skill Chém Nặng - Hoàng Hôn: Vô Nhân Sinh Tồn gây Spectro DMG bằng &lt;color=#c49e55&gt;{7}&lt;/color&gt; Attack của Zani, được tính là Sát Thương Heavy Attack và Spectro DMG Frazzle.
-Khi Zani tham gia với tư cách Resonator Concerto, Forte Circuit - Heliacal Ember sẽ không có hiệu lực.</t>
+- Kỹ năng Chém Nặng - Hoàng Hôn và đòn tấn công cuối của Đòn Basic Attack Giai Đoạn &lt;color=#c49e55&gt;{0}&lt;/color&gt; sẽ tạo ra &lt;color=#c49e55&gt;&lt;SapTag=1&gt;{1}&lt;/SapTag&gt;&lt;/color&gt; {Cus:Ipt,Touch=tapping PC=pressing Gamepad=pressing} và &lt;color=#c49e55&gt;{2}&lt;/color&gt; điểm Resonance Energy.
+- Khi ở Tư Thế Sẵn Sàng, hồi phục &lt;color=#c49e55&gt;&lt;SapTag=3&gt;{3}&lt;/SapTag&gt;&lt;/color&gt; {Cus:Sap,S=Blaze P=Blazes SapTag=3} mỗi giây, và ngay lập tức hồi phục &lt;color=#c49e55&gt;&lt;SapTag=4&gt;{4}&lt;/SapTag&gt;&lt;/color&gt; {Cus:Sap,S=Blaze P=Blazes SapTag=4} khi bị tấn công, đồng thời nhận một lá chắn tương đương &lt;color=#c49e55&gt;{5}&lt;/color&gt; HP tối đa. Hiệu ứng này kéo dài trong &lt;color=#c49e55&gt;{6} giây&lt;/color&gt;.
+Khi Blaze đạt tối đa ở Chế Độ Hỏa Ngục:
+- Tiêu thụ toàn bộ Blazes để thi triển Kỹ năng Chém Nặng - Hoàng Hôn: Vô Nhân Sinh Tồn theo các cách sau: {Cus:Ipt,Touch=chạm PC=nhấn Gamepad=nhấn} Resonance Skill, thả nút Resonance Skill ở Tư Thế Sẵn Sàng, khi Tư Thế Sẵn Sàng kết thúc, hoặc khi bị tấn công trong Tư Thế Sẵn Sàng.
+- Kỹ năng Chém Nặng - Hoàng Hôn: Vô Nhân Sinh Tồn gây Sát Thương Spectro bằng &lt;color=#c49e55&gt;{7}&lt;/color&gt; ATK của Zani, được tính là Sát Thương Đòn Heavy Attack và Sát Thương Spectro Frazzle.
+Khi Zani tham gia với tư cách Cộng Hưởng Giả Concerto, Forte Circuit - Heliacal Ember sẽ không có hiệu lực.</t>
         </is>
       </c>
     </row>
@@ -16067,7 +16067,7 @@
         <is>
           <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt;
 - Zani nhận được một tầng Imminent Reckoning khi sử dụng Heavy Slash - Nightfall.
-- Mỗi tầng Imminent Reckoning tăng Spectro DMG của Zani lên &lt;color=#c49e55&gt;{0}&lt;/color&gt;.
+- Mỗi tầng Imminent Reckoning tăng Sát Thương Spectro của Zani lên &lt;color=#c49e55&gt;{0}&lt;/color&gt;.
 - Kết thúc chế độ Inferno sẽ xóa toàn bộ tầng Imminent Reckoning.</t>
         </is>
       </c>
@@ -16141,13 +16141,13 @@
       <c r="M233" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Liberation]&lt;/color&gt;
-- Loại bỏ giới hạn &lt;color=#c49e55&gt;{0}&lt;/color&gt; Ngọn Lửa của Kiên Cường Cuối Cùng, nhưng chỉ có thể sử dụng &lt;color=#c49e55&gt;&lt;SapTag=2&gt;{2}&lt;/SapTag&gt;&lt;/color&gt; {Cus:Sap,S=lần P=lần SapTag=2} trong &lt;color=#c49e55&gt;{1}s&lt;/color&gt;.
-- Khi Zani sử dụng Resonance Liberation - Giữa Dawn và Hoàng Hôn và Kiên Cường Cuối Cùng, cô nhận được một tầng Tính Sổ Gần Kề, tối đa &lt;color=#c49e55&gt;{3}&lt;/color&gt; tầng.
+- Loại bỏ giới hạn &lt;color=#c49e55&gt;{0}&lt;/color&gt; Ngọn Lửa của Kiên Cường Cuối Cùng, nhưng chỉ có thể sử dụng &lt;color=#c49e55&gt;&lt;SapTag=2&gt;{2}&lt;/SapTag&gt;&lt;/color&gt; {Cus:Sap,S=lần P=lần SapTag=2} trong &lt;color=#c49e55&gt;{1} giây&lt;/color&gt;.
+- Khi Zani sử dụng Resonance Liberation - Giữa Bình Minh và Hoàng Hôn và Kiên Cường Cuối Cùng, cô nhận được một tầng Tính Sổ Gần Kề, tối đa &lt;color=#c49e55&gt;{3}&lt;/color&gt; tầng.
 - Kiên Cường Cuối Cùng nhận được các hiệu ứng cộng dồn dựa trên số tầng Tính Sổ Gần Kề:
-Tầng 1: Sử dụng Kiên Cường Cuối Cùng sẽ làm mới thời gian của Inferno Mode và nhận thêm &lt;color=#c49e55&gt;&lt;SapTag=4&gt;{4}&lt;/SapTag&gt;&lt;/color&gt; {Cus:Sap,S=Ngọn Lửa P=Ngọn Lửa SapTag=4}.
+Tầng 1: Sử dụng Kiên Cường Cuối Cùng sẽ làm mới thời gian của Chế Độ Hỏa Ngục và nhận thêm &lt;color=#c49e55&gt;&lt;SapTag=4&gt;{4}&lt;/SapTag&gt;&lt;/color&gt; {Cus:Sap,S=Ngọn Lửa P=Ngọn Lửa SapTag=4}.
 Tầng 2: Phạm vi của Kiên Cường Cuối Cùng được mở rộng.
-Tầng 3: Hệ Số Sát Thương của Kiên Cường Cuối Cùng tăng thêm &lt;color=#c49e55&gt;{5}&lt;/color&gt; mỗi giây trong Inferno Mode.
-Sau khi sử dụng Kiên Cường Cuối Cùng &lt;color=#c49e55&gt;{6}&lt;/color&gt; lần trong Inferno Mode, Inferno Mode sẽ kết thúc và tất cả tầng Tính Sổ Gần Kề sẽ bị xóa.</t>
+Tầng 3: Hệ Số Sát Thương của Kiên Cường Cuối Cùng tăng thêm &lt;color=#c49e55&gt;{5}&lt;/color&gt; mỗi giây trong Chế Độ Hỏa Ngục.
+Sau khi sử dụng Kiên Cường Cuối Cùng &lt;color=#c49e55&gt;{6}&lt;/color&gt; lần trong Chế Độ Hỏa Ngục, Chế Độ Hỏa Ngục sẽ kết thúc và tất cả tầng Tính Sổ Gần Kề sẽ bị xóa.</t>
         </is>
       </c>
     </row>
@@ -16216,9 +16216,9 @@
       <c r="M234" t="inlineStr">
         <is>
           <t>&lt;color=Highlight&gt;[Resonance Skill]&lt;/color&gt;
-- Mục tiêu trúng Resonance Skill - Cartethyia sẽ chịu thêm Aero DMG bằng &lt;color=Highlight&gt;{0}&lt;/color&gt; HP tối đa (cũng được tính là Sát Thương Erosion Aero) và bị nhiễm thêm &lt;color=Highlight&gt;&lt;SapTag=1&gt;{1}&lt;/SapTag&gt;&lt;/color&gt; {Cus:Sap,S=lớp P=lớp Erosion Aero SapTag=1}. Khi sử dụng Resonance Skill - Cartethyia, sẽ triệu hồi thêm một Kiếm Bóng Thần Tính và giảm Cooldown chiêu của Resonance Liberation đi &lt;color=Highlight&gt;{2}s&lt;/color&gt;.
-- Kháng làm gián đoạn được tăng lên khi sử dụng Resonance Skill - Kiếm Đáp Lời Tiếng Sóng và Resonance Skill - Tempest Phá Tan Triều Cường. Sát Thương của chúng được Khuếch Đại thêm &lt;color=Highlight&gt;{3}&lt;/color&gt;. Đánh trúng mục tiêu bằng hai kỹ năng này sẽ gây thêm &lt;color=Highlight&gt;&lt;SapTag=4&gt;{4}&lt;/SapTag&gt;&lt;/color&gt; {Cus:Sap,S=lớp P=lớp Erosion Aero SapTag=4}.
-- Ngoài ra, Cartethyia và Fleurdelys nhận được Hư Không Gió: Khi đánh trúng mục tiêu, tăng số lớp Erosion Aero tối đa mục tiêu có thể nhận thêm 3 trong 10s. Hiệu ứng này không cộng dồn.</t>
+- Mục tiêu trúng Resonance Skill - Cartethyia sẽ chịu thêm Sát Thương Aero bằng &lt;color=Highlight&gt;{0}&lt;/color&gt; HP tối đa (cũng được tính là Sát Thương Xói Mòn Aero) và bị nhiễm thêm &lt;color=Highlight&gt;&lt;SapTag=1&gt;{1}&lt;/SapTag&gt;&lt;/color&gt; {Cus:Sap,S=lớp P=lớp Xói Mòn Aero SapTag=1}. Khi sử dụng Resonance Skill - Cartethyia, sẽ triệu hồi thêm một Kiếm Bóng Thần Tính và giảm thời gian hồi chiêu của Resonance Liberation đi &lt;color=Highlight&gt;{2}s&lt;/color&gt;.
+- Kháng làm gián đoạn được tăng lên khi sử dụng Resonance Skill - Kiếm Đáp Lời Tiếng Sóng và Resonance Skill - Bão Tố Phá Tan Triều Cường. Sát Thương của chúng được Khuếch Đại thêm &lt;color=Highlight&gt;{3}&lt;/color&gt;. Đánh trúng mục tiêu bằng hai kỹ năng này sẽ gây thêm &lt;color=Highlight&gt;&lt;SapTag=4&gt;{4}&lt;/SapTag&gt;&lt;/color&gt; {Cus:Sap,S=lớp P=lớp Xói Mòn Aero SapTag=4}.
+- Ngoài ra, Cartethyia và Fleurdelys nhận được Hư Không Gió: Khi đánh trúng mục tiêu, tăng số lớp Xói Mòn Aero tối đa mục tiêu có thể nhận thêm 3 trong 10s. Hiệu ứng này không cộng dồn.</t>
         </is>
       </c>
     </row>
@@ -16293,15 +16293,15 @@
       <c r="M235" t="inlineStr">
         <is>
           <t>&lt;color=Highlight&gt;[Resonance Liberation]&lt;/color&gt;
-- Resonance Liberation - Lời Nguyện Cầu Chân Thành của Kỵ Sĩ sẽ ban 2 tầng Thánh Khiết. Nếu Fleurdelys có 120 điểm Conviction và Thánh Khiết, Resonance Skill sẽ được thay thế bằng Resonance Skill - Thẩm Phán Tà Ác.
+- Resonance Liberation - Lời Nguyện Cầu Chân Thành của Kỵ Sĩ sẽ ban 2 tầng Thánh Khiết. Nếu Fleurdelys có 120 điểm Niềm Tin và Thánh Khiết, Resonance Skill sẽ được thay thế bằng Resonance Skill - Thẩm Phán Tà Ác.
 - Resonance Skill - Thẩm Phán Tà Ác:
-Sử dụng kỹ năng sẽ tiêu hao 1 tầng Thánh Khiết và toàn bộ Conviction, gây Aero DMG bằng &lt;color=Highlight&gt;{0}&lt;/color&gt; HP tối đa lên tất cả mục tiêu trong phạm vi theo đường thẳng phía trước. Sát thương gây ra được tính là cả Sát Thương Erosion Aero và Sát Thương Basic Attack. Sau đó, áp đặt &lt;color=Highlight&gt;&lt;SapTag=1&gt;{1}&lt;/SapTag&gt;&lt;/color&gt; {Cus:Sap,S=tầng P=tầng Erosion Aero SapTag=1} Erosion Aero lên mục tiêu trúng đòn và hồi phục 50% HP tối đa.
-Sau khi sử dụng Resonance Skill - Thẩm Phán Tà Ác, Fleurdelys sẽ tái nhập Trạng Thái Hiện Thân và nhận 1 tầng Nghi Lễ Freedom, có thể tích lũy tối đa 2 tầng. Sử dụng Resonance Liberation - Lưỡi Kiếm Bão Gào của Fleurdelys hoặc Đòn Mid-air Attack - Cartethyia của Cartethyia trong trạng thái Bão Phước Lành sẽ tiêu hao toàn bộ tầng Nghi Lễ Freedom, mỗi tầng tiêu hao làm tăng Hệ Số Sát Thương của đòn tấn công này thêm &lt;color=Highlight&gt;{2}&lt;/color&gt;. Sau đó, xóa toàn bộ Thánh Khiết.
-- Khi Fleurdelys lần đầu biến hình trở lại thành Cartethyia trong Trạng Thái Hiện Thân, cô sẽ sử dụng Intro Skill - Kiếm Khắc Dấu Vết Thủy Triều và tiêu hao 1 tầng Thánh Khiết để nhận Lời Thề Bất Diệt trong &lt;color=Highlight&gt;{3}s&lt;/color&gt;.
+Sử dụng kỹ năng sẽ tiêu hao 1 tầng Thánh Khiết và toàn bộ Niềm Tin, gây Sát Thương Aero bằng &lt;color=Highlight&gt;{0}&lt;/color&gt; HP tối đa lên tất cả mục tiêu trong phạm vi theo đường thẳng phía trước. DMG gây ra được tính là cả Sát Thương Xói Mòn Aero và Sát Thương Đòn Cơ Bản. Sau đó, áp đặt &lt;color=Highlight&gt;&lt;SapTag=1&gt;{1}&lt;/SapTag&gt;&lt;/color&gt; {Cus:Sap,S=tầng P=tầng Xói Mòn Aero SapTag=1} Xói Mòn Aero lên mục tiêu trúng đòn và hồi phục 50% HP tối đa.
+Sau khi sử dụng Resonance Skill - Thẩm Phán Tà Ác, Fleurdelys sẽ tái nhập Trạng Thái Hiện Thân và nhận 1 tầng Nghi Lễ Tự Do, có thể tích lũy tối đa 2 tầng. Sử dụng Resonance Liberation - Lưỡi Kiếm Bão Gào của Fleurdelys hoặc Đòn Tấn Công Giữa Không - Cartethyia của Cartethyia trong trạng thái Bão Phước Lành sẽ tiêu hao toàn bộ tầng Nghi Lễ Tự Do, mỗi tầng tiêu hao làm tăng Hệ Số Sát Thương của đòn tấn công này thêm &lt;color=Highlight&gt;{2}&lt;/color&gt;. Sau đó, xóa toàn bộ Thánh Khiết.
+- Khi Fleurdelys lần đầu biến hình trở lại thành Cartethyia trong Trạng Thái Hiện Thân, cô sẽ sử dụng Kỹ Năng Khởi Động - Kiếm Khắc Dấu Vết Thủy Triều và tiêu hao 1 tầng Thánh Khiết để nhận Lời Thề Bất Diệt trong &lt;color=Highlight&gt;{3} giây&lt;/color&gt;.
 Lời Thề Bất Diệt:
-- Tất cả sát thương Cartethyia gây ra được Khuếch Đại thêm &lt;color=Highlight&gt;{4}&lt;/color&gt;.
-- Khoảng thời gian kích hoạt Sát Thương Erosion Aero trên mục tiêu trong phạm vi nhất định quanh Cartethyia giảm 50%, và Sát Thương Erosion Aero gây ra được Khuếch Đại thêm 50%.
-- Nếu Cartethyia đồng thời sở hữu Heart of Virtue, Mandate of Divinity và Quyền Năng Bất Hòa mà không ở trạng thái Bão Phước Lành, Đòn Mid-air Attack - Cartethyia khi trúng mục tiêu sẽ kéo dài Lời Thề Bất Diệt thêm &lt;color=Highlight&gt;{5}s&lt;/color&gt; và ban 1 tầng Nghi Lễ Freedom.</t>
+- Tất cả DMG Cartethyia gây ra được Khuếch Đại thêm &lt;color=Highlight&gt;{4}&lt;/color&gt;.
+- Khoảng thời gian kích hoạt Sát Thương Xói Mòn Aero trên mục tiêu trong phạm vi nhất định quanh Cartethyia giảm 50%, và Sát Thương Xói Mòn Aero gây ra được Khuếch Đại thêm 50%.
+- Nếu Cartethyia đồng thời sở hữu Trái Tim Nhân Đức, Thiên Mệnh và Quyền Năng Bất Hòa mà không ở trạng thái Bão Phước Lành, Đòn Tấn Công Giữa Không - Cartethyia khi trúng mục tiêu sẽ kéo dài Lời Thề Bất Diệt thêm &lt;color=Highlight&gt;{5} giây&lt;/color&gt; và ban 1 tầng Nghi Lễ Tự Do.</t>
         </is>
       </c>
     </row>
@@ -16369,8 +16369,8 @@
       <c r="M236" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt;
-- Basic Attack - Fleurdelys Stage 4, Mid-air Attack - Fleurdelys Stage 2, Dodge Counter - Fleurdelys, Resonance Skill - May Tempest Break the Tides và Intro Skill - Kiếm to Mark Tide's Trace sẽ triệu hồi 1 đợt Mưa Thanh Tẩy. Nếu Cartethyia sở hữu Heart of Virtue, Mandate of Divinity và Power of Discord, Mid-air Attack - Cartethyia cũng sẽ triệu hồi một đợt Mưa Thanh Tẩy.
-- Mưa Thanh Tẩy giảm Cooldown chiêu của Resonance Skill - Kiếm to Answer Waves' Call đi &lt;color=#c49e55&gt;{0}s&lt;/color&gt; và gây Aero Sát Thương bằng &lt;color=#c49e55&gt;{1}&lt;/color&gt; Tổng HP lên mục tiêu trong phạm vi. Sát Thương gây ra được tính là cả Aero Erosion DMG và Sát Thương Basic Attack.</t>
+- Đòn Basic Attack - Fleurdelys Giai Đoạn 4, Tấn Công Giữa Không - Fleurdelys Giai Đoạn 2, Dodge Counter Tránh - Fleurdelys, Resonance Skill - May Tempest Break the Tides và Kỹ Năng Khởi Động - Kiếm đơn to Mark Tide's Trace sẽ triệu hồi 1 đợt Mưa Thanh Tẩy. Nếu Cartethyia sở hữu Heart of Virtue, Mandate of Divinity và Power of Discord, Tấn Công Giữa Không - Cartethyia cũng sẽ triệu hồi một đợt Mưa Thanh Tẩy.
+- Mưa Thanh Tẩy giảm thời gian hồi chiêu của Resonance Skill - Kiếm đơn to Answer Waves' Call đi &lt;color=#c49e55&gt;{0} giây&lt;/color&gt; và gây Aero Sát Thương bằng &lt;color=#c49e55&gt;{1}&lt;/color&gt; Tổng HP lên mục tiêu trong phạm vi. Sát Thương gây ra được tính là cả Aero Erosion DMG và Sát Thương Basic Attack.</t>
         </is>
       </c>
     </row>
@@ -16440,10 +16440,10 @@
       <c r="M237" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt;
-- Cooldown chiêu của Resonance Skill - Awakening Gale giảm &lt;color=#c49e55&gt;{0}&lt;/color&gt;, và Rover: Aero miễn nhiễm với gián đoạn khi thi triển kỹ năng.
-- Thi triển Đòn Mid-air Attack - Cloudburst Dance và Basic Attack Giữa Không sẽ tăng Sát Thương Resonance Skill thêm &lt;color=#c49e55&gt;{1}&lt;/color&gt; trong &lt;color=#c49e55&gt;{2}s&lt;/color&gt;, có thể tích lũy tối đa &lt;color=#c49e55&gt;{3} lần&lt;/color&gt;.
-- Phạm vi tấn công của Cloudburst Dance và Basic Attack Giữa Không được mở rộng, và khi trúng mục tiêu sẽ gây &lt;color=#c49e55&gt;&lt;SapTag=4&gt;{4}&lt;/SapTag&gt;&lt;/color&gt; tầng {Cus:Sap,S=Erosion P=Erosion Aero} Aero.
-- Khi Rover: Aero tấn công mục tiêu và gây Erosion Aero, mỗi tầng Erosion sẽ gây thêm Aero DMG bằng &lt;color=#c49e55&gt;{5}&lt;/color&gt; Attack của Rover: Aero, được tính là Sát Thương Resonance Skill.</t>
+- Thời gian hồi chiêu của Resonance Skill - Awakening Gale giảm &lt;color=#c49e55&gt;{0}&lt;/color&gt;, và Vận Mệnh Giả: Aero miễn nhiễm với gián đoạn khi thi triển kỹ năng.
+- Thi triển Đòn ATK Giữa Không - Cloudburst Dance và Đòn ATK Cơ Bản Giữa Không sẽ tăng Sát Thương Resonance Skill thêm &lt;color=#c49e55&gt;{1}&lt;/color&gt; trong &lt;color=#c49e55&gt;{2} giây&lt;/color&gt;, có thể tích lũy tối đa &lt;color=#c49e55&gt;{3} lần&lt;/color&gt;.
+- Phạm vi tấn công của Cloudburst Dance và Đòn ATK Cơ Bản Giữa Không được mở rộng, và khi trúng mục tiêu sẽ gây &lt;color=#c49e55&gt;&lt;SapTag=4&gt;{4}&lt;/SapTag&gt;&lt;/color&gt; tầng {Cus:Sap,S=Xói Mòn P=Xói Mòn Aero} Aero.
+- Khi Vận Mệnh Giả: Aero tấn công mục tiêu và gây Xói Mòn Aero, mỗi tầng Xói Mòn sẽ gây thêm Sát Thương Aero bằng &lt;color=#c49e55&gt;{5}&lt;/color&gt; ATK của Vận Mệnh Giả: Aero, được tính là Sát Thương Resonance Skill.</t>
         </is>
       </c>
     </row>
@@ -16513,10 +16513,10 @@
       <c r="M238" t="inlineStr">
         <is>
           <t>&lt;color=Highlight&gt;[Resonance Skill]&lt;/color&gt;
-- Sử dụng Resonance Skill - "Thức Tỉnh Cơn Gió", Resonance Skill - "Thiên Lạc Đoạn", và Heavy Attack - "Lưỡi Gió Sắc" sẽ nhận &lt;color=Highlight&gt;&lt;SapTag=0&gt;{0}&lt;/SapTag&gt;&lt;/color&gt; {Cus:Sap,S=luỹ thế P=luỹ thế SapTag=0} Windstring Lam, tối đa &lt;color=Highlight&gt;&lt;SapTag=1&gt;{1}&lt;/SapTag&gt;&lt;/color&gt; {Cus:Sap,S=luỹ thế P=luỹ thế SapTag=1}.
-- Nếu Windstring chưa đầy, {Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack ngay sau khi dùng Basic Attack Trên Không để tiêu hao &lt;color=Highlight&gt;&lt;SapTag=2&gt;{2}&lt;/SapTag&gt;&lt;/color&gt; {Cus:Sap,S=luỹ thế P=luỹ thế SapTag=2} Windstring Lam và thi triển Resonance Skill - "Lưu Chuyển Tự Do: Bản Chất".
-- Lưu Chuyển Tự Do: Bản Chất: Skill này không tiêu hao Windstring, và sát thương gây ra bằng &lt;color=Highlight&gt;{3}&lt;/color&gt; sát thương của Resonance Skill - Lưu Chuyển Tự Do.
-- Sử dụng Lưu Chuyển Tự Do khi có Windstring sẽ tiêu hao toàn bộ luỹ thế Windstring Lam, mỗi luỹ thế tăng &lt;color=Highlight&gt;{4}&lt;/color&gt; sát thương gây ra.</t>
+- Sử dụng Resonance Skill - "Thức Tỉnh Cơn Gió", Resonance Skill - "Thiên Lạc Đoạn", và Đòn Heavy Attack - "Lưỡi Gió Sắc" sẽ nhận &lt;color=Highlight&gt;&lt;SapTag=0&gt;{0}&lt;/SapTag&gt;&lt;/color&gt; {Cus:Ipt,Touch=tap PC=press Gamepad=press} Dây Gió Lam, tối đa &lt;color=Highlight&gt;&lt;SapTag=1&gt;{1}&lt;/SapTag&gt;&lt;/color&gt; {Cus:Sap,S=luỹ thế P=luỹ thế SapTag=1}.
+- Nếu Dây Gió chưa đầy, {Cus:Ipt,Touch=chạm PC=nhấn Gamepad=nhấn} Đòn Normal Attack ngay sau khi dùng Đòn Tấn Công Cơ Bản Trên Không để tiêu hao &lt;color=Highlight&gt;&lt;SapTag=2&gt;{2}&lt;/SapTag&gt;&lt;/color&gt; {Cus:Sap,S=luỹ thế P=luỹ thế SapTag=2} Dây Gió Lam và thi triển Resonance Skill - "Lưu Chuyển Tự Do: Bản Chất".
+- Lưu Chuyển Tự Do: Bản Chất: Kỹ năng này không tiêu hao Dây Gió, và DMG gây ra bằng &lt;color=Highlight&gt;{3}&lt;/color&gt; DMG của Resonance Skill - Lưu Chuyển Tự Do.
+- Sử dụng Lưu Chuyển Tự Do khi có Dây Gió sẽ tiêu hao toàn bộ luỹ thế Dây Gió Lam, mỗi luỹ thế tăng &lt;color=Highlight&gt;{4}&lt;/color&gt; DMG gây ra.</t>
         </is>
       </c>
     </row>
@@ -16584,8 +16584,8 @@
       <c r="M239" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt;
-- Cooldown chiêu của Resonance Skill - Skyfall Severance giảm &lt;color=#c49e55&gt;{0}&lt;/color&gt; và nhận &lt;color=#c49e55&gt;&lt;SapTag=1&gt;{1}&lt;/SapTag&gt;&lt;/color&gt; {Cus:Sap,S=lần tích trữ P=lần tích trữ SapTag=1}. Khi trúng đòn, Rover: Aero có thể tiêu hao &lt;color=#c49e55&gt;{2}&lt;/color&gt; HP hiện tại để thi triển Skyfall Severance.
-- Thi triển Resonance Skill - Skyfall Severance sẽ tạo một Lá Chắn không thể chồng chất, có giá trị bằng &lt;color=#c49e55&gt;{3}&lt;/color&gt; HP tối đa của Rover: Aero, kéo dài trong &lt;color=#c49e55&gt;{4}s&lt;/color&gt;. Skill này có thể được tiếp nối bằng Đòn Mid-air Attack - Cloudburst Dance.</t>
+- Thời gian hồi chiêu của Resonance Skill - Skyfall Severance giảm &lt;color=#c49e55&gt;{0}&lt;/color&gt; và nhận &lt;color=#c49e55&gt;&lt;SapTag=1&gt;{1}&lt;/SapTag&gt;&lt;/color&gt; {Cus:Sap,S=lần tích trữ P=lần tích trữ SapTag=1}. Khi trúng đòn, Vận Mệnh Giả: Aero có thể tiêu hao &lt;color=#c49e55&gt;{2}&lt;/color&gt; HP hiện tại để thi triển Skyfall Severance.
+- Thi triển Resonance Skill - Skyfall Severance sẽ tạo một Lá Chắn không thể chồng chất, có giá trị bằng &lt;color=#c49e55&gt;{3}&lt;/color&gt; HP tối đa của Vận Mệnh Giả: Aero, kéo dài trong &lt;color=#c49e55&gt;{4} giây&lt;/color&gt;. Kỹ năng này có thể được tiếp nối bằng Đòn Tấn Công Giữa Không - Cloudburst Dance.</t>
         </is>
       </c>
     </row>
@@ -16656,11 +16656,11 @@
       <c r="M240" t="inlineStr">
         <is>
           <t>&lt;color=Highlight&gt;[Forte Circuit]&lt;/color&gt;
-- Mỗi khi Shorekeeper gây sát thương bằng bướm (Roam Star Butterfly, Ferry Star Butterfly, Altered Dim Star Butterfly, Altered Flare Star Butterfly), cô hồi phục &lt;color=Highlight&gt;{0}&lt;/color&gt; điểm Resonance Energy.
-- Khi ở trạng thái Unbound Form (giữ nút Normal Attack để kích hoạt), Shorekeeper miễn nhiễm với mọi sát thương.
+- Mỗi khi Shorekeeper gây DMG bằng bướm (Roam Star Butterfly, Ferry Star Butterfly, Altered Dim Star Butterfly, Altered Flare Star Butterfly), cô hồi phục &lt;color=Highlight&gt;{0}&lt;/color&gt; điểm Resonance Energy.
+- Khi ở trạng thái Unbound Form (giữ nút Normal Attack để kích hoạt), Shorekeeper miễn nhiễm với mọi DMG.
 - Khi kết thúc Unbound Form:
-Kích hoạt vụ nổ gây Spectro DMG bằng &lt;color=Highlight&gt;{1}&lt;/color&gt; Attack của Shorekeeper. Mỗi đoạn Data Suy Diễn tích lũy làm tăng Hệ Số Sát Thương của vụ nổ thêm &lt;color=Highlight&gt;{2}&lt;/color&gt; và mở rộng phạm vi nổ.
-Tạo ra 5 Roam Star Butterfly tự động truy đuổi kẻ địch, gây Spectro DMG bằng &lt;color=Highlight&gt;{3}&lt;/color&gt; Attack của Shorekeeper. Hồi phục &lt;color=Highlight&gt;{4}&lt;/color&gt; HP của Shorekeeper và giảm &lt;color=Highlight&gt;{5}&lt;/color&gt; Spectro RES DMG của mục tiêu trong &lt;color=Highlight&gt;{6}s&lt;/color&gt; khi trúng đích.</t>
+Kích hoạt vụ nổ gây Sát Thương Spectro bằng &lt;color=Highlight&gt;{1}&lt;/color&gt; ATK của Shorekeeper. Mỗi đoạn Dữ Liệu Suy Diễn tích lũy làm tăng Hệ Số Sát Thương của vụ nổ thêm &lt;color=Highlight&gt;{2}&lt;/color&gt; và mở rộng phạm vi nổ.
+Tạo ra 5 Roam Star Butterfly tự động truy đuổi kẻ địch, gây Sát Thương Spectro bằng &lt;color=Highlight&gt;{3}&lt;/color&gt; ATK của Shorekeeper. Hồi phục &lt;color=Highlight&gt;{4}&lt;/color&gt; HP của Shorekeeper và giảm &lt;color=Highlight&gt;{5}&lt;/color&gt; Kháng Sát Thương Spectro của mục tiêu trong &lt;color=Highlight&gt;{6}s&lt;/color&gt; khi trúng đích.</t>
         </is>
       </c>
     </row>
@@ -16728,8 +16728,8 @@
       <c r="M241" t="inlineStr">
         <is>
           <t>&lt;color=Highlight&gt;[Forte Circuit]&lt;/color&gt;
-- Kích hoạt Suy Luận hoặc Biến Hóa của Forte Circuit sẽ tăng Crit. Rate của Shorekeeper thêm &lt;color=Highlight&gt;{0}&lt;/color&gt; và Crit. DMG thêm &lt;color=Highlight&gt;{1}&lt;/color&gt; trong &lt;color=Highlight&gt;{2}s&lt;/color&gt;.
-- Suy Luận hoặc Biến Hóa gây sát thương bằng &lt;color=Highlight&gt;{3}&lt;/color&gt; sát thương của Intro Skill: Phán Đoán khi trúng mục tiêu. Hiệu ứng này có thể kích hoạt mỗi &lt;color=Highlight&gt;{4}s&lt;/color&gt; một lần.</t>
+- Kích hoạt Suy Luận hoặc Biến Hóa của Forte Circuit sẽ tăng Crit. Rate của Shorekeeper thêm &lt;color=Highlight&gt;{0}&lt;/color&gt; và Crit. DMG thêm &lt;color=Highlight&gt;{1}&lt;/color&gt; trong &lt;color=Highlight&gt;{2} giây&lt;/color&gt;.
+- Suy Luận hoặc Biến Hóa gây DMG bằng &lt;color=Highlight&gt;{3}&lt;/color&gt; DMG của Kỹ Năng Khởi Động: Phán Đoán khi trúng mục tiêu. Hiệu ứng này có thể kích hoạt mỗi &lt;color=Highlight&gt;{4} giây&lt;/color&gt; một lần.</t>
         </is>
       </c>
     </row>
@@ -16799,8 +16799,8 @@
         <is>
           <t>&lt;color=Highlight&gt;[Forte Circuit]&lt;/color&gt;
 Mỗi 30 giây, nhận các hiệu ứng sau:
-- Khi Dodge, Resonators đang hoạt động gần đó trong đội sẽ hồi phục khỏi trạng thái gián đoạn khi bị tấn công hoặc tung lên không, được tính là Dodge thành công. Nếu họ đang ở trên không, họ sẽ hạ cánh xuống mặt đất. Hiệu ứng này có thể kích hoạt tối đa 5 lần.
-- Khi kích hoạt Dodge thành công bằng hiệu ứng trên, Shorekeeper phục hồi HP với tốc độ &lt;color=Highlight&gt;{0}&lt;/color&gt; mỗi giây cho đến khi cô chịu sát thương. Khi hiệu ứng trên chưa được kích hoạt, Shorekeeper nhận thêm &lt;color=Highlight&gt;{1}&lt;/color&gt; Spectro DMG Bonus.</t>
+- Khi né tránh, các Resonator đang hoạt động gần đó trong đội sẽ hồi phục khỏi trạng thái gián đoạn khi bị tấn công hoặc tung lên không, được tính là né tránh thành công. Nếu họ đang ở trên không, họ sẽ hạ cánh xuống mặt đất. Hiệu ứng này có thể kích hoạt tối đa 5 lần.
+- Khi kích hoạt né tránh thành công bằng hiệu ứng trên, Shorekeeper phục hồi HP với tốc độ &lt;color=Highlight&gt;{0}&lt;/color&gt; mỗi giây cho đến khi cô chịu DMG. Khi hiệu ứng trên chưa được kích hoạt, Shorekeeper nhận thêm &lt;color=Highlight&gt;{1}&lt;/color&gt; Tăng Sát Thương Spectro.</t>
         </is>
       </c>
     </row>
@@ -16868,7 +16868,7 @@
       <c r="M243" t="inlineStr">
         <is>
           <t>&lt;color=Highlight&gt;[Forte Circuit]&lt;/color&gt;
-- Kỹ năng Heavy Slash - Nightfall và đòn cuối của Basic Attack Stage 4 cấp &lt;color=Highlight&gt;&lt;SapTag=0&gt;{0}&lt;/SapTag&gt;&lt;/color&gt; {Cus:Sap,S=Blaze P=Blazes SapTag=0} và &lt;color=Highlight&gt;{1}&lt;/color&gt; điểm Resonance Energy.
+- Kỹ năng Heavy Slash - Nightfall và đòn cuối của Basic Attack Giai Đoạn 4 cấp &lt;color=Highlight&gt;&lt;SapTag=0&gt;{0}&lt;/SapTag&gt;&lt;/color&gt; {Cus:Sap,S=Blaze P=Blazes SapTag=0} và &lt;color=Highlight&gt;{1}&lt;/color&gt; điểm Resonance Energy.
 - Khi đòn cuối của Heavy Slash - Nightfall gây sát thương, có &lt;color=Highlight&gt;{2}&lt;/color&gt;% cơ hội thay thế Basic Attack tiếp theo bằng Heavy Slash - Nightfall.</t>
         </is>
       </c>
@@ -16937,8 +16937,8 @@
       <c r="M244" t="inlineStr">
         <is>
           <t>&lt;color=Highlight&gt;[Forte Circuit]&lt;/color&gt;
-- Zani nhận 1 tầng Quyết Tử Lâm Nàn khi gây sát thương bằng đòn cuối của Kỹ Năng Heavy Attack - Hoàng Hôn Lưỡi Kiếm.
-- Mỗi tầng Quyết Tử Lâm Nàn tăng tổng sát thương của Zani thêm {0} trong &lt;color=Highlight&gt;{1}s&lt;/color&gt;, tối đa &lt;color=Highlight&gt;{2}&lt;/color&gt; tầng.</t>
+- Zani nhận 1 tầng Quyết Tử Lâm Nàn khi gây DMG bằng đòn cuối của Kỹ Năng Trọng Kích - Hoàng Hôn Lưỡi Kiếm.
+- Mỗi tầng Quyết Tử Lâm Nàn tăng tổng DMG của Zani thêm {0} trong &lt;color=Highlight&gt;{1} giây&lt;/color&gt;, tối đa &lt;color=Highlight&gt;{2}&lt;/color&gt; tầng.</t>
         </is>
       </c>
     </row>
@@ -17005,7 +17005,7 @@
       <c r="M245" t="inlineStr">
         <is>
           <t>&lt;color=Highlight&gt;[Forte Circuit]&lt;/color&gt;
-Gây sát thương bằng đòn cuối của Kỹ Năng Heavy Attack - Hoàng Hôn Lưỡi Kiếm sẽ giảm Spectro RES của mục tiêu đi &lt;color=Highlight&gt;{0}&lt;/color&gt; trong &lt;color=Highlight&gt;{1}s&lt;/color&gt;.</t>
+Gây sát thương bằng đòn cuối của Kỹ Năng Trọng Kích - Hoàng Hôn Lưỡi Kiếm sẽ giảm Kháng Spectro của mục tiêu đi &lt;color=Highlight&gt;{0}&lt;/color&gt; trong &lt;color=Highlight&gt;{1} giây&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -17072,7 +17072,7 @@
       <c r="M246" t="inlineStr">
         <is>
           <t>&lt;color=Highlight&gt;[Forte Circuit]&lt;/color&gt;
-Resonance Skill - Khiêu Vũ Cùng Sói và Resonance Skill - Khiêu Vũ Cùng Sói: Cao Trào sẽ giảm Fusion RES của mục tiêu &lt;color=Highlight&gt;{0}&lt;/color&gt; trong &lt;color=Highlight&gt;{1}s&lt;/color&gt; khi trúng đích.</t>
+Resonance Skill - Khiêu Vũ Cùng Sói và Resonance Skill - Khiêu Vũ Cùng Sói: Cao Trào sẽ giảm Kháng Fusion của mục tiêu &lt;color=Highlight&gt;{0}&lt;/color&gt; trong &lt;color=Highlight&gt;{1} giây&lt;/color&gt; khi trúng đích.</t>
         </is>
       </c>
     </row>
@@ -17141,9 +17141,9 @@
       <c r="M247" t="inlineStr">
         <is>
           <t>&lt;color=Highlight&gt;Resonance Liberation&lt;/color&gt;
-- Tăng &lt;color=Highlight&gt;{0}&lt;/color&gt; Spectro DMG.
-- Kích hoạt Resonance Liberation - Dawn Giác Ngộ sẽ gây ra &lt;color=Highlight&gt;{1}&lt;/color&gt; vụ nổ, mỗi vụ gây Spectro DMG bằng &lt;color=Highlight&gt;{2}&lt;/color&gt; Attack của Phoebe, được tính là Sát Thương Kỹ Năng Basic.
-- Resonance Liberation giảm &lt;color=Highlight&gt;{3}&lt;/color&gt; Spectro RES của mục tiêu trong &lt;color=Highlight&gt;{4}s&lt;/color&gt; khi trúng đích.</t>
+- Tăng &lt;color=Highlight&gt;{0}&lt;/color&gt; Sát Thương Spectro.
+- Kích hoạt Resonance Liberation - Bình Minh Giác Ngộ sẽ gây ra &lt;color=Highlight&gt;{1}&lt;/color&gt; vụ nổ, mỗi vụ gây Sát Thương Spectro bằng &lt;color=Highlight&gt;{2}&lt;/color&gt; ATK của Phoebe, được tính là Sát Thương Kỹ Năng Cơ Bản.
+- Resonance Liberation giảm &lt;color=Highlight&gt;{3}&lt;/color&gt; Kháng Spectro của mục tiêu trong &lt;color=Highlight&gt;{4} giây&lt;/color&gt; khi trúng đích.</t>
         </is>
       </c>
     </row>
@@ -17211,8 +17211,8 @@
       <c r="M248" t="inlineStr">
         <is>
           <t>&lt;color=Highlight&gt;[Forte Circuit]&lt;/color&gt;
-- Kích hoạt Resonance Liberation - Lưỡi Kiếm Gió Gào và Resonance Skill - Người Phán Xét Tội Ác sẽ nhận được Lưỡi Kiếm Phản Kháng. Nếu Cartethyia đang sở hữu Heart of Virtue, Mandate of Divinity Thần Quyền và Sức Mạnh Discord, Đòn Mid-air Attack - Cartethyia cũng sẽ nhận được Lưỡi Kiếm Phản Kháng.
-- Lưỡi Kiếm Phản Kháng: Tăng HP tối đa thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;. Tất cả sát thương gây ra sẽ bỏ qua &lt;color=Highlight&gt;{1}&lt;/color&gt; Aero RES của mục tiêu. Hiệu ứng này kéo dài &lt;color=Highlight&gt;{2} giây&lt;/color&gt; và có thể cộng dồn tối đa &lt;color=Highlight&gt;{3}&lt;/color&gt; lần.</t>
+- Kích hoạt Resonance Liberation - Lưỡi Kiếm Gió Gào và Resonance Skill - Người Phán Xét Tội Ác sẽ nhận được Lưỡi Kiếm Phản Kháng. Nếu Cartethyia đang sở hữu Trái Tim Nhân Đức, Thiên Mệnh Thần Quyền và Sức Mạnh Tacet Discord, Đòn Mid-air Attack - Cartethyia cũng sẽ nhận được Lưỡi Kiếm Phản Kháng.
+- Lưỡi Kiếm Phản Kháng: Tăng HP tối đa thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;. Tất cả DMG gây ra sẽ bỏ qua &lt;color=Highlight&gt;{1}&lt;/color&gt; Kháng Aero của mục tiêu. Hiệu ứng này kéo dài &lt;color=Highlight&gt;{2} giây&lt;/color&gt; và có thể cộng dồn tối đa &lt;color=Highlight&gt;{3}&lt;/color&gt; lần.</t>
         </is>
       </c>
     </row>
@@ -17282,10 +17282,10 @@
       <c r="M249" t="inlineStr">
         <is>
           <t>&lt;color=Highlight&gt;[Resonance Skill]&lt;/color&gt;
-- Crit. Rate tăng &lt;color=Highlight&gt;{0}&lt;/color&gt;. Resonance Skill - Lưu Chuyển Tự Do tiêu hao Windstring sẽ trở thành Resonance Skill - Lưu Chuyển Tự Do: Siêu Cấp.
+- Crit. Rate tăng &lt;color=Highlight&gt;{0}&lt;/color&gt;. Resonance Skill - Lưu Chuyển Tự Do tiêu hao Dây Gió sẽ trở thành Resonance Skill - Lưu Chuyển Tự Do: Siêu Cấp.
 Resonance Skill - Lưu Chuyển Tự Do: Siêu Cấp:
-- Giai đoạn &lt;color=Highlight&gt;{1}&lt;/color&gt; hút mục tiêu xung quanh. Skill có thêm hai giai đoạn tấn công.
-- Rover: Aero miễn nhiễm với gián đoạn khi thi triển kỹ năng, phạm vi rộng hơn và gây &lt;color=Highlight&gt;&lt;SapTag=2&gt;{2}&lt;/SapTag&gt;&lt;/color&gt; {Cus:Sap,S=luỹ thế P=luỹ thế SapTag=2} Erosion Aero khi trúng mục tiêu.</t>
+- Giai đoạn &lt;color=Highlight&gt;{1}&lt;/color&gt; hút mục tiêu xung quanh. Kỹ năng có thêm hai giai đoạn tấn công.
+- Rover: Aero miễn nhiễm với gián đoạn khi thi triển kỹ năng, phạm vi rộng hơn và gây &lt;color=Highlight&gt;&lt;SapTag=2&gt;{2}&lt;/SapTag&gt;&lt;/color&gt; {Cus:Sap,S=luỹ thế P=luỹ thế SapTag=2} Xói Mòn Aero khi trúng mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -17353,8 +17353,8 @@
       <c r="M250" t="inlineStr">
         <is>
           <t>&lt;color=Highlight&gt;[Resonance Liberation]&lt;/color&gt;
-- Resonance Liberation - Bão Omega bổ sung gây &lt;color=Highlight&gt;&lt;SapTag=0&gt;{0}&lt;/SapTag&gt;&lt;/color&gt; {Cus:Sap,S=lần P=lần SapTag=0} Aero DMG bằng &lt;color=Highlight&gt;{1}&lt;/color&gt; Tấn Công của Rover: Aero và giảm Aero RES của mục tiêu &lt;color=Highlight&gt;{2}&lt;/color&gt; khi trúng đòn trong &lt;color=Highlight&gt;{3}s&lt;/color&gt;. Hiệu ứng này không thể chồng chất.
-- Sử dụng Resonance Liberation - Bão Omega sẽ tăng cường Kỹ Năng Kết Thúc của Rover: Aero: Khi trúng mục tiêu, tăng số tầng Erosion Aero tối đa mục tiêu có thể nhận thêm &lt;color=Highlight&gt;{4}&lt;/color&gt; trong &lt;color=Highlight&gt;{5}s&lt;/color&gt;.</t>
+- Resonance Liberation - Bão Omega bổ sung gây &lt;color=Highlight&gt;&lt;SapTag=0&gt;{0}&lt;/SapTag&gt;&lt;/color&gt; {Cus:Sap,S=lần P=lần SapTag=0} Sát Thương Aero bằng &lt;color=Highlight&gt;{1}&lt;/color&gt; ATK của Rover: Aero và giảm Kháng Aero của mục tiêu &lt;color=Highlight&gt;{2}&lt;/color&gt; khi trúng đòn trong &lt;color=Highlight&gt;{3} giây&lt;/color&gt;. Hiệu ứng này không thể chồng chất.
+- Sử dụng Resonance Liberation - Bão Omega sẽ tăng cường Outro Skill của Rover: Aero: Khi trúng mục tiêu, tăng số tầng Xói Mòn Aero tối đa mục tiêu có thể nhận thêm &lt;color=Highlight&gt;{4}&lt;/color&gt; trong &lt;color=Highlight&gt;{5} giây&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -17421,7 +17421,7 @@
       <c r="M251" t="inlineStr">
         <is>
           <t>&lt;color=Highlight&gt;[Forte Circuit]&lt;/color&gt;
-Dạng Ác Quỷ tăng &lt;color=Highlight&gt;{0}&lt;/color&gt; Sát Thương Kỹ Năng Dư Âm và tăng tổng sát thương của Basic Attack và Đòn Heavy Attack thêm &lt;color=Highlight&gt;{1}&lt;/color&gt;.</t>
+Dạng Ác Quỷ tăng &lt;color=Highlight&gt;{0}&lt;/color&gt; Sát Thương Kỹ Năng Dư Âm và tăng tổng DMG của Đòn Basic Attack và Đòn Heavy Attack thêm &lt;color=Highlight&gt;{1}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -17488,7 +17488,7 @@
       <c r="M252" t="inlineStr">
         <is>
           <t>&lt;color=Highlight&gt;[Forte Circuit]&lt;/color&gt;
-Khi ở trong trạng thái "Bút Tháp Tâm Linh", "Lời Kiếm Dạy Đạo", "Lời Kiếm Cứu Độ" và "Lời Kiếm Hy Sinh" sẽ tăng tổng Sát Thương lên &lt;color=Highlight&gt;{0}&lt;/color&gt;, giảm lượng tiêu hao của "Swordster's Soliloquy" xuống &lt;color=Highlight&gt;{1}&lt;/color&gt;, đồng thời hồi phục &lt;color=Highlight&gt;{2}&lt;/color&gt; điểm Resonance Energy.</t>
+Khi ở trong trạng thái "Bút Tháp Tâm Linh", "Lời Kiếm Dạy Đạo", "Lời Kiếm Cứu Độ" và "Lời Kiếm Hy Sinh" sẽ tăng tổng Sát Thương lên &lt;color=Highlight&gt;{0}&lt;/color&gt;, giảm lượng tiêu hao của "Độc Thoại Kiếm Khách" xuống &lt;color=Highlight&gt;{1}&lt;/color&gt;, đồng thời hồi phục &lt;color=Highlight&gt;{2}&lt;/color&gt; điểm Resonance Energy.</t>
         </is>
       </c>
     </row>
@@ -17555,7 +17555,7 @@
       <c r="M253" t="inlineStr">
         <is>
           <t>&lt;color=Highlight&gt;[Forte Circuit]&lt;/color&gt;
-Mỗi lần nhận Shield sẽ tăng Sát Thương Heavy Attack và tăng Giảm Sát Thương.</t>
+Mỗi lần nhận Khiên sẽ tăng Sát Thương Heavy Attack và tăng Giảm Sát Thương.</t>
         </is>
       </c>
     </row>
@@ -17689,7 +17689,7 @@
       <c r="M255" t="inlineStr">
         <is>
           <t>&lt;color=Highlight&gt;[Resonance Liberation]&lt;/color&gt;
-Resonance Liberation - Đòn Phá Hủy có tổng Sát Thương tăng thêm &lt;color=Highlight&gt;{0}&lt;/color&gt; và Cooldown chiêu giảm &lt;color=Highlight&gt;{1}s&lt;/color&gt;.</t>
+Resonance Liberation - Đòn Phá Hủy có tổng Sát Thương tăng thêm &lt;color=Highlight&gt;{0}&lt;/color&gt; và Thời gian hồi chiêu giảm &lt;color=Highlight&gt;{1} giây&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -17756,7 +17756,7 @@
       <c r="M256" t="inlineStr">
         <is>
           <t>&lt;color=Highlight&gt;[Resonance Liberation]&lt;/color&gt;
-Resonance Liberation - Đòn Phá Hủy có tổng Sát Thương cao hơn và Cooldown chiêu ngắn hơn.</t>
+Resonance Liberation - Đòn Phá Hủy có tổng Sát Thương cao hơn và Thời gian hồi chiêu ngắn hơn.</t>
         </is>
       </c>
     </row>
@@ -17823,7 +17823,7 @@
       <c r="M257" t="inlineStr">
         <is>
           <t>&lt;color=Highlight&gt;[Resonance Liberation]&lt;/color&gt;
-Resonance Liberation - Khoảnh Khắc Hư Vô có tổng Sát Thương tăng thêm &lt;color=Highlight&gt;{0}&lt;/color&gt; và Cooldown chiêu giảm &lt;color=Highlight&gt;{1}s&lt;/color&gt;.</t>
+Resonance Liberation - Khoảnh Khắc Hư Vô có tổng Sát Thương tăng thêm &lt;color=Highlight&gt;{0}&lt;/color&gt; và Thời gian hồi chiêu giảm &lt;color=Highlight&gt;{1} giây&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -17890,7 +17890,7 @@
       <c r="M258" t="inlineStr">
         <is>
           <t>&lt;color=Highlight&gt;[Resonance Liberation]&lt;/color&gt;
-Resonance Liberation - Khoảnh Khắc Hư Vô có tổng Sát Thương cao hơn và Cooldown chiêu ngắn hơn.</t>
+Resonance Liberation - Khoảnh Khắc Hư Vô có tổng Sát Thương cao hơn và Thời gian hồi chiêu ngắn hơn.</t>
         </is>
       </c>
     </row>
@@ -18024,7 +18024,7 @@
       <c r="M260" t="inlineStr">
         <is>
           <t>&lt;color=Highlight&gt;[Basic Attack]&lt;/color&gt;
-Trong &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; - Incarnation, Attack tăng &lt;color=Highlight&gt;{1}&lt;/color&gt;, và mỗi lần sử dụng Basic Attack hoặc Resonance Skill sẽ hồi phục &lt;color=Highlight&gt;{0}&lt;/color&gt; điểm Forte Gauge. Hiệu ứng kéo dài &lt;color=Highlight&gt;{2}s&lt;/color&gt; và có thể chồng chất tối đa &lt;color=Highlight&gt;{3}&lt;/color&gt; lần.</t>
+Trong &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; - Hóa Thân, ATK tăng &lt;color=Highlight&gt;{1}&lt;/color&gt;, và mỗi lần sử dụng Basic Attack hoặc Resonance Skill sẽ hồi phục &lt;color=Highlight&gt;{0}&lt;/color&gt; điểm Forte Gauge. Hiệu ứng kéo dài &lt;color=Highlight&gt;{2}s&lt;/color&gt; và có thể chồng chất tối đa &lt;color=Highlight&gt;{3}&lt;/color&gt; lần.</t>
         </is>
       </c>
     </row>
@@ -18092,7 +18092,7 @@
       <c r="M261" t="inlineStr">
         <is>
           <t>&lt;color=Highlight&gt;[Forte Circuit]&lt;/color&gt;
-- Kỹ năng Heavy Slash - Nightfall và đòn cuối của Basic Attack Stage 4 cấp Blaze và Resonance Energy.
+- Kỹ năng Heavy Slash - Nightfall và đòn cuối của Basic Attack Giai Đoạn 4 cấp Blaze và Resonance Energy.
 - Khi đòn cuối của Heavy Slash - Nightfall gây sát thương, Basic Attack tiếp theo có thể được thay thế bằng Heavy Slash - Nightfall.</t>
         </is>
       </c>
@@ -18160,7 +18160,7 @@
       <c r="M262" t="inlineStr">
         <is>
           <t>&lt;color=Highlight&gt;[Forte Circuit]&lt;/color&gt;
-- Zani nhận hiệu ứng Quyết Tử Lâm Nàn khi gây sát thương bằng đòn cuối của Kỹ Năng Heavy Attack - Hoàng Hôn Lưỡi Kiếm, giúp tăng tổng sát thương của cô.</t>
+- Zani nhận hiệu ứng Quyết Tử Lâm Nàn khi gây DMG bằng đòn cuối của Kỹ Năng Trọng Kích - Hoàng Hôn Lưỡi Kiếm, giúp tăng tổng DMG của cô.</t>
         </is>
       </c>
     </row>
@@ -18227,7 +18227,7 @@
       <c r="M263" t="inlineStr">
         <is>
           <t>&lt;color=Highlight&gt;[Forte Circuit]&lt;/color&gt;
-Gây sát thương bằng đòn cuối của Kỹ Năng Heavy Attack - Hoàng Hôn Lưỡi Kiếm sẽ giảm Spectro RES của mục tiêu.</t>
+Gây sát thương bằng đòn cuối của Kỹ Năng Trọng Kích - Hoàng Hôn Lưỡi Kiếm sẽ giảm Kháng Spectro của mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -18292,7 +18292,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>Sử dụng Outro Skill của Sigrika 100 lần.</t>
+          <t>Sử dụng Kỹ Năng Outro của Sigrika 100 lần.</t>
         </is>
       </c>
     </row>
@@ -18422,7 +18422,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>Đang sử dụng Kỹ Năng Domain</t>
+          <t>Đang sử dụng Kỹ Năng Tổ Tacet</t>
         </is>
       </c>
     </row>
@@ -18487,7 +18487,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>Đang sử dụng Kỹ Năng Domain</t>
+          <t>Đang sử dụng Kỹ Năng Tổ Tacet</t>
         </is>
       </c>
     </row>
@@ -18552,7 +18552,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>Đang sử dụng Kỹ Năng Domain</t>
+          <t>Đang sử dụng Kỹ Năng Tổ Tacet</t>
         </is>
       </c>
     </row>
@@ -18617,7 +18617,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>Đang sử dụng Kỹ Năng Domain</t>
+          <t>Đang sử dụng Kỹ Năng Tổ Tacet</t>
         </is>
       </c>
     </row>
@@ -18682,7 +18682,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>Đang sử dụng Kỹ Năng Domain</t>
+          <t>Đang sử dụng Kỹ Năng Tổ Tacet</t>
         </is>
       </c>
     </row>
@@ -18747,7 +18747,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>Đang sử dụng Kỹ Năng Domain</t>
+          <t>Đang sử dụng Kỹ Năng Tổ Tacet</t>
         </is>
       </c>
     </row>
@@ -18812,7 +18812,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>Thử thách: Sử dụng Skill Chủ động 5 lần, hoặc đạt Round 5.</t>
+          <t>Thử thách: Sử dụng Kỹ năng Chủ động 5 lần, hoặc đạt Vòng 5.</t>
         </is>
       </c>
     </row>
@@ -18877,7 +18877,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>Thử thách: Sử dụng Skill Chủ động 5 lần, hoặc đạt Round 5.</t>
+          <t>Thử thách: Sử dụng Kỹ năng Chủ động 5 lần, hoặc đạt Vòng 5.</t>
         </is>
       </c>
     </row>
@@ -18942,7 +18942,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>Thử thách: Trigger hiệu ứng Nạp năng lượng 5 lần, hoặc đạt Round 5.</t>
+          <t>Thử thách: Kích hoạt hiệu ứng Nạp năng lượng 5 lần, hoặc đạt Vòng 5.</t>
         </is>
       </c>
     </row>
@@ -19007,7 +19007,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>Thử thách: Sử dụng Skill Chủ động 5 lần, hoặc đạt Round 5.</t>
+          <t>Thử thách: Sử dụng Kỹ năng Chủ động 5 lần, hoặc đạt Vòng 5.</t>
         </is>
       </c>
     </row>
@@ -19072,7 +19072,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>Thử thách: Sử dụng Skill Chủ động 5 lần, hoặc đạt Round 5.</t>
+          <t>Thử thách: Sử dụng Kỹ năng Chủ động 5 lần, hoặc đạt Vòng 5.</t>
         </is>
       </c>
     </row>
@@ -19137,7 +19137,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>Thử thách: Trigger hiệu ứng Nạp năng lượng 5 lần, hoặc đạt Round 5.</t>
+          <t>Thử thách: Kích hoạt hiệu ứng Nạp năng lượng 5 lần, hoặc đạt Vòng 5.</t>
         </is>
       </c>
     </row>
@@ -19202,7 +19202,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>Đang sử dụng Kỹ Năng Domain</t>
+          <t>Đang sử dụng Kỹ Năng Tổ Tacet</t>
         </is>
       </c>
     </row>
@@ -19267,7 +19267,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>Đang sử dụng Kỹ Năng Domain</t>
+          <t>Đang sử dụng Kỹ Năng Tổ Tacet</t>
         </is>
       </c>
     </row>
@@ -19332,7 +19332,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>Đang sử dụng Kỹ Năng Domain</t>
+          <t>Đang sử dụng Kỹ Năng Tổ Tacet</t>
         </is>
       </c>
     </row>
@@ -19528,8 +19528,8 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>Khi Giai Đoạn Triển Khai kết thúc, tăng toàn bộ Sát Thương cho Echoes của bạn thêm {0} trong 1 lượt.
-- Khi Battle Stage bắt đầu, tất cả Echoes của bạn nhận được 1 lớp Vỏ Băng mỗi {1} giây, tối đa {2} lớp. Vỏ Băng sẽ bị tiêu hao vào lần tiếp theo Echoes chịu sát thương, giảm sát thương đó xuống còn {3}, sau đó kích hoạt vụ nổ băng gây Glacio DMG lên Echoes của đối thủ, được tính là Sát Thương Đồ Vặt.</t>
+          <t>Khi Giai Đoạn Triển Khai kết thúc, tăng toàn bộ Sát Thương cho Echo của bạn thêm {0} trong 1 lượt.
+- Khi Giai Đoạn Chiến Đấu bắt đầu, tất cả Echo của bạn nhận được 1 lớp Vỏ Băng mỗi {1} giây, tối đa {2} lớp. Vỏ Băng sẽ bị tiêu hao vào lần tiếp theo Echo chịu DMG, giảm DMG đó xuống còn {3}, sau đó kích hoạt vụ nổ băng gây Sát Thương Glacio lên Echo của đối thủ, được tính là Sát Thương Đồ Vặt.</t>
         </is>
       </c>
     </row>
@@ -19596,9 +19596,9 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>Khi Giai Đoạn Triển Khai kết thúc, tăng toàn bộ Kháng Hóa cho Echoes của bạn thêm {1} trong 1 lượt.
+          <t>Khi Giai Đoạn Triển Khai kết thúc, tăng toàn bộ Kháng Hóa cho Echo của bạn thêm {1} trong 1 lượt.
 - Khi bắt đầu trận đấu, nếu bộ bài của bạn chứa ít nhất {0} Đồ Vặt, bạn sẽ nhận được hiệu ứng sau:
-- Khi Battle Stage bắt đầu, tăng Sát Thương Đồ Vặt cho tất cả Echoes thêm {2} cho đến khi lượt kết thúc.</t>
+- Khi Giai Đoạn Chiến Đấu bắt đầu, tăng Sát Thương Đồ Vặt cho tất cả Echo thêm {2} cho đến khi lượt kết thúc.</t>
         </is>
       </c>
     </row>
@@ -19664,7 +19664,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>Mỗi khi triển khai Echoes với Thuộc Tính, kích hoạt Kỹ Năng Special này.</t>
+          <t>Mỗi khi triển khai Echo với Thuộc Tính, kích hoạt Kỹ Năng Đặc Biệt này.</t>
         </is>
       </c>
     </row>
@@ -19729,7 +19729,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>Khi triển khai Echoes này, nhận &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=điểm P=điểm SapTag=0} Năng Lượng, thêm tối đa 1 Mining Reindeer từ bộ bài vào tay, và tăng toàn bộ STR và CON của các Echoes của bạn lên {1} trong 1 lượt.</t>
+          <t>Khi triển khai Echo này, nhận &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=điểm P=điểm SapTag=0} Năng Lượng, thêm tối đa 1 Mining Reindeer từ bộ bài vào tay, và tăng toàn bộ STR và CON của các Echo của bạn lên {1} trong 1 lượt.</t>
         </is>
       </c>
     </row>
@@ -19794,7 +19794,7 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>Khi triển khai Echoes này, nhận &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=điểm P=điểm SapTag=0} Năng Lượng, thêm tối đa 1 Spacetrek Explorer từ bộ bài vào tay, và tăng toàn bộ STR và CON của các Echoes của bạn lên {1} trong 1 lượt.</t>
+          <t>Khi triển khai Echo này, nhận &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=điểm P=điểm SapTag=0} Năng Lượng, thêm tối đa 1 Spacetrek Explorer từ bộ bài vào tay, và tăng toàn bộ STR và CON của các Echo của bạn lên {1} trong 1 lượt.</t>
         </is>
       </c>
     </row>
@@ -19924,7 +19924,7 @@
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>- Khi triển khai Echoes này, Tái Cấu Trúc tất cả các lá trong Vùng Triển khai (không bao gồm Core Echoes). Echoes này sẽ nhận DMG, STR và CON của tất cả Echoes được Tái Cấu Trúc. Với mỗi Novelty được Tái Cấu Trúc, tăng DMG, STR và CON của Echoes này thêm {0}.</t>
+          <t>- Khi triển khai Echo này, Tái Cấu Trúc tất cả các lá trong Vùng Triển Khai (không bao gồm Core Echo). Echo này sẽ nhận DMG, STR và CON của tất cả Echo được Tái Cấu Trúc. Với mỗi Novelty được Tái Cấu Trúc, tăng DMG, STR và CON của Echo này thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>Khi triển khai Echo này, triển khai một Echo có Tăng Cường Rally từ bộ bài và mất {0} HP.</t>
+          <t>Khi triển khai Echo này, triển khai một Echo có Tăng Cường Tập Hợp từ bộ bài và mất {0} HP.</t>
         </is>
       </c>
     </row>
@@ -20119,7 +20119,7 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>Khi triển khai Echoes này, tăng STR và CON của tất cả các Echoes của bạn lên {0}.</t>
+          <t>Khi triển khai Echo này, tăng STR và CON của tất cả các Echo của bạn lên {0}.</t>
         </is>
       </c>
     </row>
@@ -20184,7 +20184,7 @@
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>Khi triển khai Echoes này, giảm {0} HP của đối thủ và tăng STR và CON của tất cả các Echoes của bạn lên {1} trong 1 lượt.</t>
+          <t>Khi triển khai Echo này, giảm {0} HP của đối thủ và tăng STR và CON của tất cả các Echo của bạn lên {1} trong 1 lượt.</t>
         </is>
       </c>
     </row>
@@ -20315,7 +20315,7 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>Khi Giai Đoạn Triển Khai bắt đầu, Activate Rally và Tăng Cường Rally cho các Tacet Discord cùng hàng.
+          <t>Khi Giai Đoạn Triển Khai bắt đầu, Kích Hoạt Tập Hợp và Tăng Cường Tập Hợp cho các Tacet Discord cùng hàng.
 Khi Giai Đoạn Triển Khai kết thúc, tăng STR và CON của các Tacet Discord cùng hàng thêm {0} trong 1 hiệp.</t>
         </is>
       </c>
@@ -20448,9 +20448,9 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>Khi triển khai Echoes này, nó sẽ có Đồng Điệu.
-- Add tối đa 2 Echoes có Đồng Điệu từ bộ bài vào tay và đặt lại Cooldown chiêu của Active Skill của Domain.
-- Khi giai đoạn Triển khai kết thúc, tăng toàn bộ Sát Thương, STR và CON của các Echoes của bạn lên {0} và {1} trong 1 lượt.</t>
+          <t>Khi triển khai Echo này, nó sẽ có Đồng Điệu.
+- Thêm tối đa 2 Echo có Đồng Điệu từ bộ bài vào tay và đặt lại thời gian hồi chiêu của Kỹ Năng Chủ Động của Domain.
+- Khi giai đoạn Triển Khai kết thúc, tăng toàn bộ Sát Thương, STR và CON của các Echo của bạn lên {0} và {1} trong 1 lượt.</t>
         </is>
       </c>
     </row>
@@ -20515,7 +20515,7 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>Khi Battle Stage bắt đầu, bạn mất {0} HP.</t>
+          <t>Khi Giai Đoạn Chiến Đấu bắt đầu, bạn mất {0} HP.</t>
         </is>
       </c>
     </row>
@@ -20645,7 +20645,7 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>- Biến Hóa (3): Tất cả Echoes của bạn có Attunement kích hoạt sẽ tăng {0} Sát Thương, Sức Mạnh và Sức Bền trong 1 lượt. Echoes này sẽ không bị tiêu hao khi Biến Hóa mà thay vào đó được xáo lại vào bộ bài.</t>
+          <t>- Biến Hóa (3): Tất cả Echo của bạn có Attunement kích hoạt sẽ tăng {0} Sát Thương, Sức Mạnh và Sức Bền trong 1 lượt. Echo này sẽ không bị tiêu hao khi Biến Hóa mà thay vào đó được xáo lại vào bộ bài.</t>
         </is>
       </c>
     </row>
@@ -20710,7 +20710,7 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>Biến Hóa (3): Đặt lại Cooldown chiêu của Active Skill Domain. Bản sao này sẽ không bị tiêu hao khi Biến Hóa mà sẽ được xáo lại vào bộ bài.</t>
+          <t>Biến Hóa (3): Reset the thời gian hồi of your Domain's Active Skill. This Echo will not be consumed when Transformed but instead shuffled back to the deck.</t>
         </is>
       </c>
     </row>
@@ -20778,10 +20778,10 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;- When your opponent Reconstructs a card, they gain no Energy. 
-- Each time you deploy an Echo, increase one of your Echoes' STR and CON by {0}.&lt;/color&gt;
-- Khi Giai đoạn Triển khai kết thúc, tăng CON của tất cả Echoes của ngươi lên {1} trong 1 hiệp.
-- Khi Giai đoạn Chiến đấu bắt đầu, tăng Sát Thương Đột Phá của tất cả Echoes lên {2} đến hết hiệp.</t>
+          <t>&lt;color=Highlight&gt;- Khi đối thủ Tái cấu trúc thẻ, chúng không nhận được Năng lượng. 
+- Mỗi lần triển khai Echo, tăng STR và CON của một Echo bất kỳ của ngươi lên {0}.&lt;/color&gt;
+- Khi Giai đoạn Triển khai kết thúc, tăng CON của tất cả Echo của ngươi lên {1} trong 1 hiệp.
+- Khi Giai đoạn Chiến đấu bắt đầu, tăng Sát Thương Đột Phá của tất cả Echo lên {2} đến hết hiệp.</t>
         </is>
       </c>
     </row>
@@ -20850,11 +20850,11 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;- When your opponent Reconstructs a card, they gain no Energy.
-- When the Battle Stage starts, increase all your Echoes' STR and CON by {3}.
-- Each time you deploy an Echo, increase one of your Echoes' STR and CON by {0}.&lt;/color&gt;
-- Khi Giai Đoạn Triển khai kết thúc, tăng {1} CON cho tất cả Echoes của bạn trong 1 lượt.
-- Khi Battle Stage bắt đầu, tăng {2} Sát Thương Đột Phá cho tất cả Echoes cho đến khi lượt kết thúc.</t>
+          <t>&lt;color=Highlight&gt;- Khi đối thủ Tái Cấu Trúc thẻ, chúng không nhận được Năng Lượng.
+- Khi Giai Đoạn Chiến Đấu bắt đầu, tăng {3} STR và CON cho tất cả Echo của bạn.
+- Mỗi lần triển khai Echo, tăng {0} STR và CON cho một Echo của bạn.&lt;/color&gt;
+- Khi Giai Đoạn Triển Khai kết thúc, tăng {1} CON cho tất cả Echo của bạn trong 1 lượt.
+- Khi Giai Đoạn Chiến Đấu bắt đầu, tăng {2} Sát Thương Đột Phá cho tất cả Echo cho đến khi lượt kết thúc.</t>
         </is>
       </c>
     </row>
@@ -20924,12 +20924,12 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;- When your opponent Reconstructs a card, they gain no Energy.
-- When the Battle Stage starts, increase all your Echoes' STR and CON by {3}.
-- When the round starts, you recover {4} HP.
-- When you deploy an Echo, increase one of your Echoes' STR and CON by {0}.&lt;/color&gt;
-- Khi Giai Đoạn Triển khai kết thúc, tăng chỉ số Thể Trạng của tất cả Resonator của ngươi thêm {1} trong 1 hiệp.
-- Khi Battle Stage bắt đầu, tăng toàn bộ Sát Thương Đột Phá của Resonator thêm {2} đến hết hiệp.</t>
+          <t>&lt;color=Highlight&gt;- Khi đối thủ Tái Cấu Trúc thẻ, họ không nhận được Năng Lượng.
+- Khi Giai Đoạn Chiến Đấu bắt đầu, tăng toàn bộ chỉ số Sức Mạnh và Thể Trạng của Cộng Hưởng Giả của ngươi thêm {3}.
+- Khi hiệp bắt đầu, ngươi hồi {4} HP.
+- Khi triển khai Cộng Hưởng Giả, tăng chỉ số Sức Mạnh và Thể Trạng của một Cộng Hưởng Giả của ngươi thêm {0}.&lt;/color&gt;
+- Khi Giai Đoạn Triển Khai kết thúc, tăng chỉ số Thể Trạng của tất cả Cộng Hưởng Giả của ngươi thêm {1} trong 1 hiệp.
+- Khi Giai Đoạn Chiến Đấu bắt đầu, tăng toàn bộ Sát Thương Đột Phá của Cộng Hưởng Giả thêm {2} đến hết hiệp.</t>
         </is>
       </c>
     </row>
@@ -20995,8 +20995,8 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>- Trong lượt này, tất cả Echoes cùng hàng với Thẻ Novelty này sẽ nhận hiệu ứng sau:
-- Trong Battle Stage, các Echoes này sẽ kích hoạt một vụ nổ băng quanh mình mỗi {0} giây, gây Glacio DMG lên Echoes của đối thủ, được tính là Sát Thương Novelty.</t>
+          <t>- Trong lượt này, tất cả Echo cùng hàng với Thẻ Novelty này sẽ nhận hiệu ứng sau:
+- Trong Giai Đoạn Chiến Đấu, các Echo này sẽ kích hoạt một vụ nổ băng quanh mình mỗi {0} giây, gây Sát Thương Glacio lên Echo của đối thủ, được tính là Sát Thương Novelty.</t>
         </is>
       </c>
     </row>
@@ -21127,7 +21127,7 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>Increase STR và CON của Echo này lên {0} trong 1 hiệp.
+          <t>Tăng STR và CON của Echo này lên {0} trong 1 hiệp.
 - Trước khi Giai Đoạn Triển Khai tiếp theo bắt đầu, hãy Tái Tạo lá bài này.</t>
         </is>
       </c>
@@ -21194,8 +21194,8 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>- Trong vòng này, tất cả Echoes của bạn sẽ nhận hiệu ứng sau:
-- Mỗi khi gây Sát Thương Mới Lạ (ngoại trừ Sát Thương Mới Lạ từ Điện Tích Nổ), sẽ tạo ra một quả cầu lửa gây thêm Fusion DMG, được tính là Sát Thương Mới Lạ. Hiệu ứng này có thể kích hoạt mỗi {0} giây một lần.</t>
+          <t>- Trong vòng này, tất cả Echo của bạn sẽ nhận hiệu ứng sau:
+- Mỗi khi gây Sát Thương Mới Lạ (ngoại trừ Sát Thương Mới Lạ từ Điện Tích Nổ), sẽ tạo ra một quả cầu lửa gây thêm Sát Thương Fusion, được tính là Sát Thương Mới Lạ. Hiệu ứng này có thể kích hoạt mỗi {0} giây một lần.</t>
         </is>
       </c>
     </row>
@@ -21325,7 +21325,7 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>- Đặt lại Cooldown chiêu Active Skill của lá bài đã chọn.</t>
+          <t>- Đặt lại thời gian hồi chiêu Kỹ Năng Chủ Động của lá bài đã chọn.</t>
         </is>
       </c>
     </row>
@@ -21390,7 +21390,7 @@
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>Triển khai Nhanh 1 Flautist từ tay vào ô trống và Tái Cấu trúc lá bài này. Bạn mất {0} HP.</t>
+          <t>Triển Khai Nhanh 1 Flautist từ tay vào ô trống và Tái Cấu trúc lá bài này. Bạn mất {0} HP.</t>
         </is>
       </c>
     </row>
@@ -21455,7 +21455,7 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>Increase STR và CON của Echo mục tiêu lên {0} trong &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; {Cus:Sap,S=hiệp P=hiệp SapTag=1}.</t>
+          <t>Tăng STR và CON của Echo mục tiêu lên {0} trong &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; {Cus:Sap,S=hiệp P=hiệp SapTag=1}.</t>
         </is>
       </c>
     </row>
@@ -21585,7 +21585,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Triển khai Nhanh 1 Tambourinist từ tay vào ô trống và Tái Cấu trúc lá bài này. Bạn mất {0} HP.</t>
+          <t>Triển Khai Nhanh 1 Tambourinist từ tay vào ô trống và Tái Cấu trúc lá bài này. Bạn mất {0} HP.</t>
         </is>
       </c>
     </row>
@@ -21650,7 +21650,7 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>- Ngay lập tức, Bản Sao bên trái Echo này nhận &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=lượt sử dụng P=lượt sử dụng SapTag=0} của Active Skill và Cooldown chiêu được đặt lại.</t>
+          <t>- Ngay lập tức, Bản Sao bên trái Echo này nhận &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=lượt sử dụng P=lượt sử dụng SapTag=0} của Kỹ Năng Chủ Động và thời gian hồi chiêu được đặt lại.</t>
         </is>
       </c>
     </row>
@@ -21715,7 +21715,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>- Đặt lại Cooldown chiêu Active Skill của Echo đã chọn và Tái Cấu trúc lá bài này.</t>
+          <t>- Đặt lại thời gian hồi chiêu Kỹ Năng Chủ Động của Echo đã chọn và Tái Cấu trúc lá bài này.</t>
         </is>
       </c>
     </row>
@@ -21780,7 +21780,7 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>- Đặt lại Cooldown chiêu Active Skill của một Novelty khác.</t>
+          <t>- Đặt lại thời gian hồi chiêu Kỹ Năng Chủ Động của một Novelty khác.</t>
         </is>
       </c>
     </row>
@@ -21979,7 +21979,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>- Nạp Năng: Mỗi khi sử dụng Active Skill của lá bài, lá này nhận 1 điểm Nạp Năng.</t>
+          <t>- Nạp Năng: Mỗi khi sử dụng Kỹ Năng Chủ Động của lá bài, lá này nhận 1 điểm Nạp Năng.</t>
         </is>
       </c>
     </row>
@@ -22047,7 +22047,7 @@
       <c r="M321" t="inlineStr">
         <is>
           <t>Khi trận đấu bắt đầu, nếu bộ bài của ngươi có ít nhất 6 lá Fusion, ngươi sẽ nhận được các hiệu ứng sau:
-- Nạp Năng: Lá bài này nhận 1 điểm Nạp Năng mỗi khi ngươi sử dụng Active Skill của lá bài khác.
+- Nạp Năng: Lá bài này nhận 1 điểm Nạp Năng mỗi khi ngươi sử dụng Kỹ Năng Chủ Động của lá bài khác.
 - Quá Tải: Khi Nạp Năng đạt {0} điểm, xóa toàn bộ điểm và giảm {1} HP của đối thủ.</t>
         </is>
       </c>
@@ -22116,8 +22116,8 @@
       <c r="M322" t="inlineStr">
         <is>
           <t>Khi trận đấu bắt đầu, nếu bộ bài của ngươi có ít nhất 6 lá Electro, ngươi sẽ nhận được các hiệu ứng sau:
-- Nạp Năng: Lá bài này nhận 1 điểm Nạp Năng mỗi khi ngươi sử dụng Active Skill của lá bài khác.
-- Quá Tải: Khi Nạp Năng đạt {0} điểm, xóa toàn bộ điểm và đặt lại Cooldown chiêu Active Skill của Domain này.</t>
+- Nạp Năng: Lá bài này nhận 1 điểm Nạp Năng mỗi khi ngươi sử dụng Kỹ Năng Chủ Động của lá bài khác.
+- Quá Tải: Khi Nạp Năng đạt {0} điểm, xóa toàn bộ điểm và đặt lại thời gian hồi chiêu Kỹ Năng Chủ Động của Tổ Tacet này.</t>
         </is>
       </c>
     </row>
@@ -22186,7 +22186,7 @@
         <is>
           <t>Khi trận đấu bắt đầu, nếu bộ bài của ngươi có ít nhất 8 lá bài có Chi Phí 3, ngươi sẽ nhận được các hiệu ứng sau:
 - Nạp Năng: Lá bài này nhận 1 điểm Nạp Năng mỗi khi ngươi Tái Cấu Trúc một lá bài.
-- Quá Tải: Khi Nạp Năng đạt {0} điểm, xóa toàn bộ điểm và đặt lại Cooldown chiêu Active Skill của Domain này.</t>
+- Quá Tải: Khi Nạp Năng đạt {0} điểm, xóa toàn bộ điểm và đặt lại thời gian hồi chiêu Kỹ Năng Chủ Động của Tổ Tacet này.</t>
         </is>
       </c>
     </row>
@@ -22453,8 +22453,8 @@
       <c r="M327" t="inlineStr">
         <is>
           <t>- Khi bắt đầu trận đấu, nếu bộ bài của bạn có ít nhất 3 Vật Phẩm Đặc Biệt, nhận các hiệu ứng sau:
-- Nạp Năng: Domain này nhận 1 tầng Nạp Năng mỗi khi bạn kích hoạt hiệu ứng Nạp Năng của lá bài khác.
-- Quá Tải: Khi Nạp Năng đạt {0} tầng, xóa toàn bộ tầng và tăng STR và CON của một Echoes của bạn lên {1}.</t>
+- Nạp Năng: Miền này nhận 1 tầng Nạp Năng mỗi khi bạn kích hoạt hiệu ứng Nạp Năng của lá bài khác.
+- Quá Tải: Khi Nạp Năng đạt {0} tầng, xóa toàn bộ tầng và tăng STR và CON của một Echo của bạn lên {1}.</t>
         </is>
       </c>
     </row>
@@ -22521,7 +22521,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>- Nạp Năng: Mỗi khi sử dụng Active Skill của lá bài, lá này nhận 1 điểm Nạp Năng.</t>
+          <t>- Nạp Năng: Mỗi khi sử dụng Kỹ Năng Chủ Động của lá bài, lá này nhận 1 điểm Nạp Năng.</t>
         </is>
       </c>
     </row>
@@ -22586,7 +22586,7 @@
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>Đã đạt giới hạn Thể Lực Flight</t>
+          <t>Max Flight STA</t>
         </is>
       </c>
     </row>
@@ -22651,7 +22651,7 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>Kích hoạt tất cả Resonance Beacon ở Lahai-Roi.</t>
+          <t>Kích hoạt tất cả Đèn Cộng Hưởng ở Lahai-Roi.</t>
         </is>
       </c>
     </row>
@@ -22716,7 +22716,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>Mở khóa 3 Resonance Nexus bất kỳ tại Lahai-Roi</t>
+          <t>Mở khóa 3 Điểm Cộng Hưởng bất kỳ ở Lahai-Roi</t>
         </is>
       </c>
     </row>
@@ -22781,7 +22781,7 @@
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>- Đặt lại Cooldown chiêu Active Skill của lá bài đã chọn.</t>
+          <t>- Đặt lại thời gian hồi chiêu Kỹ Năng Chủ Động của lá bài đã chọn.</t>
         </is>
       </c>
     </row>
@@ -22846,7 +22846,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>- Đặt lại Cooldown chiêu Active Skill của lá bài đã chọn.</t>
+          <t>- Đặt lại thời gian hồi chiêu Kỹ Năng Chủ Động của lá bài đã chọn.</t>
         </is>
       </c>
     </row>
@@ -22911,7 +22911,7 @@
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>- Đặt lại Cooldown chiêu Active Skill của lá bài đã chọn.</t>
+          <t>- Đặt lại thời gian hồi chiêu Kỹ Năng Chủ Động của lá bài đã chọn.</t>
         </is>
       </c>
     </row>
@@ -23174,9 +23174,9 @@
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;- When your opponent Reconstructs a card, they gain no Energy.
-- Each time you deploy an Echo, increase one of your Echoes' STR and CON by {2}.&lt;/color&gt;
-- Nạp Năng: Thẻ này nhận 1 điểm Nạp Năng mỗi khi bạn sử dụng Active Skill của thẻ khác.
+          <t>&lt;color=Highlight&gt;- Khi đối thủ Tái Cấu Trúc thẻ, chúng không nhận được Năng Lượng.
+- Mỗi lần triển khai Echo, tăng {2} STR và CON cho một Echo của bạn.&lt;/color&gt;
+- Nạp Năng: Thẻ này nhận 1 điểm Nạp Năng mỗi khi bạn sử dụng Kỹ Năng Chủ Động của thẻ khác.
 - Quá Tải: Khi Nạp Năng đạt {0} điểm, xóa toàn bộ điểm và giảm {1} HP của đối thủ.</t>
         </is>
       </c>
@@ -23246,10 +23246,10 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;- When your opponent Reconstructs a card, they gain no Energy.
-- When the Battle Stage starts, increase all your Echoes' STR and CON by {3}.
-- Each time you deploy an Echo, increase one of your Echoes' STR and CON by {2}.&lt;/color&gt;
-- Nạp Năng: Thẻ này nhận 1 điểm Nạp Năng mỗi khi ngươi sử dụng Active Skill của thẻ khác.
+          <t>&lt;color=Highlight&gt;- Khi đối thủ Tái Cấu Trúc thẻ, họ không nhận được Năng Lượng.
+- Khi Giai Đoạn Chiến Đấu bắt đầu, tăng toàn bộ chỉ số Sức Mạnh và Thể Trạng của Cộng Hưởng Giả của ngươi thêm {3}.
+- Mỗi lần triển khai Cộng Hưởng Giả, tăng chỉ số Sức Mạnh và Thể Trạng của một Cộng Hưởng Giả của ngươi thêm {2}.&lt;/color&gt;
+- Nạp Năng: Thẻ này nhận 1 điểm Nạp Năng mỗi khi ngươi sử dụng Kỹ Năng Chủ Động của thẻ khác.
 - Quá Tải: Khi Nạp Năng đạt {0} điểm, xóa toàn bộ điểm và giảm HP của đối thủ đi {1}.</t>
         </is>
       </c>
@@ -23320,11 +23320,11 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;- When your opponent Reconstructs a card, they gain no Energy.
-- When the Battle Stage starts, increase all your Echoes' STR and CON by {3}.
-- When the round starts, you recover {4} HP.
-- Each time you deploy an Echo, increase one of your Echoes' STR and CON by {2}.&lt;/color&gt;
-- Nạp Năng: Thẻ này nhận 1 điểm Nạp Năng mỗi khi ngươi sử dụng Active Skill của thẻ khác.
+          <t>&lt;color=Highlight&gt;- Khi đối thủ Tái Cấu Trúc thẻ, họ không nhận được Năng Lượng.
+- Khi Giai Đoạn Chiến Đấu bắt đầu, tăng toàn bộ chỉ số Sức Mạnh và Thể Trạng của Cộng Hưởng Giả của ngươi thêm {3}.
+- Khi hiệp bắt đầu, ngươi hồi {4} HP.
+- Mỗi lần triển khai Cộng Hưởng Giả, tăng chỉ số Sức Mạnh và Thể Trạng của một Cộng Hưởng Giả của ngươi thêm {2}.&lt;/color&gt;
+- Nạp Năng: Thẻ này nhận 1 điểm Nạp Năng mỗi khi ngươi sử dụng Kỹ Năng Chủ Động của thẻ khác.
 - Quá Tải: Khi Nạp Năng đạt {0} điểm, xóa toàn bộ điểm và giảm HP của đối thủ đi {1}.</t>
         </is>
       </c>
@@ -23393,10 +23393,10 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;- When your opponent Reconstructs a card, they gain no Energy.
-- Whenever you deploy an Echo, increase one of your Echoes' STR and CON by {1}.&lt;/color&gt;
+          <t>&lt;color=Highlight&gt;- Khi đối thủ Tái Cấu Trúc thẻ, họ không nhận được Năng Lượng.
+- Mỗi khi triển khai Cộng Hưởng Giả, tăng chỉ số Sức Mạnh và Thể Trạng của một Cộng Hưởng Giả của ngươi thêm {1}.&lt;/color&gt;
 - Nạp Năng: Thẻ này nhận 1 điểm Nạp Năng mỗi khi ngươi Tái Cấu Trúc thẻ.
-- Quá Tải: Khi Nạp Năng đạt {0} điểm, xóa toàn bộ điểm và đặt lại Cooldown chiêu Active Skill của Domain này.</t>
+- Quá Tải: Khi Nạp Năng đạt {0} điểm, xóa toàn bộ điểm và đặt lại thời gian hồi chiêu Kỹ Năng Chủ Động của Tổ Tacet này.</t>
         </is>
       </c>
     </row>
@@ -23465,11 +23465,11 @@
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;- When your opponent Reconstructs a card, they gain no Energy.
-- When the Battle Stage starts, increase all your Echoes' STR and CON by {2}.
-- Each time you deploy an Echo, increase one of your Echoes' STR and CON by {1}.&lt;/color&gt;
+          <t>&lt;color=Highlight&gt;- Khi đối thủ Tái Cấu Trúc thẻ, chúng không nhận được Năng Lượng.
+- Khi Giai Đoạn Chiến Đấu bắt đầu, tăng {2} STR và CON cho tất cả Echo của bạn.
+- Mỗi lần triển khai Echo, tăng {1} STR và CON cho một Echo của bạn.&lt;/color&gt;
 - Nạp Năng: Thẻ này nhận 1 điểm Nạp Năng mỗi khi bạn Tái Cấu Trúc thẻ.
-- Quá Tải: Khi Nạp Năng đạt {0} điểm, xóa toàn bộ điểm và đặt lại Cooldown chiêu Active Skill của Domain này.</t>
+- Quá Tải: Khi Nạp Năng đạt {0} điểm, xóa toàn bộ điểm và đặt lại thời gian hồi chiêu Kỹ Năng Chủ Động của Tổ Tacet này.</t>
         </is>
       </c>
     </row>
@@ -23539,12 +23539,12 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;- When your opponent Reconstructs a card, they gain no Energy.
-- When the Battle Stage starts, increase all your Echoes' STR and CON by {2}.
-- When the round starts, you recover {3} HP.
-- Each time you deploy an Echo, increase one of your Echoes' STR and CON by {1}.&lt;/color&gt;
+          <t>&lt;color=Highlight&gt;- Khi đối thủ Tái Cấu Trúc thẻ, chúng không nhận được Năng Lượng.
+- Khi Giai Đoạn Chiến Đấu bắt đầu, tăng {2} STR và CON cho tất cả Echo của bạn.
+- Khi lượt bắt đầu, bạn hồi phục {3} HP.
+- Mỗi lần triển khai Echo, tăng {1} STR và CON cho một Echo của bạn.&lt;/color&gt;
 - Nạp Năng: Thẻ này nhận 1 điểm Nạp Năng mỗi khi bạn Tái Cấu Trúc thẻ.
-- Quá Tải: Khi Nạp Năng đạt {0} điểm, xóa toàn bộ điểm và đặt lại Cooldown chiêu Active Skill của Domain này.</t>
+- Quá Tải: Khi Nạp Năng đạt {0} điểm, xóa toàn bộ điểm và đặt lại thời gian hồi chiêu Kỹ Năng Chủ Động của Tổ Tacet này.</t>
         </is>
       </c>
     </row>
@@ -23612,10 +23612,10 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;- When your opponent Reconstructs a card, they gain no Energy.
-- Each time you deploy an Echo, increase one of your Echoes' STR and CON by {1}.&lt;/color&gt;
-- Nạp Năng: Lá bài này nhận 1 điểm Nạp Năng mỗi khi bạn sử dụng Active Skill của lá bài khác.
-- Quá Tải: Khi Nạp Năng đạt {0} điểm, xóa toàn bộ điểm và đặt lại Cooldown chiêu Active Skill của Domain này.</t>
+          <t>&lt;color=Highlight&gt;- Khi đối thủ Tái Cấu trúc một lá bài, họ không nhận được Năng Lượng.
+- Mỗi khi triển khai một Echo, tăng {1} STR và CON cho một trong các Echo của bạn.&lt;/color&gt;
+- Nạp Năng: Lá bài này nhận 1 điểm Nạp Năng mỗi khi bạn sử dụng Kỹ Năng Chủ Động của lá bài khác.
+- Quá Tải: Khi Nạp Năng đạt {0} điểm, xóa toàn bộ điểm và đặt lại thời gian hồi chiêu Kỹ Năng Chủ Động của Tổ Tacet này.</t>
         </is>
       </c>
     </row>
@@ -23684,11 +23684,11 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;- When your opponent Reconstructs a card, they gain no Energy.
-- When the Battle Stage starts, increase all your Echoes' STR and CON by {2}.
-- Each time you deploy an Echo, increase one of your Echoes' STR and CON by {1}.&lt;/color&gt;
-- Nạp Năng: Thẻ này nhận 1 điểm Nạp Năng mỗi khi bạn sử dụng Active Skill của thẻ khác.
-- Quá Tải: Khi Nạp Năng đạt {0} điểm, xóa toàn bộ điểm và đặt lại Cooldown chiêu Active Skill của Domain này.</t>
+          <t>&lt;color=Highlight&gt;- Khi đối thủ Tái Cấu Trúc thẻ, chúng không nhận được Năng Lượng.
+- Khi Giai Đoạn Chiến Đấu bắt đầu, tăng {2} STR và CON cho tất cả Echo của bạn.
+- Mỗi lần triển khai Echo, tăng {1} STR và CON cho một Echo của bạn.&lt;/color&gt;
+- Nạp Năng: Thẻ này nhận 1 điểm Nạp Năng mỗi khi bạn sử dụng Kỹ Năng Chủ Động của thẻ khác.
+- Quá Tải: Khi Nạp Năng đạt {0} điểm, xóa toàn bộ điểm và đặt lại thời gian hồi chiêu Kỹ Năng Chủ Động của Tổ Tacet này.</t>
         </is>
       </c>
     </row>
@@ -23758,12 +23758,12 @@
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;- When your opponent Reconstructs a card, they gain no Energy.
-- When the Battle Stage starts, increase all your Echoes' STR and CON by {2}.
-- When the round starts, you recover {3} HP.
-- Each time you deploy an Echo, increase one of your Echoes' STR and CON by {1}.&lt;/color&gt;
-- Nạp Năng: Thẻ này nhận 1 điểm Nạp Năng mỗi khi bạn sử dụng Active Skill của thẻ khác.
-- Quá Tải: Khi Nạp Năng đạt {0} điểm, xóa toàn bộ điểm và đặt lại Cooldown chiêu Active Skill của Domain này.</t>
+          <t>&lt;color=Highlight&gt;- Khi đối thủ Tái Cấu Trúc thẻ, chúng không nhận được Năng Lượng.
+- Khi Giai Đoạn Chiến Đấu bắt đầu, tăng {2} STR và CON cho tất cả Echo của bạn.
+- Khi lượt bắt đầu, bạn hồi phục {3} HP.
+- Mỗi lần triển khai Echo, tăng {1} STR và CON cho một Echo của bạn.&lt;/color&gt;
+- Nạp Năng: Thẻ này nhận 1 điểm Nạp Năng mỗi khi bạn sử dụng Kỹ Năng Chủ Động của thẻ khác.
+- Quá Tải: Khi Nạp Năng đạt {0} điểm, xóa toàn bộ điểm và đặt lại thời gian hồi chiêu Kỹ Năng Chủ Động của Tổ Tacet này.</t>
         </is>
       </c>
     </row>
@@ -23831,10 +23831,10 @@
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;- When your opponent Reconstructs a card, they gain no Energy.
-- Each time you deploy an Echo, increase one of your Echoes' STR and CON by {2}.&lt;/color&gt;
-- Nạp Năng: Domain này nhận 1 điểm Nạp Năng mỗi khi bạn kích hoạt hiệu ứng Nạp Năng của lá bài khác.
-- Quá Tải: Khi Nạp Năng đạt {0} điểm, xóa toàn bộ điểm và tăng {1} STR và CON cho một trong các Echoes của bạn.</t>
+          <t>&lt;color=Highlight&gt;- Khi đối thủ Tái Cấu trúc một lá bài, họ không nhận được Năng Lượng.
+- Mỗi khi triển khai một Echo, tăng {2} STR và CON cho một trong các Echo của bạn.&lt;/color&gt;
+- Nạp Năng: Tổ Tacet này nhận 1 điểm Nạp Năng mỗi khi bạn kích hoạt hiệu ứng Nạp Năng của lá bài khác.
+- Quá Tải: Khi Nạp Năng đạt {0} điểm, xóa toàn bộ điểm và tăng {1} STR và CON cho một trong các Echo của bạn.</t>
         </is>
       </c>
     </row>
@@ -23903,11 +23903,11 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;- When your opponent Reconstructs a card, they gain no Energy.
-- When the Battle Stage starts, increase all your Echoes' STR and CON by {3}.
-- Each time you deploy an Echo, increase one of your Echoes' STR and CON by {2}.&lt;/color&gt;
-- Nạp Năng: Domain này nhận 1 điểm Nạp Năng mỗi khi bạn kích hoạt hiệu ứng Nạp Năng của thẻ khác.
-- Quá Tải: Khi Nạp Năng đạt {0} điểm, xóa toàn bộ điểm và tăng {1} STR và CON cho một Echoes của bạn.</t>
+          <t>&lt;color=Highlight&gt;- Khi đối thủ Tái Cấu Trúc thẻ, chúng không nhận được Năng Lượng.
+- Khi Giai Đoạn Chiến Đấu bắt đầu, tăng {3} STR và CON cho tất cả Echo của bạn.
+- Mỗi lần triển khai Echo, tăng {2} STR và CON cho một Echo của bạn.&lt;/color&gt;
+- Nạp Năng: Tổ Tacet này nhận 1 điểm Nạp Năng mỗi khi bạn kích hoạt hiệu ứng Nạp Năng của thẻ khác.
+- Quá Tải: Khi Nạp Năng đạt {0} điểm, xóa toàn bộ điểm và tăng {1} STR và CON cho một Echo của bạn.</t>
         </is>
       </c>
     </row>
@@ -23977,12 +23977,12 @@
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;- When your opponent Reconstructs a card, they gain no Energy.
-- When the Battle Stage starts, increase all your Echoes' STR and CON by {3}.
-- When the round starts, you recover {4} HP.
-- Each time you deploy an Echo, increase one of your Echoes' STR and CON by {2}.&lt;/color&gt;
-- Nạp Năng: Domain này nhận 1 điểm Nạp Năng mỗi khi ngươi kích hoạt hiệu ứng Nạp Năng của thẻ khác.
-- Quá Tải: Khi Nạp Năng đạt {0} điểm, xóa toàn bộ điểm và tăng chỉ số Sức Mạnh và Thể Trạng của một Resonator của ngươi thêm {1}.</t>
+          <t>&lt;color=Highlight&gt;- Khi đối thủ Tái Cấu Trúc thẻ, họ không nhận được Năng Lượng.
+- Khi Giai Đoạn Chiến Đấu bắt đầu, tăng toàn bộ chỉ số Sức Mạnh và Thể Trạng của Cộng Hưởng Giả của ngươi thêm {3}.
+- Khi hiệp bắt đầu, ngươi hồi {4} HP.
+- Mỗi lần triển khai Cộng Hưởng Giả, tăng chỉ số Sức Mạnh và Thể Trạng của một Cộng Hưởng Giả của ngươi thêm {2}.&lt;/color&gt;
+- Nạp Năng: Tổ Tacet này nhận 1 điểm Nạp Năng mỗi khi ngươi kích hoạt hiệu ứng Nạp Năng của thẻ khác.
+- Quá Tải: Khi Nạp Năng đạt {0} điểm, xóa toàn bộ điểm và tăng chỉ số Sức Mạnh và Thể Trạng của một Cộng Hưởng Giả của ngươi thêm {1}.</t>
         </is>
       </c>
     </row>
@@ -24047,7 +24047,7 @@
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>Hôm nay không thể nhận thêm EXP Modding bằng cách đánh bại kẻ địch</t>
+          <t>Hôm nay không thể nhận thêm Điểm Kinh Nghiệm Modding bằng cách đánh bại kẻ địch</t>
         </is>
       </c>
     </row>
@@ -24177,7 +24177,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>Hồi chiêu Boost</t>
+          <t>Thời gian hồi Tăng cường</t>
         </is>
       </c>
     </row>
@@ -24242,7 +24242,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>Cooldown Khiên Lực</t>
+          <t>Hồi Chiêu Khiên Lực</t>
         </is>
       </c>
     </row>
@@ -24437,7 +24437,7 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>Khi chịu ảnh hưởng của Void Storm, Resonators trong đội nhận ít sát thương hơn.</t>
+          <t>Khi chịu ảnh hưởng của Bão Hư Không, Resonator trong đội nhận ít DMG hơn.</t>
         </is>
       </c>
     </row>
@@ -24502,7 +24502,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>Sau khi giải phóng Ram Dynamics, Crit. Rate của Resonators trong đội tăng lên.</t>
+          <t>Sau khi giải phóng Ram Dynamics, Crit. Rate của các Resonator trong đội tăng lên.</t>
         </is>
       </c>
     </row>
@@ -24567,7 +24567,7 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>Chiến Thuật Chủ Động ({0}): Increase sức mạnh và thể chất của Echoes lên {1} trong một lượt.</t>
+          <t>Chiến Thuật Chủ Động ({0}): Tăng sức mạnh và thể chất của Echo lên {1} trong một lượt.</t>
         </is>
       </c>
     </row>
@@ -24632,7 +24632,7 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>Chiến Thuật Chủ Động ({0}): Gây {1} sát thương lên đối thủ.</t>
+          <t>Chiến Thuật Chủ Động ({0}): Gây {1} DMG lên đối thủ.</t>
         </is>
       </c>
     </row>
@@ -24697,7 +24697,7 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>Passive Tactic: Mỗi lần Triển khai Nhanh, bạn nhận được {0} HP.</t>
+          <t>Thụ Động Chiến Thuật: Mỗi lần Triển Khai Nhanh, bạn nhận được {0} HP.</t>
         </is>
       </c>
     </row>
@@ -24762,7 +24762,7 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>Chiến Thuật Thụ Động: Increase Sát Thương của Echoes thêm {0} khi bắt đầu Battle Stage trong một hiệp.</t>
+          <t>Chiến Thuật Thụ Động: Tăng Sát Thương của Echoes thêm {0} khi bắt đầu Giai Đoạn Chiến Đấu trong một hiệp.</t>
         </is>
       </c>
     </row>
@@ -24827,7 +24827,7 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>Increase STR và CON của một trong các Echoes của bạn lên {0} trong 1 hiệp.</t>
+          <t>Tăng STR và CON của một trong các Echo của bạn lên {0} trong 1 hiệp.</t>
         </is>
       </c>
     </row>
@@ -24892,7 +24892,7 @@
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>Increase STR và CON của một trong các Echoes của bạn lên {0} trong 1 hiệp.</t>
+          <t>Tăng STR và CON của một trong các Echo của bạn lên {0} trong 1 hiệp.</t>
         </is>
       </c>
     </row>
@@ -24957,7 +24957,7 @@
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>Increase STR và CON của một trong các Echoes của bạn lên {0} trong 1 hiệp.</t>
+          <t>Tăng STR và CON của một trong các Echo của bạn lên {0} trong 1 hiệp.</t>
         </is>
       </c>
     </row>
@@ -25022,7 +25022,7 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>Increase STR và CON của một trong các Echoes của bạn lên {0} trong 1 hiệp.</t>
+          <t>Tăng STR và CON của một trong các Echo của bạn lên {0} trong 1 hiệp.</t>
         </is>
       </c>
     </row>
@@ -25087,7 +25087,7 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>Increase STR và CON của một trong các Echoes của bạn lên {0} trong 1 hiệp.</t>
+          <t>Tăng STR và CON của một trong các Echo của bạn lên {0} trong 1 hiệp.</t>
         </is>
       </c>
     </row>
@@ -25152,7 +25152,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>Increase STR và CON của một trong các Echoes của bạn lên {0} trong 1 hiệp.</t>
+          <t>Tăng STR và CON của một trong các Echo của bạn lên {0} trong 1 hiệp.</t>
         </is>
       </c>
     </row>
@@ -25217,7 +25217,7 @@
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t>Increase STR và CON của một trong các Echoes của bạn lên {0} trong 1 hiệp.</t>
+          <t>Tăng STR và CON của một trong các Echo của bạn lên {0} trong 1 hiệp.</t>
         </is>
       </c>
     </row>
@@ -25282,7 +25282,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>Kích hoạt Resonance Nexus tại Startorch Academy trong Nhiệm Vụ Chính "What Burns Beneath Frostlands" để mở khóa.</t>
+          <t>Kích hoạt Mạch Cộng hưởng tại Học viện Startorch trong Nhiệm vụ Chính "Điều Gì Nung Nấu Dưới Lãnh Nguyên" để mở khóa</t>
         </is>
       </c>
     </row>
@@ -25347,7 +25347,7 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>&lt;color=#e4c69b&gt;Rally&lt;/color&gt; - Khi kích hoạt, mỗi lần Resonator này sử dụng Active Skill, Triệu Hồi nhanh một Resonator có kỹ năng Rally chưa kích hoạt từ bộ bài vào Vùng Triển khai và Tái Tạo Resonator này. Nếu Resonator có nhiều kỹ năng Rally hoặc Rally Cường Hóa, chỉ kỹ năng đầu tiên được kích hoạt mới có hiệu lực.</t>
+          <t>&lt;color=#e4c69b&gt;Tập Hợp&lt;/color&gt; - Khi kích hoạt, mỗi lần Cộng Hưởng Giả này sử dụng Kỹ Năng Chủ Động, Triệu Hồi nhanh một Cộng Hưởng Giả có kỹ năng Tập Hợp chưa kích hoạt từ bộ bài vào Vùng Triển Khai và Tái Tạo Cộng Hưởng Giả này. Nếu Cộng Hưởng Giả có nhiều kỹ năng Tập Hợp hoặc Tập Hợp Cường Hóa, chỉ kỹ năng đầu tiên được kích hoạt mới có hiệu lực.</t>
         </is>
       </c>
     </row>
@@ -25412,7 +25412,7 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>&lt;color=#e4c69b&gt;Enhanced Rally&lt;/color&gt; - Khi kích hoạt, mỗi lần Tacet Discord này sử dụng Active Skill, Triển khai Nhanh một Tacet Discord có Rally hoặc Enhanced Rally chưa kích hoạt từ bộ bài lên Vùng Triển khai và Tái cấu trúc Tacet Discord này. Nếu Tacet Discord có nhiều kỹ năng Rally hoặc Enhanced Rally, chỉ kỹ năng đầu tiên được kích hoạt mới có thể kích hoạt hiệu ứng này.</t>
+          <t>&lt;color=#e4c69b&gt;Enhanced Rally&lt;/color&gt; - Khi kích hoạt, mỗi lần Tacet Discord này sử dụng Kỹ Năng Chủ Động, Triển Khai Nhanh một Tacet Discord có Rally hoặc Enhanced Rally chưa kích hoạt từ bộ bài lên Vùng Triển Khai và Tái cấu trúc Tacet Discord này. Nếu Tacet Discord có nhiều kỹ năng Rally hoặc Enhanced Rally, chỉ kỹ năng đầu tiên được kích hoạt mới có thể kích hoạt hiệu ứng này.</t>
         </is>
       </c>
     </row>
@@ -25477,7 +25477,7 @@
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>&lt;color=#e4c69b&gt;Rally&lt;/color&gt; &lt;color=#fb6464&gt;(Unactivated)&lt;/color&gt; - Khi kích hoạt, mỗi lần Resonator này sử dụng Active Skill, Triệu Hồi nhanh một Resonator có kỹ năng Rally chưa kích hoạt từ bộ bài vào Vùng Triển khai và Tái Tạo Resonator này. Nếu Resonator có nhiều kỹ năng Rally hoặc Rally Cường Hóa, chỉ kỹ năng đầu tiên được kích hoạt mới có hiệu lực.</t>
+          <t>&lt;color=#e4c69b&gt;Tập Hợp&lt;/color&gt; &lt;color=#fb6464&gt;(Chưa kích hoạt)&lt;/color&gt; - Khi kích hoạt, mỗi lần Cộng Hưởng Giả này sử dụng Kỹ Năng Chủ Động, Triệu Hồi nhanh một Cộng Hưởng Giả có kỹ năng Tập Hợp chưa kích hoạt từ bộ bài vào Vùng Triển Khai và Tái Tạo Cộng Hưởng Giả này. Nếu Cộng Hưởng Giả có nhiều kỹ năng Tập Hợp hoặc Tập Hợp Cường Hóa, chỉ kỹ năng đầu tiên được kích hoạt mới có hiệu lực.</t>
         </is>
       </c>
     </row>
@@ -25542,7 +25542,7 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>&lt;color=#e4c69b&gt;Enhanced Rally&lt;/color&gt; &lt;color=#fb6464&gt;(Unactivated)&lt;/color&gt; - Khi kích hoạt, mỗi lần Tacet Discord này sử dụng Active Skill, Triển khai Nhanh một Tacet Discord có Rally hoặc Enhanced Rally chưa kích hoạt từ bộ bài lên Vùng Triển khai và Tái cấu trúc Tacet Discord này. Nếu Tacet Discord có nhiều kỹ năng Rally hoặc Enhanced Rally, chỉ kỹ năng đầu tiên được kích hoạt mới có thể kích hoạt hiệu ứng này.</t>
+          <t>&lt;color=#e4c69b&gt;Enhanced Rally&lt;/color&gt; &lt;color=#fb6464&gt;(Chưa kích hoạt)&lt;/color&gt; - Khi kích hoạt, mỗi lần Tacet Discord này sử dụng Kỹ Năng Chủ Động, Triển Khai Nhanh một Tacet Discord có Rally hoặc Enhanced Rally chưa kích hoạt từ bộ bài lên Vùng Triển Khai và Tái cấu trúc Tacet Discord này. Nếu Tacet Discord có nhiều kỹ năng Rally hoặc Enhanced Rally, chỉ kỹ năng đầu tiên được kích hoạt mới có thể kích hoạt hiệu ứng này.</t>
         </is>
       </c>
     </row>
@@ -25672,7 +25672,7 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>Đạt Cấp Liên Minh 8 và kích hoạt Trạm Resonance Học Viện Startorch trong Nhiệm Vụ Chính "Lửa Dưới Băng Giá".</t>
+          <t>Đạt Cấp Liên Minh 8 và kích hoạt Trạm Cộng Hưởng Học Viện Startorch trong Nhiệm Vụ Chính "Lửa Dưới Băng Giá".</t>
         </is>
       </c>
     </row>
@@ -25737,7 +25737,7 @@
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>Kích hoạt Resonance Nexus Học Viện Startorch trong Nhiệm Vụ Chính "Điều Gì Nung Nấu Dưới Lãnh Nguyên."</t>
+          <t>Kích hoạt Mạng Lưới Cộng Hưởng Học Viện Startorch trong Nhiệm Vụ Chính "Điều Gì Nung Nấu Dưới Lãnh Nguyên."</t>
         </is>
       </c>
     </row>
@@ -25932,7 +25932,7 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>Trong Giai đoạn Triển khai và Giai đoạn Chiến đấu, mỗi lần mất HP, Resonator chỉ mất ít hơn 1 HP.</t>
+          <t>Trong Giai đoạn Triển khai và Giai đoạn Chiến đấu, mỗi lần mất HP, Cộng Hưởng Giả chỉ mất ít hơn 1 HP.</t>
         </is>
       </c>
     </row>
@@ -25997,7 +25997,7 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>Mỗi lần Resonator chịu sát thương sẽ được giảm đi 5.</t>
+          <t>Mỗi lần Cộng Hưởng Giả chịu DMG sẽ được giảm đi 5.</t>
         </is>
       </c>
     </row>
@@ -26129,9 +26129,9 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>Mỗi khi đấu thủ triển khai Echoes, Echoes đó sẽ nhận được Kháng Phá và Resilience.
-Đấu thủ sẽ mất ít hơn 1 HP mỗi khi bị trừ HP trong Giai Đoạn Triển Khai và Battle Stage.
-Cuối mỗi hiệp đấu, các Echoes của đấu thủ sẽ nhận được X điểm Sức Mạnh và Thể Chất, với X là số hiệp hiện tại.</t>
+          <t>Mỗi khi đấu thủ triển khai Echo, Echo đó sẽ nhận được Kháng Phá và Kiên Cường.
+Đấu thủ sẽ mất ít hơn 1 HP mỗi khi bị trừ HP trong Giai Đoạn Triển Khai và Giai Đoạn Chiến Đấu.
+Cuối mỗi hiệp đấu, các Echo của đấu thủ sẽ nhận được X điểm Sức Mạnh và Thể Chất, với X là số hiệp hiện tại.</t>
         </is>
       </c>
     </row>
@@ -26204,11 +26204,11 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>["Hồ sơ do &lt;te href=851071&gt;Spacetrek Collective&lt;/te&gt; lưu trữ: Hồ sơ học viên &lt;te href=851069&gt;Startorch Academy&lt;/te&gt;]
-[Report Khảo sát Forte RA2906-G]
-Name học viên: Lynae
+          <t>["Hồ sơ do &lt;te href=851071&gt;Tập Đoàn Spacetrek&lt;/te&gt; lưu trữ: Hồ sơ học viên &lt;te href=851069&gt;Học viện Startorch&lt;/te&gt;]
+[Báo cáo Khảo sát Forte RA2906-G]
+Tên học viên: Lynae
 Kết quả Đồng Bộ Hóa: Âm tính
-Overview Forte: Kiểm tra cho thấy &lt;te href=850067&gt;Rabelle's Curve&lt;/te&gt; có dạng sóng tuần hoàn rõ rệt. Do đó, học viên được xếp loại là &lt;te href=850068&gt;Congenital Resonator&lt;/te&gt;. &lt;te href=850072&gt;Tacet Mark&lt;/te&gt; của cô nằm ở mặt sau đùi trái.
+Tổng quan Forte: Kiểm tra cho thấy &lt;te href=850067&gt;Đường cong Rabelle&lt;/te&gt; có dạng sóng tuần hoàn rõ rệt. Do đó, học viên được xếp loại là &lt;te href=850068&gt;Resonator Bẩm Sinh&lt;/te&gt;. &lt;te href=850072&gt;Dấu Tacet&lt;/te&gt; của cô nằm ở mặt sau đùi trái.
 Theo hồ sơ cá nhân trước nhập học và lời khai của học viên, cô có độ nhạy cảm bẩm sinh với ánh sáng khả kiến và khả năng thiên bẩm với các màu sắc phức tạp, hiếm gặp. Bằng cách sử dụng “mực sắc tố”, cô có thể thay đổi bước sóng hoặc tần số ánh sáng khả kiến trong một khu vực giới hạn, “pha trộn” màu sắc theo ý muốn. Những sắc tố này chủ yếu được dùng trong sơn phun. Kiểm tra cho thấy chúng khác biệt so với vật liệu công nghiệp, hoạt động giống như các hình chiếu quang học phi vật lý.
 Ngoài ra, các báo cáo từ nhiều học viên khác cho thấy đối tượng có thể thay đổi bước sóng ánh sáng khả kiến gần đó để gây nhiễu các thiết bị dò tần số, tạo hiệu ứng tương tự “tàng hình” cả về mặt thị giác lẫn nhận thức tần số.
 &lt;i&gt;“Dù sao cũng nhắc cô ấy đừng dùng khả năng đó để trốn học nữa.”&lt;/i&gt;
@@ -26292,15 +26292,15 @@
       <c r="M384" t="inlineStr">
         <is>
           <t>["Báo Cáo Đánh Giá Sức Khỏe và Năng Lực Định Kỳ - Nhà Nghiên Cứu Cao Cấp &lt;te href=851071&gt;Spacetrek Collective&lt;/te&gt;"]
-Name: Mornye
+Tên: Mornye
 Đơn vị trực thuộc: Spacetrek Collective - Viện Nghiên Cứu và Bộ Phận Kỹ Thuật Exostrider
 1. Đánh Giá Năng Lực Đặc Biệt
 1.1 Phân Loại Cơ Bản
-Đối tượng được phân loại là &lt;te href=850070&gt;Natural Resonator&lt;/te&gt;, với &lt;te href=850072&gt;Tacet Mark&lt;/te&gt; nằm ở mặt bên đùi trái.
+Đối tượng được phân loại là &lt;te href=850070&gt;Resonator Tự Nhiên&lt;/te&gt;, với &lt;te href=850072&gt;Dấu Tacet&lt;/te&gt; nằm ở mặt bên đùi trái.
 1.2 Thông Số và Đặc Điểm
 - Phạm Vi Hiệu Quả: Khoảng 20 mét. Trong bán kính này, đối tượng thể hiện khả năng điều khiển trực tiếp và chi tiết các thực thể cơ khí có cấu trúc phức tạp. Độ chính xác điều khiển duy trì ổn định trong toàn bộ phạm vi hiệu quả, không ghi nhận suy giảm tín hiệu.
 - Điều Kiện Kích Hoạt: Khả năng đặc biệt yêu cầu phân tích cấu trúc cơ khí bên trong của mục tiêu. Không thể kích hoạt đối với vật thể có cấu trúc bên trong chưa xác định.
-&lt;i&gt;"Khoan, ý họ là sao…? Tôi chưa bao giờ thấy Giáo sư Mornye thất bại trong việc kiểm soát máy móc!"&lt;/i&gt;
+&lt;i&gt;"Đợi đã, ý họ là sao…? Tôi chưa bao giờ thấy Giáo sư Mornye thất bại trong việc kiểm soát máy móc!"&lt;/i&gt;
 2. Tổng Quan Tình Trạng Thể Chất
 2.1 Chẩn Đoán
 Đối tượng mắc chứng giảm sản bẩm sinh đám rối thần kinh thắt lưng-cùng, dẫn đến mất chức năng vận động vĩnh viễn từ vùng xương cụt trở xuống và không có khả năng di chuyển tự chủ.
@@ -26450,13 +26450,13 @@
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>Trong hệ thống hành chính của &lt;te href=851069&gt;Startorch Academy&lt;/te&gt;, hồ sơ vắng mặt của Lynae đọc như một cuốn du ký kỳ ảo đầy màu sắc hơn là một biên bản kỷ luật.
+          <t>Trong hệ thống hành chính của &lt;te href=851069&gt;Học viện Startorch&lt;/te&gt;, hồ sơ vắng mặt của Lynae đọc như một cuốn du ký kỳ ảo đầy màu sắc hơn là một biên bản kỷ luật.
 Trong khi các bạn cùng lớp ngồi nghe giảng bài Lịch sử Văn hóa Thế giới của Giáo sư Mauclair trong giảng đường, Lynae lại đang ở cách đó vài kilomet, ngồi trên cây cẩn thận gia cố tổ của một đàn Kronapuff mới nở. Khi các bạn khác luyện tập chiến thuật trên sân tập, cô lại có mặt tại Kho Lưu trữ Spacetrek, giúp một sinh viên Khoa Năng lượng đang hoảng loạn khôi phục dữ liệu tốt nghiệp quan trọng từ đống file bị hỏng.
 Đôi bàn tay từng được rèn luyện để cầm vũ khí và phá vỡ hệ thống an ninh giờ đây lại cầm bình xịt với sự chính xác và dịu dàng đến bất ngờ. Lynae đơn giản là không thể ngồi yên. Sự tò mò kéo cô từ góc này sang góc khác của Học viện, và lý do trốn học của cô luôn đầy sáng tạo.
 "Em đang giúp một anh chị ngăn dự án tốt nghiệp của họ... bỏ trốn."
 "Em điều chỉnh lại thuật toán nêm gia vị cho droid căng tin. Có thể em đã vô tình kích hoạt một cuộc đình công toàn hệ thống."
 "Những Rimewisp trong buồng mô phỏng đang có dao động phổ bất thường. Rõ ràng là em phải ghi lại chứ!"
-Ban đầu, cô Voss thấy mệt mỏi với chuyện này. Nhưng mọi thứ bắt đầu thay đổi. Sự thay đổi đến từ lá thư khen chính thức của Khoa Kỹ thuật, ghi nhận công lao của Lynae trong việc bảo vệ toàn bộ thiết bị khảo sát vùng băng giá trước một cơn &lt;te href=851070&gt;Void Storm&lt;/te&gt;. Sự thay đổi đến khi hộp thư góp ý bắt đầu tràn ngập những lời cảm ơn gửi đến một "tình nguyện viên" ẩn danh. Sự thay đổi đến khi Giáo sư Mauclair, trong một cuộc họp Khoa Năng lượng, hào hứng trình bày một bộ dữ liệu phổ rõ ràng chưa từng có từ một "điểm quan sát đặc biệt", và ghi chú: "Do một sinh viên giấu tên cung cấp. Đề nghị đưa vào giáo trình."
+Ban đầu, cô Voss thấy mệt mỏi với chuyện này. Nhưng mọi thứ bắt đầu thay đổi. Sự thay đổi đến từ lá thư khen chính thức của Khoa Kỹ thuật, ghi nhận công lao của Lynae trong việc bảo vệ toàn bộ thiết bị khảo sát vùng băng giá trước một cơn &lt;te href=851070&gt;Bão Hư Không&lt;/te&gt;. Sự thay đổi đến khi hộp thư góp ý bắt đầu tràn ngập những lời cảm ơn gửi đến một "tình nguyện viên" ẩn danh. Sự thay đổi đến khi Giáo sư Mauclair, trong một cuộc họp Khoa Năng lượng, hào hứng trình bày một bộ dữ liệu phổ rõ ràng chưa từng có từ một "điểm quan sát đặc biệt", và ghi chú: "Do một sinh viên giấu tên cung cấp. Đề nghị đưa vào giáo trình."
 Trước hồ sơ dài dòng, khó hiểu nhưng không thể phủ nhận là xuất sắc của Lynae, cô Voss chỉ còn biết thở dài.
 Cô gái này chẳng bao giờ có mặt trên lớp, nhưng sự hiện diện của cô lại len lỏi vào mọi ngóc ngách của Học viện. Dường như cô đang bảo vệ nơi mà giờ đây cô gọi là "nhà", theo cách riêng, không theo quy tắc nào cả.
 "…Dù sao thì em vẫn phải viết bản kiểm điểm đấy."
@@ -26638,19 +26638,19 @@
       <c r="M388" t="inlineStr">
         <is>
           <t>Lúc đầu, cô chỉ coi chúng là những email lừa đảo.
-Chúng xuất hiện bất thình lình. Sáng sớm, giữa giờ học, đêm khuya, hay thậm chí ngay giữa lúc cười đùa cùng bạn bè. Những dòng mã đỏ lòe, khó hiểu đột nhiên hiện lên trên Terminal của cô. Nhìn thấy chúng giống như bị một mũi kim sắc nhọn đâm xuyên ngực. Nó luồn lách qua tim, qua từng mạch máu, thậm chí cả dòng máu trong người cô.
+Chúng xuất hiện bất thình lình. Sáng sớm, giữa giờ học, đêm khuya, hay thậm chí ngay giữa lúc cười đùa cùng bạn bè. Những dòng mã đỏ lòe, khó hiểu đột nhiên hiện lên trên Thiết bị đầu cuối của cô. Nhìn thấy chúng giống như bị một mũi kim sắc nhọn đâm xuyên ngực. Nó luồn lách qua tim, qua từng mạch máu, thậm chí cả dòng máu trong người cô.
 Mất thời gian để giải mã chúng. Nhưng khi cuối cùng cũng khôi phục được thông điệp gốc, một cơn lạnh buốt chạy dọc sống lưng.
-The Fractsidus.
+Fractsidus.
 Có lẽ từ lúc cầm lá thư nhập học, cô đã biết, nhưng vẫn níu giữ một tia hy vọng mong manh. Cô cố không nghĩ quá nhiều, để bản thân chìm đắm trong cuộc sống học đường đẹp đẽ hơn mọi điều cô từng dám mơ.
 — Cho đến khi "nhiệm vụ" ấy ập đến.
 "Xâm nhập hệ thống Viện. Truy xuất và thay đổi thông số của Máy dò Hyvatia."
-Cô biết ý nghĩa của New Solar Ceremony đối với cả &lt;te href=851071&gt;Spacetrek Collective&lt;/te&gt; lẫn &lt;te href=260004&gt;Lahai-Roi&lt;/te&gt;, và tầm quan trọng của Máy dò Hyvatia trong sự kiện đó. Một âm mưu khổng lồ đang len lỏi trong bóng tối của Lahai-Roi. Trong khoảnh khắc ấy, Lynae hiểu rõ một cách lạnh người: lựa chọn của cô có thể đẩy Lahai-Roi vào nguy hiểm. Cô không tin một kẻ đánh thuê bỏ trốn như mình có thể đe dọa một tổ chức lớn như The Fractsidus. Nhưng ý nghĩ ấy cứ quay cuồng trong đầu, không chịu buông tha.
-&lt;te href=851069&gt;Startorch Academy&lt;/te&gt;, "thiên đường" dưới vùng băng giá, đã trở thành ngôi nhà của cô. Cô còn có thể nhắm mắt làm ngơ, giả vờ sống cuộc sống "học đường" này với lương tâm thanh thản được bao lâu nữa?
+Cô biết ý nghĩa của Lễ Hội Mặt Trời Mới đối với cả &lt;te href=851071&gt;Spacetrek Collective&lt;/te&gt; lẫn &lt;te href=260004&gt;Lahai-Roi&lt;/te&gt;, và tầm quan trọng của Máy dò Hyvatia trong sự kiện đó. Một âm mưu khổng lồ đang len lỏi trong bóng tối của Lahai-Roi. Trong khoảnh khắc ấy, Lynae hiểu rõ một cách lạnh người: lựa chọn của cô có thể đẩy Lahai-Roi vào nguy hiểm. Cô không tin một kẻ đánh thuê bỏ trốn như mình có thể đe dọa một tổ chức lớn như Fractsidus. Nhưng ý nghĩ ấy cứ quay cuồng trong đầu, không chịu buông tha.
+&lt;te href=851069&gt;Học viện Startorch&lt;/te&gt;, "thiên đường" dưới vùng băng giá, đã trở thành ngôi nhà của cô. Cô còn có thể nhắm mắt làm ngơ, giả vờ sống cuộc sống "học đường" này với lương tâm thanh thản được bao lâu nữa?
 Nhận ra không thể trốn mãi, cô quyết định. Đã đến lúc kết thúc.
 Bước một: cắt đứt vai trò "người trong" của họ.
 Ngón tay cô run run khi nhấn gửi. Đó là tin nhắn đầu tiên cô viết với tư cách nội gián của Fractsidus:
 "Đã lấy được dữ liệu mục tiêu. Giao hàng trực tiếp."
-Tọa độ đính kèm chỉ đến vùng ngoại ô nơi sinh sống của Voidworm. Sau tiếng súng nổ, &lt;te href=851070&gt;Void Storm&lt;/te&gt; sẽ xóa sạch mọi dấu vết còn lại.
+Tọa độ đính kèm chỉ đến vùng ngoại ô nơi sinh sống của Voidworm. Sau tiếng súng nổ, &lt;te href=851070&gt;Cơn Bão Hư Không&lt;/te&gt; sẽ xóa sạch mọi dấu vết còn lại.
 Tin nhắn đã gửi, cô tựa vào chiếc mô-tô và ngước nhìn bầu trời Lahai-Roi.
 Gió đã đổi chiều. Và lần này, không còn đường lui.</t>
         </is>
@@ -26736,24 +26736,24 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>Đáng lẽ chỉ là một nhiệm vụ khác. Xám xịt, đen tối, nhợt nhạt như thạch cao. Chỉ là một nhiệm vụ tiêu diệt vài cá nhân mà Liên bang New gắn mác "mối đe dọa tiềm tàng."
+          <t>Đáng lẽ chỉ là một nhiệm vụ khác. Xám xịt, đen tối, nhợt nhạt như thạch cao. Chỉ là một nhiệm vụ tiêu diệt vài cá nhân mà Liên bang Mới gắn mác "mối đe dọa tiềm tàng."
 Tại sao những người chưa hề đe dọa ai vẫn phải biến mất, đó chưa bao giờ là câu hỏi cô được phép hỏi.
 Cô nhìn mục tiêu chạy trốn trong hoảng loạn qua con hẻm tối. Cô không phải thợ săn duy nhất trong bóng đêm. Những đường ngắm màu đỏ mảnh mai đan xen trong không khí, hội tụ, khóa chặt, rồi mang đến một cái kết im lặng, tuyệt đối.
 Một tiếng thở gấp, nghẹn trong tiếng tĩnh điện vọng vào tai nghe của cô.
-"Đừng lo... Ta sẽ đến &lt;te href=260004&gt;Lahai-Roi&lt;/te&gt; đúng hẹn... &lt;te href=851069&gt;Startorch Academy&lt;/te&gt;..."
-"Ta sẽ hoàn thành... sứ mệnh của... Grand Architect..."
+"Đừng lo... Ta sẽ đến &lt;te href=260004&gt;Lahai-Roi&lt;/te&gt; đúng hẹn... &lt;te href=851069&gt;Học viện Startorch&lt;/te&gt;..."
+"Ta sẽ hoàn thành... sứ mệnh của... Kiến Trúc Sư Vĩ Đại..."
 Kháng cự vô ích.
 Khi Lynae tiến đến gần, sinh khí cuối cùng đã tắt lịm.
 Đáng lẽ chỉ là một nhiệm vụ bình thường.
 Nhưng lần này, có điều gì đó khác lạ. Một vệt vàng trên lá thư nhập học rơi xuống thu hút ánh nhìn cô, như một vết sơn loang trên nền thạch cao trắng xóa, như một tia sáng lọt qua khe nứt. Cô không thể rời mắt.
 "Lynae"—cái tên được in nổi trên tờ giấy như số phận đang giễu cợt, nửa thật nửa giả. Cô cúi xuống, phủi đi bụi bẩn và vết máu. Mái tóc đen của cô bắt lấy ánh vàng phản chiếu, khơi dậy điều gì đó trong lồng ngực cô mà bao năm làm lính đánh thuê vô cảm chưa từng đánh thức nổi: khát khao tự do.
-"Em là Lynae đến từ Liên bang New phải không?"
+"Em là Lynae đến từ Liên bang Mới phải không?"
 Trước câu hỏi của giáo viên, cô cảm thấy thoáng chút tội lỗi. Cô cuốn một lọn tóc mới nhuộm—từng là màu nâu sẫm, giờ là vàng nhạt dịu dàng, dù vẫn giữ lại vài lọn màu gốc—và gật đầu, nở nụ cười tươi nhất.
-"Yes."
-"Em không cần lo lắng. Chúng tôi biết Liên bang New đối xử với Resonators như thế nào... nhưng ở Lahai-Roi, em hoàn toàn tự do. Mọi cơ hội và tri thức đều mở ra cho tất cả mọi người."
+"Vâng."
+"Em không cần lo lắng. Chúng tôi biết Liên bang Mới đối xử với Resonator như thế nào... nhưng ở Lahai-Roi, em hoàn toàn tự do. Mọi cơ hội và tri thức đều mở ra cho tất cả mọi người."
 Cô im lặng khi giáo viên lật qua hồ sơ học sinh mà cô đã điền qua loa. Cô từng khoác nhiều vỏ bọc cho các nhiệm vụ, nhưng chưa lần nào khiến cô căng thẳng như thế này.
 "Hm? Mục 'Sở thích' để trống à..."
-Không ổn rồi. Lẽ ra cô nên viết gì đó... Vẽ graffiti chẳng hạn? Cô thích để lại vài Dodget vẽ sau nhiệm vụ, thói quen học từ một bộ phim, nhưng lính đánh thuê không được để lại dấu vết, nên cô luôn xóa sạch. Hay xe máy? Chỉ có tiếng gió gào thét bên tai khi lao vút trên đường thẳng, để lại vệt màu rực rỡ. Liệu đó có gọi là "sở thích" không?
+Không ổn rồi. Lẽ ra cô nên viết gì đó... Vẽ graffiti chẳng hạn? Cô thích để lại vài nét vẽ sau nhiệm vụ, thói quen học từ một bộ phim, nhưng lính đánh thuê không được để lại dấu vết, nên cô luôn xóa sạch. Hay xe máy? Chỉ có tiếng gió gào thét bên tai khi lao vút trên đường thẳng, để lại vệt màu rực rỡ. Liệu đó có gọi là "sở thích" không?
 "Không sao đâu." Nhìn cô chìm vào suy nghĩ, người phụ nữ tóc dài đội mũ đóng hồ sơ lại. Cô mỉm cười và đặt một tấm thẻ học sinh mới tinh vào lòng bàn tay cô.
 "Em có thể từ từ khám phá chúng ở đây."</t>
         </is>
@@ -26835,13 +26835,13 @@
 Giờ học sáng đầu tiên vẫn khiến cô gật gù dù đã cố gắng hết sức, dù cô đã thành thạo việc giả vờ chăm chú ghi chép ngay trước khi ánh mắt sắc bén của giáo viên kịp phát hiện. Cô đã từng học chính lớp này, viết chính những dòng ghi chú ấy… Vậy nên, cơn buồn ngủ của cô hoàn toàn có lý do.
 Những giờ giải lao vẫn kín đặc: giúp đàn anh khoa Kỹ thuật thử nghiệm động cơ mới, tạo hiệu ứng chuyển cảnh "hoành tráng" cho sân khấu Câu lạc bộ Kịch Nghệ, và vâng, vẫn phải viết mấy bản báo cáo cảm nghĩ…
 Nhưng khác biệt nằm ở chỗ, giờ cô được kéo theo người từng là "hậu bối" của mình cùng xếp hàng ở căng-tin, thử mấy món "vị mới" cùng nhau.
-Kể từ khi nhập học, {Male=cậu ấy;Female=cô ấy} còn bận rộn hơn trước. Đây là một trong những khoảnh khắc hiếm hoi họ có được bên nhau. Giờ đây, hai người ngồi sát vai trên chiếc ghế ở Quảng trường Stargram, cùng chia nhau một lon "Vị Ngạc Nhiên Đóng Hộp" mà Lynae nhất định phải mua.
+Kể từ khi nhập học, {Male=him;Female=her} còn bận rộn hơn trước. Đây là một trong những khoảnh khắc hiếm hoi họ có được bên nhau. Giờ đây, hai người ngồi sát vai trên chiếc ghế ở Quảng trường Stargram, cùng chia nhau một lon "Vị Ngạc Nhiên Đóng Hộp" mà Lynae nhất định phải mua.
 Trước kia, sự im lặng khiến cô lo lắng. Cô sẽ vội vàng lấp đầy nó bằng công việc hoặc lời nói. Nhưng giờ, nó lại ấm áp. Thật dễ chịu.
-Lynae quay sang nhìn gương mặt điềm tĩnh bên cạnh, chỉ để thấy đôi mắt vàng ấy giãn ra sau một hương vị… quá đỗi bất ngờ. Cô bật cười. Điều đó khiến cô nhớ lại lần đầu họ gặp nhau—{Male=cậu ấy;Female=cô ấy} đã có biểu cảm y hệt như vậy.
-Hồi đó, Lynae không biết liệu {PlayerName}, người từ trên trời rơi thẳng xuống, có chứng kiến khoảnh khắc cô thực hiện kế hoạch của mình hay không. Cô nhìn {Male=cậu ấy;Female=cô ấy} đứng dậy từ mặt đất, ngón tay cô bản năng siết chặt cò súng. Nhưng sự lạnh lùng trong ánh mắt cô biến mất ngay khi thấy một lá thư nhập học rơi xuống giữa họ. Trong khoảnh khắc ấy, cô nhận ra—
+Lynae quay sang nhìn gương mặt điềm tĩnh bên cạnh, chỉ để thấy đôi mắt vàng ấy giãn ra sau một hương vị… quá đỗi bất ngờ. Cô bật cười. Điều đó khiến cô nhớ lại lần đầu họ gặp nhau—{Male=he;Female=she} đã có biểu cảm y hệt như vậy.
+Hồi đó, Lynae không biết liệu {PlayerName}, người từ trên trời rơi thẳng xuống, có chứng kiến khoảnh khắc cô thực hiện kế hoạch của mình hay không. Cô nhìn {Male=him;Female=her} đứng dậy từ mặt đất, ngón tay cô bản năng siết chặt cò súng. Nhưng sự lạnh lùng trong ánh mắt cô biến mất ngay khi thấy một lá thư nhập học rơi xuống giữa họ. Trong khoảnh khắc ấy, cô nhận ra—
 —Cô không còn là "lính đánh thuê" lẩn khuất trong bóng tối nữa. Giờ cô chỉ là một sinh viên. Một người chỉ muốn sống một cuộc đời tự do.
-Cô lập tức cất vũ khí đi, mồ hôi lạnh toát ra. Lỡ cô vừa đâm sầm vào một tân sinh viên thì sao? Điều đó còn tệ hơn cả thành tích điểm danh thảm hại của cô! Nếu {Male=cậu ấy;Female=cô ấy} không chịu tha thứ, cô coi như xong!
-Vậy nên cô vội vàng đưa tay ra, kéo {PlayerName} đứng dậy và lôi {Male=cậu ấy;Female=cô ấy} lên ghế sau xe máy của mình. Và ngay lúc đó, một Voidworm quằn quại trên mặt đất, sẵn sàng trút ý đồ độc ác lên cả hai.
+Cô lập tức cất vũ khí đi, mồ hôi lạnh toát ra. Lỡ cô vừa đâm sầm vào một tân sinh viên thì sao? Điều đó còn tệ hơn cả thành tích điểm danh thảm hại của cô! Nếu {Male=he;Female=she} không chịu tha thứ, cô coi như xong!
+Vậy nên cô vội vàng đưa tay ra, kéo {PlayerName} đứng dậy và lôi {Male=him;Female=her} lên ghế sau xe máy của mình. Và ngay lúc đó, một Voidworm quằn quại trên mặt đất, sẵn sàng trút ý đồ độc ác lên cả hai.
 Lúc ấy cô không biết, nhưng câu chuyện thực sự thuộc về Lynae đã bắt đầu từ chính khoảnh khắc đó.</t>
         </is>
       </c>
@@ -26917,16 +26917,16 @@
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t>Năm mười sáu tuổi, Mornye nhận được thư nhập học từ &lt;te href=851069&gt;Startorch Academy&lt;/te&gt;.
+          <t>Năm mười sáu tuổi, Mornye nhận được thư nhập học từ &lt;te href=851069&gt;Học viện Startorch&lt;/te&gt;.
 Khả năng Forte của cô đã thức tỉnh từ trước đó, vào một buổi chiều bình thường như bao ngày khác, khi cô nhận ra mình không còn cần phải tự đẩy những bánh xe nặng nề của chiếc xe lăn nữa. Điều đó chẳng có gì đặc biệt đáng mừng, bởi cô đã hiểu rõ nguyên lý vận hành từ lâu. Dù là xoay chuyển chúng trong đầu hay ngoài đời, cũng chẳng khác nhau là mấy. Cơ thể bất động của cô vẫn bị giam cầm trên chiếc khung kim loại nặng nề ấy.
-Đêm hôm đó, khi tự di chuyển lên giường, cô chợt thấy vết Echo phát sáng lờ mờ trên đùi mình. Nó như một trò đùa ác ý dành riêng cho cô.
+Đêm hôm đó, khi tự di chuyển lên giường, cô chợt thấy vết Tổ Tacet phát sáng lờ mờ trên đùi mình. Nó như một trò đùa ác ý dành riêng cho cô.
 Nhưng lá thư nhập học thì khác.
-Startorch Academy nổi tiếng là ngôi trường hàng đầu đào tạo nhân tài trên khắp &lt;te href=850079&gt;Solaris&lt;/te&gt;, và tổ chức chủ quản của nó, &lt;te href=851071&gt;Spacetrek Collective&lt;/te&gt;, đại diện cho đỉnh cao công nghệ nhân loại. Tấm giấy in tinh xảo ấy như xé toang một vết nứt trong thế giới chật hẹp của Mornye, chứng minh rằng ngay cả một người không thể cử động, ngay cả người sở hữu một khả năng Forte mà chính cô cũng cho là vô dụng, vẫn có thể được coi là "xứng đáng".
+Học viện Startorch nổi tiếng là ngôi trường hàng đầu đào tạo nhân tài trên khắp &lt;te href=850079&gt;Solaris&lt;/te&gt;, và tổ chức chủ quản của nó, &lt;te href=851071&gt;Spacetrek Collective&lt;/te&gt;, đại diện cho đỉnh cao công nghệ nhân loại. Tấm giấy in tinh xảo ấy như xé toang một vết nứt trong thế giới chật hẹp của Mornye, chứng minh rằng ngay cả một người không thể cử động, ngay cả người sở hữu một khả năng Forte mà chính cô cũng cho là vô dụng, vẫn có thể được coi là "xứng đáng".
 Liệu một người như cô có thực sự là một trong những vì sao mai, được sinh ra để thắp sáng tương lai nhân loại?
 Cô nhanh chóng hoàn thành Chương trình Dự bị, và khả năng Forte của cô được đánh giá phù hợp nhất với Khoa Kỹ thuật Exostrider. Cô trở thành thiên tài được thì thầm trong các hành lang, học trò cưng của các thầy cô, trợ giảng trẻ nhất khoa. Nhưng tất cả vẫn chưa bao giờ là đủ. Cô dành vô số đêm chìm đắm trong báo cáo và thí nghiệm, thường xuyên lao vào những nhiệm vụ nguy hiểm đẩy khả năng Forte của mình đến giới hạn Overclocking. Một đêm nọ, đầu óc choáng váng vì bỏ bữa Nutri-Pack, cô chợt tự hỏi—nếu, chỉ là nếu—cơ thể cô một ngày nào đó có thể trở thành nền tảng của những đại sảnh khoa học mà cô hằng mơ ước. Nếu thế, đó sẽ là một kết thúc thỏa mãn.
 "Đã nửa đêm rồi. Cô không nghỉ ngơi à?"
 Cô ngẩng đầu lên và bắt gặp đôi mắt vàng.
-Cô nhớ người này. Người khởi xướng dự án hiện tại của cô, tiền bối và người hướng dẫn tại Startorch Academy. Cô luôn bị thu hút bởi đôi mắt vàng ấy, mang theo một nỗi cô đơn mênh mông mà Mornye chưa thể hiểu hết. Chúng nhìn mọi người với sự bình thản vô tư, không hề có chút thương hại mà cô vẫn thường gặp.
+Cô nhớ người này. Người khởi xướng dự án hiện tại của cô, tiền bối và người hướng dẫn tại Học viện Startorch. Cô luôn bị thu hút bởi đôi mắt vàng ấy, mang theo một nỗi cô đơn mênh mông mà Mornye chưa thể hiểu hết. Chúng nhìn mọi người với sự bình thản vô tư, không hề có chút thương hại mà cô vẫn thường gặp.
 "Nếu cô không nghỉ ngơi," người đó nói, giọng đều đặn và điềm tĩnh, "cô sẽ bỏ lỡ những vì sao."</t>
         </is>
       </c>
@@ -27004,15 +27004,15 @@
       <c r="M392" t="inlineStr">
         <is>
           <t>"Giáo sư Mornye, lần này Cody và Vance lại cãi nhau về linh kiện thử nghiệm Helios rồi. Chắc là... phải nhờ cô đến thôi."
-Mornye thở dài một tiếng gần như không nghe thấy. Phía trên, bộ Starstack cải tiến vẫn đều đều rung lên, truyền Forte của cô vào bàn phím nổi để trả lời hàng loạt email về tình hình Lễ Mặt Trời New. Tay trái cô điều chỉnh thông số mô phỏng đánh lửa trên một màn hình nổi khác, còn tay phải thì giải dãy phép tính đàn hồi dẻo. Cô có thể xử lý hàng tá công việc cùng lúc, nhưng những cuộc tranh cãi kiểu này luôn khiến mọi tiến độ của cô chững lại.
-Hai kẻ cãi nhau là hai sinh viên mới tốt nghiệp—thông minh, đầy tham vọng, và khao khát chứng tỏ bản thân. Mornye chưa bao giờ trải qua thứ nhiệt huyết tuổi trẻ ấy. Dù vậy, cảnh tượng này vẫn gợi lại ký ức về những ngày đầu cô làm việc tại Viện Nghiên Cứu. Cô nhớ lần đầu tiên xung đột với hội đồng về đề xuất tái tạo bầu trời đêm sao, và sau khi cuối cùng cũng được chấp thuận, một &lt;te href=851070&gt;Void Storm&lt;/te&gt; đã ập đến. Cô nhớ mình đã &lt;te href=850073&gt;Overclocking&lt;/te&gt; để giữ cho tháp tín hiệu không sập, và tất nhiên, khoảnh khắc một linh kiện rơi xuống đập trúng chân cô.
+Mornye thở dài một tiếng gần như không nghe thấy. Phía trên, bộ Starstack cải tiến vẫn đều đều rung lên, truyền Forte của cô vào bàn phím nổi để trả lời hàng loạt email về tình hình Lễ Mặt Trời Mới. Tay trái cô điều chỉnh thông số mô phỏng đánh lửa trên một màn hình nổi khác, còn tay phải thì giải dãy phép tính đàn hồi dẻo. Cô có thể xử lý hàng tá công việc cùng lúc, nhưng những cuộc tranh cãi kiểu này luôn khiến mọi tiến độ của cô chững lại.
+Hai kẻ cãi nhau là hai sinh viên mới tốt nghiệp—thông minh, đầy tham vọng, và khao khát chứng tỏ bản thân. Mornye chưa bao giờ trải qua thứ nhiệt huyết tuổi trẻ ấy. Dù vậy, cảnh tượng này vẫn gợi lại ký ức về những ngày đầu cô làm việc tại Viện Nghiên cứu. Cô nhớ lần đầu tiên xung đột với hội đồng về đề xuất tái tạo bầu trời đêm sao, và sau khi cuối cùng cũng được chấp thuận, một &lt;te href=851070&gt;Cơn Bão Hư Không&lt;/te&gt; đã ập đến. Cô nhớ mình đã &lt;te href=850073&gt;Ép xung&lt;/te&gt; để giữ cho tháp tín hiệu không sập, và tất nhiên, khoảnh khắc một linh kiện rơi xuống đập trúng chân cô.
 ...Chà, có lẽ cô cũng không khác mấy so với đám sinh viên trẻ này.
 Khi cuộc tranh cãi được giải quyết, Mảng Dựng Hình Bầu Trời đã chuyển sang chế độ ban đêm. Một khẩu Pháo Bay giao bữa tối cho cô—gói Nutri-Pack hôm nay có hương vị "Bò hun khói", một sản phẩm mới từ Bộ phận Nông nghiệp. Cô vặn nắp mở, tắt màn hình nổi cuối cùng, rồi để ánh mắt lơ đãng hướng ra những vì sao nhân tạo bên ngoài cửa sổ.
 Người thầy của cô đã ra đi từ lâu.
-Biết bao chuyện đã xảy ra kể từ đó. Cô tốt nghiệp và gia nhập Viện. Nhiệm vụ đầu tiên là dựng lên một bầu trời cho &lt;te href=260004&gt;Lahai-Roi&lt;/te&gt;. Đôi chân của cô, được tái tạo qua nhiều cuộc phẫu thuật, giờ đây đã di chuyển một cách tự nhiên. Và vào ngày cuối cùng cô gặp thầy, {Male=ông ấy;Female=bà ấy} đã nói rằng Lahai-Roi đã sẵn sàng tự bước tiếp.
-{Male=Ông ấy;Female=Bà ấy} không thuộc về Lahai-Roi. Đó là lúc Mornye hiểu vì sao đôi mắt vàng ấy luôn giữ khoảng cách với mọi người. {Male=Ông ấy;Female=Bà ấy} sinh ra vốn không để ở lại bất cứ nơi nào quá lâu.
+Biết bao chuyện đã xảy ra kể từ đó. Cô tốt nghiệp và gia nhập Viện. Nhiệm vụ đầu tiên là dựng lên một bầu trời cho &lt;te href=260004&gt;Lahai-Roi&lt;/te&gt;. Đôi chân của cô, được tái tạo qua nhiều cuộc phẫu thuật, giờ đây đã di chuyển một cách tự nhiên. Và vào ngày cuối cùng cô gặp thầy, {Male=He;Female=She} đã nói rằng Lahai-Roi đã sẵn sàng tự bước tiếp.
+{Male=He;Female=She} không thuộc về Lahai-Roi. Đó là lúc Mornye hiểu vì sao đôi mắt vàng ấy luôn giữ khoảng cách với mọi người. {Male=He;Female=She} sinh ra vốn không để ở lại bất cứ nơi nào quá lâu.
 Nhưng điều đó cũng không sao.
-Bên dưới, trong phòng thử nghiệm, Helios tỏa ánh sáng bạc trong bóng tối. Lễ Mặt Trời New—ngay cả người thầy của cô cũng chưa từng mường tượng được một dự án vĩ đại đến thế để đánh thức Exostrider.
+Bên dưới, trong phòng thử nghiệm, Helios tỏa ánh sáng bạc trong bóng tối. Lễ Mặt Trời Mới—ngay cả người thầy của cô cũng chưa từng mường tượng được một dự án vĩ đại đến thế để đánh thức Exostrider.
 —"Con đã tìm ra điều mình muốn làm rồi, thầy ơi. Và... con có thể đi xa hơn cả những gì thầy đã làm."
 —"Vậy khi con trở về một ngày nào đó... liệu con có sẵn sàng để đứng bên cạnh thầy không?"</t>
         </is>
@@ -27540,7 +27540,7 @@
       </c>
       <c r="M400" t="inlineStr">
         <is>
-          <t>Kỹ năng chủ động</t>
+          <t>Kỹ Năng Chủ Động</t>
         </is>
       </c>
     </row>
@@ -27735,7 +27735,7 @@
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t>Skills Đặc Biệt chỉ có thể sử dụng sau khi đáp ứng điều kiện nhất định. Active Skill chỉ có thể dùng một lần mỗi lượt. Một số hiệu ứng có thể reset số lần sử dụng Active Skill của thẻ.</t>
+          <t>Kỹ năng Đặc Biệt chỉ có thể sử dụng sau khi đáp ứng điều kiện nhất định. Kỹ Năng Chủ Động chỉ có thể dùng một lần mỗi lượt. Một số hiệu ứng có thể reset số lần sử dụng Kỹ Năng Chủ Động của thẻ.</t>
         </is>
       </c>
     </row>
@@ -27800,7 +27800,7 @@
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>Trong Giai đoạn Triển khai và Giai đoạn Chiến đấu, mỗi lần mất HP, Resonator chỉ mất ít hơn 1 HP.</t>
+          <t>Trong Giai đoạn Triển khai và Giai đoạn Chiến đấu, mỗi lần mất HP, Cộng Hưởng Giả chỉ mất ít hơn 1 HP.</t>
         </is>
       </c>
     </row>
@@ -27865,7 +27865,7 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>Mỗi lần Resonator chịu sát thương sẽ được giảm đi 5.</t>
+          <t>Mỗi lần Cộng Hưởng Giả chịu DMG sẽ được giảm đi 5.</t>
         </is>
       </c>
     </row>
@@ -27997,9 +27997,9 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>Mỗi khi đấu thủ triển khai Echoes, Echoes đó sẽ nhận được Kháng Phá và Resilience.
-Đấu thủ sẽ mất ít hơn 1 HP mỗi khi bị trừ HP trong Giai Đoạn Triển Khai và Battle Stage.
-Cuối mỗi hiệp đấu, các Echoes của đấu thủ sẽ nhận được X điểm Sức Mạnh và Thể Chất, với X là số hiệp hiện tại.</t>
+          <t>Mỗi khi đấu thủ triển khai Echo, Echo đó sẽ nhận được Kháng Phá và Kiên Cường.
+Đấu thủ sẽ mất ít hơn 1 HP mỗi khi bị trừ HP trong Giai Đoạn Triển Khai và Giai Đoạn Chiến Đấu.
+Cuối mỗi hiệp đấu, các Echo của đấu thủ sẽ nhận được X điểm Sức Mạnh và Thể Chất, với X là số hiệp hiện tại.</t>
         </is>
       </c>
     </row>
@@ -28064,7 +28064,7 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>Chế độ Cộng hưởng - Giai điệu Vỡ</t>
+          <t>Chế Độ Cộng Hưởng - Đứt Gãy Giai Điệu</t>
         </is>
       </c>
     </row>
@@ -28129,7 +28129,7 @@
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>Trong &lt;color=Highlight&gt;Resonance Mode - Tune Rupture&lt;/color&gt;, Lynae có thể gây hiệu ứng &lt;color=Highlight&gt;Tune Rupture - Shifting&lt;/color&gt; lên mục tiêu. Khi gây hiệu ứng &lt;color=Highlight&gt;Photochromic Flux&lt;/color&gt; lên mục tiêu, cô cũng sẽ đồng thời gây hiệu ứng &lt;color=Highlight&gt;Tune Rupture - Shifting&lt;/color&gt;.</t>
+          <t>Trong &lt;color=Highlight&gt;Chế Độ Cộng Hưởng - Vỡ Giai Điệu&lt;/color&gt;, Lynae có thể gây hiệu ứng &lt;color=Highlight&gt;Vỡ Giai Điệu - Chuyển Dịch&lt;/color&gt; lên mục tiêu. Khi gây hiệu ứng &lt;color=Highlight&gt;Dòng Phổ Quang&lt;/color&gt; lên mục tiêu, cô cũng sẽ đồng thời gây hiệu ứng &lt;color=Highlight&gt;Vỡ Giai Điệu - Chuyển Dịch&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -28194,7 +28194,7 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>Chế độ Cộng hưởng - Giai điệu Căng</t>
+          <t>Chế Độ Cộng Hưởng - Căng Thẳng Giai Điệu</t>
         </is>
       </c>
     </row>
@@ -28259,7 +28259,7 @@
       </c>
       <c r="M411" t="inlineStr">
         <is>
-          <t>Khi ở trong &lt;color=Highlight&gt;Resonance Mode - Tune Strain&lt;/color&gt;, Lynae có thể gây &lt;color=Highlight&gt;Tune Strain - Shifting&lt;/color&gt; lên mục tiêu. Khi gây &lt;color=Highlight&gt;Photochromic Flux&lt;/color&gt; lên mục tiêu, cô cũng đồng thời gây &lt;color=Highlight&gt;Tune Strain - Shifting&lt;/color&gt;.</t>
+          <t>Khi ở trong &lt;color=Highlight&gt;Chế Độ Cộng Hưởng - Đoạn Tần Căng Thẳng&lt;/color&gt;, Lynae có thể gây &lt;color=Highlight&gt;Đoạn Tần Căng Thẳng - Dịch Chuyển&lt;/color&gt; lên mục tiêu. Khi gây &lt;color=Highlight&gt;Dòng Photon Biến Đổi&lt;/color&gt; lên mục tiêu, cô cũng đồng thời gây &lt;color=Highlight&gt;Đoạn Tần Căng Thẳng - Dịch Chuyển&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -28393,7 +28393,7 @@
       <c r="M413" t="inlineStr">
         <is>
           <t>Soliskin cũng chơi *Peaks of Prestige* à? Hay chỉ là vỏ bọc chiến thuật của Eloni thôi?
-Đặc tính Đấu Thủ: Trong Battle Stage, đấu thủ chịu ít hơn 5 sát thương.</t>
+Đặc tính Đấu Thủ: Trong Giai Đoạn Chiến Đấu, đấu thủ chịu ít hơn 5 DMG.</t>
         </is>
       </c>
     </row>
@@ -28531,9 +28531,9 @@
         <is>
           <t>Aldo rất hứng thú với những sinh vật cổ xưa của Lahai-Roi và đã đưa trí tưởng tượng của mình về chúng vào bộ bài.
 Đặc tính Người Chơi:
-Mỗi khi triển khai một Echoes, Echoes đó sẽ nhận được Kháng Cự và Resilience.
+Mỗi khi triển khai một Echo, Echo đó sẽ nhận được Kháng Cự và Kiên Cường.
 Người chơi mất ít hơn 1 HP mỗi khi bị trừ HP trong Giai đoạn Triển Khai và Giai đoạn Chiến Đấu.
-Cuối mỗi lượt, các Echoes của người chơi sẽ nhận được X điểm Sức Mạnh và Thể Chất, với X là số thứ tự lượt hiện tại.</t>
+Cuối mỗi lượt, các Echo của người chơi sẽ nhận được X điểm Sức Mạnh và Thể Chất, với X là số thứ tự lượt hiện tại.</t>
         </is>
       </c>
     </row>
@@ -28610,7 +28610,7 @@
         <is>
           <t>Để duy trì cam kết chung về hòa bình và hợp tác, các bên ký kết của Hiệp hội Tiên phong đã họp mặt. Sau những cuộc đàm phán kéo dài, các nguyên thủ quốc gia của họ quyết định thành lập một tổ chức liên chính phủ mới mang tên "Khối Cực Địa" (Ghi chú của biên tập: tiền thân của Khối Spacetrek).
 Ngay khi hội nghị sắp kết thúc, một trưởng lão Roya, một trong những Solsworn được tôn kính của họ, xuất hiện trước hội nghị.
-Những lời đồn đoán và thì thầm về ý định của ông lan truyền khắp hội trường. Hầu hết các đại biểu nhìn ông với vẻ kiêu ngạo tinh tế của một "thế giới văn minh" khi đánh giá đại diện của một bộ tộc cổ xưa. Không hề nao núng, vị Solsworn bắt đầu vẽ một loạt các hoa văn phức tạp, bí ẩn, lẩm bẩm một mình trong lúc làm việc. Ban đầu, nhiều người cho rằng đó chỉ là những lời nguyền rủa hay những Dodget vẽ nguệch ngoạc vô nghĩa. Nhưng khi các hoa văn dần hiện hình, sự thật cũng lộ ra—đó là những công thức toán học.
+Những lời đồn đoán và thì thầm về ý định của ông lan truyền khắp hội trường. Hầu hết các đại biểu nhìn ông với vẻ kiêu ngạo tinh tế của một "thế giới văn minh" khi đánh giá đại diện của một bộ tộc cổ xưa. Không hề nao núng, vị Solsworn bắt đầu vẽ một loạt các hoa văn phức tạp, bí ẩn, lẩm bẩm một mình trong lúc làm việc. Ban đầu, nhiều người cho rằng đó chỉ là những lời nguyền rủa hay những nét vẽ nguệch ngoạc vô nghĩa. Nhưng khi các hoa văn dần hiện hình, sự thật cũng lộ ra—đó là những công thức toán học.
 Các ký hiệu ông sử dụng thuộc về một hệ thống số học hoàn toàn xa lạ với chúng ta, nhưng khi được "chuyển đổi" sang ký hiệu hiện đại, cấu trúc chúng mô tả lại trùng khớp với một số phương trình tiên tiến nhất của chúng ta. Loại toán học mà chúng ta tin rằng có thể thay đổi thế giới. Trong khoảnh khắc đó, hội nghị hiểu được ý nghĩa trong hành động của vị Solsworn. Nó chứng minh rằng người Roya sở hữu tri thức và sự tinh thông toán học ngang tầm với chúng ta, và quan trọng hơn, họ sẵn sàng chia sẻ trí tuệ cổ xưa này với Khối Cực Địa.
 Trong khoảnh khắc đó, toán học trở thành ngôn ngữ duy nhất trong phòng. Chỉ với vài điểm và đường vẽ vội vàng, vị Solsworn đã hoàn thành phép đo thiên văn về trục cực. Độ chính xác của nó không chỉ tương đương mà có lẽ còn vượt trội so với những công cụ hiện đại nhất của chúng ta. Sự kinh ngạc dần nhường chỗ cho im lặng. Không còn nghi ngờ gì nữa: những thành tựu của người Roya không chỉ đạt tới mà còn thách thức sự thống trị trí tuệ mà cái gọi là thế giới văn minh tự nhận.
 Sự im lặng không kéo dài. Vị Solsworn tiếp tục trình bày một bộ phương trình thứ hai. Chúng mô tả sự hiện diện của Hiện tượng Waveworn bên trong Lahai-Roi, cho thấy hoạt động của nó đang gia tăng theo thời gian. Thế nhưng, khi kết thúc công thức này, vị Solsworn không đưa ra giải pháp nào.
@@ -28804,8 +28804,8 @@
 Vì Người Khổng Lồ đã ở đây.
 Vì Người Khổng Lồ đã ở đây.
 —Trích đoạn dân ca Royan *Vì Người Khổng Lồ Đã Ở Đây*
-Dù vật lộn sinh tồn trong vùng băng giá, người Roya vẫn không tìm được bình yên. Thay vào đó, họ phải đối mặt với Cơn Void Storm đầu tiên trong lịch sử được ghi chép. Biên niên sử Royan kể về một luồng sáng chói lòa xuyên qua lớp băng, đâm thẳng lên trời. Mọi thứ bị cơn bão ấy chạm đến đều bị thiêu rụi, mất đi hình hài và bị xóa sổ khỏi thế gian.
-Chính thảm họa này đã gây ra sự sụp đổ chưa từng có của vùng băng giá, đẩy tổ tiên người Roya vào một hang động ngầm rộng lớn. Thế nhưng, trong bóng tối vô tận ấy, một động cơ Reactor Drive rung chuyển đã mọc lên như bình minh mới, khi Exostrider tự rút lấy Core của mình và thắp sáng nó thành mặt trời của thế giới ngầm này.
+Dù vật lộn sinh tồn trong vùng băng giá, người Roya vẫn không tìm được bình yên. Thay vào đó, họ phải đối mặt với Cơn Bão Hư Không đầu tiên trong lịch sử được ghi chép. Biên niên sử Royan kể về một luồng sáng chói lòa xuyên qua lớp băng, đâm thẳng lên trời. Mọi thứ bị cơn bão ấy chạm đến đều bị thiêu rụi, mất đi hình hài và bị xóa sổ khỏi thế gian.
+Chính thảm họa này đã gây ra sự sụp đổ chưa từng có của vùng băng giá, đẩy tổ tiên người Roya vào một hang động ngầm rộng lớn. Thế nhưng, trong bóng tối vô tận ấy, một động cơ Reactor Drive rung chuyển đã mọc lên như bình minh mới, khi Exostrider tự rút lấy Lõi của mình và thắp sáng nó thành mặt trời của thế giới ngầm này.
 Còn về ▇▇▇▇▇, kẻ thù từng giao chiến với Exostrider, những ghi chép cổ xưa chỉ còn lại những mảnh vụn. Có lẽ, với người Roya, nỗi kinh hoàng về kẻ thù kia không quan trọng bằng sự hy sinh của người đã che chở cho họ.</t>
         </is>
       </c>
@@ -28889,7 +28889,7 @@
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>Speaker: Tiến sĩ Scott Rabelle
+          <t>Người nói: Tiến sĩ Scott Rabelle
 Thời lượng: 00:42:11
 Trích đoạn: 00:37:12 - 00:41:56
 _______
@@ -28897,13 +28897,13 @@
 (Im lặng ngắn. Có thể nghe thấy tiếng thở nhẹ.)
 Nói cách khác, ███ đang không ngừng ███ nguồn ███ phía sau ███. Những gì chúng ta thấy là một trạng thái cân bằng động, một cuộc giằng co giữa ổn định và bất ổn. Nếu nguồn "cung cấp" này bị gián đoạn, trạng thái cân bằng sẽ sụp đổ. Nguồn ███ phía sau ███ sẽ tràn vào Lahai-Roi. Bản tóm tắt nghiên cứu tạm thời P.C.–LH–R/0987 cảnh báo rằng tình trạng của Sentinel Analog rất xa với khả quan. Nếu hành động ngay bây giờ, có thể vẫn còn một tia hy vọng. Nếu không làm gì, thất bại là chắc chắn. Việc ███ mở ra là không thể tránh khỏi. Dù nó mở khi nào hay do ai mở, chúng ta phải chuẩn bị sẵn sàng.
 (Tiếng xì xào lo lắng từ khán giả.)
-Việc Sentinel tự giải phóng thông qua Resonance không phải là chưa từng có tiền lệ. Và vì chúng ta đã chứng minh được sự tương đồng gần như hoàn hảo giữa Sentinel Analog và một Sentinel thực sự, thì kích thích Resonance Tăng Cường nhân tạo là phương pháp khả thi nhất để đẩy Sentinel Analog vượt qua giới hạn tự nhiên của nó.
+Việc Sentinel tự giải phóng thông qua Cộng Hưởng không phải là chưa từng có tiền lệ. Và vì chúng ta đã chứng minh được sự tương đồng gần như hoàn hảo giữa Sentinel Analog và một Sentinel thực sự, thì kích thích Cộng Hưởng Tăng Cường nhân tạo là phương pháp khả thi nhất để đẩy Sentinel Analog vượt qua giới hạn tự nhiên của nó.
 Hoặc chúng ta chủ động điều khiển Sentinel Analog mở ███ và đối mặt trực tiếp với ███ phía sau... hoặc đứng nhìn trong bất lực khi ███ đập vỡ ███ và nuốt chửng chúng ta. Rõ ràng, chúng ta không còn lựa chọn nào khác.
 (Tiếng bàn tán nhỏ từ những người tham dự.)
 Tôi biết. Nghe có vẻ như một canh bạc liều lĩnh. Nhưng hãy nhìn xung quanh. Các bạn là những bộ óc xuất sắc nhất của Solaris. Những người tiên phong trong mọi lĩnh vực. Và tôi tin rằng... tinh thần khoa học chưa bao giờ tồn tại trong sự chắc chắn. Nó sống trong lòng dũng cảm dám bước vào bóng tối đầu tiên.
 Do đó, chúng ta đã hoàn thiện kế hoạch:
 Một sáng kiến nghiên cứu thống nhất tập trung vào nghiên cứu Exostrider, mở rộng sang hàng không vũ trụ, cộng hưởng sinh học và hệ thống năng lượng. Đây sẽ không chỉ là một dự án học thuật đơn thuần. Đây là sáng kiến tự cứu lấy nền văn minh của chúng ta.
-Tôi xin thông báo rằng Tập Đoàn Cực Bắc sẽ được đổi tên thành Spacetrek Collective. Đồng thời, chúng ta sẽ thành lập một tổ chức mới tại Lahai-Roi: Học Viện Startorch. Nó sẽ đóng vai trò tiền đồn nghiên cứu ███. Tại đó, các Roya và học giả từ khắp nơi trên thế giới sẽ nghiên cứu bản chất cơ sinh học của Exostrider và đào tạo những ███ có khả năng hình thành Resonance Tăng Cường với Sentinel Analog.
+Tôi xin thông báo rằng Tập Đoàn Cực Bắc sẽ được đổi tên thành Tập Đoàn Spacetrek. Đồng thời, chúng ta sẽ thành lập một tổ chức mới tại Lahai-Roi: Học Viện Startorch. Nó sẽ đóng vai trò tiền đồn nghiên cứu ███. Tại đó, các Roya và học giả từ khắp nơi trên thế giới sẽ nghiên cứu bản chất cơ sinh học của Exostrider và đào tạo những ███ có khả năng hình thành Cộng Hưởng Tăng Cường với Sentinel Analog.
 Thông qua Học Viện, chúng ta sẽ nghiên cứu Sentinel Analog để hiểu sâu hơn về các quy luật thời kỳ hậu Lament và cuối cùng phá vỡ sự phong tỏa của Etheric Sea. Cùng nhau, chúng ta sẽ tiến tới một không gian sâu hơn và một tương lai tiên tiến hơn. Và có lẽ một ngày nào đó, những phát hiện về Sentinel Analog có thể được chia sẻ công khai, vì lợi ích của toàn thể Solaris.
 Một sinh viên từng hỏi tôi: "Điểm đến cuối cùng của chúng ta là gì?"
 Tôi tin câu trả lời rất đơn giản. Đó không phải là trở lại với những vì sao. Mà là giành lại lòng dũng cảm để ngước nhìn vào những điều chưa biết.
@@ -28987,21 +28987,21 @@
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>Kính thưa quý đại biểu, những thành viên đáng kính của Black Shores, các Royan Solsworn tôn quý, và những nhân chứng của Pioneer Association:
-Hôm nay, chúng ta tụ họp không chỉ để đặt nền móng cho một Học viện, mà còn để tìm ra con đường khả dĩ cho sự tồn vong của chính nền văn minh này. Xin cho phép tôi trình bày mục đích của Startorch Academy qua ba nhận thức cốt lõi.
+          <t>Kính thưa quý đại biểu, những thành viên đáng kính của Black Shores, các Royan Solsworn tôn quý, và những nhân chứng của Hiệp hội Pioneer:
+Hôm nay, chúng ta tụ họp không chỉ để đặt nền móng cho một Học viện, mà còn để tìm ra con đường khả dĩ cho sự tồn vong của chính nền văn minh này. Xin cho phép tôi trình bày mục đích của Học viện Startorch qua ba nhận thức cốt lõi.
 Thứ nhất, cuộc khủng hoảng đã cận kề.
 Mọi người trong căn phòng này đều hiểu điều đó, đặc biệt là những người bạn Royan của chúng ta. Lahai-Roi giờ đây như một quả trứng đặt trên bức tường cao, với toàn bộ sự sống phụ thuộc vào hoạt động của Reactor Drive. Nhưng năng lượng của nó không phải là vĩnh cửu, và những hiện tượng Waveworn ngày càng tồi tệ nhắc nhở chúng ta rằng hiểm nguy chưa bao giờ thực sự rời xa.
 Các cuộc điều tra của chúng ta đã vén màn bí mật đằng sau ▇▇, hé lộ rằng kẻ thù lớn nhất của nền văn minh vẫn đang ẩn nấp trong bóng tối. Dù nhiệm vụ của Exostrider là bảo vệ, và cơ chế tự tái tạo của nó vẫn còn mạnh mẽ, nhưng các quá trình sinh học của nó đều có giới hạn.
 Sự phân hóa của Exoswarm đã chậm lại. Các thành phần hiện có không còn đủ để khôi phục cơ thể nó. Tệ hơn nữa, vô số Exoswarm đã bị ▇▇▇ nuốt chửng. Ngay cả khi Exostrider có thức tỉnh vào ngày mai, nó cũng không thể chiến đấu một mình.
-Thứ hai, con đường duy nhất phía trước là đánh thức Exostrider thông qua Resonance và khuếch đại sức mạnh của nó.
-Như tất cả chúng ta đều biết, Resonance có thể khuếch đại tiềm năng của mục tiêu một cách đáng kể. Nhưng Resonance tự nhiên xảy ra không thể đoán trước và không thể kiểm soát, trong khi việc ép buộc Resonators nhân tạo vi phạm những nguyên tắc đạo đức cơ bản nhất của con người. Chúng ta không thể xây dựng tương lai trên sự may rủi. Chúng ta phải theo đuổi sự chắc chắn thông qua khoa học. Bằng cách sử dụng các thiết bị cơ khí bên ngoài, chúng ta có thể thiết lập liên kết nhận thức và đạt được Resonance Tăng Cường với Exostrider. Xin hãy yên tâm, mọi người, rằng công nghệ nền tảng đã nằm trong tay chúng ta, và các vòng kiểm chứng thành công đã được hoàn tất.
+Thứ hai, con đường duy nhất phía trước là đánh thức Exostrider thông qua Cộng Hưởng và khuếch đại sức mạnh của nó.
+Như tất cả chúng ta đều biết, Cộng Hưởng có thể khuếch đại tiềm năng của mục tiêu một cách đáng kể. Nhưng Cộng Hưởng tự nhiên xảy ra không thể đoán trước và không thể kiểm soát, trong khi việc ép buộc các Resonator nhân tạo vi phạm những nguyên tắc đạo đức cơ bản nhất của con người. Chúng ta không thể xây dựng tương lai trên sự may rủi. Chúng ta phải theo đuổi sự chắc chắn thông qua khoa học. Bằng cách sử dụng các thiết bị cơ khí bên ngoài, chúng ta có thể thiết lập liên kết nhận thức và đạt được Cộng Hưởng Tăng Cường với Exostrider. Xin hãy yên tâm, mọi người, rằng công nghệ nền tảng đã nằm trong tay chúng ta, và các vòng kiểm chứng thành công đã được hoàn tất.
 Như dữ liệu trước mắt quý vị cho thấy, chúng ta đã đạt được những đột phá có thể đo lường được trong ba năm qua. Điều này xác nhận hướng đi của chúng ta là đúng đắn. Dù việc cộng hưởng với Exostrider đặt gánh nặng lên người sử dụng, nhưng qua đào tạo hệ thống, các Synchronist đủ điều kiện sẽ trở thành cầu nối lý tưởng, có khả năng kích hoạt Exostrider, đẩy lùi ▇▇, và hóa giải mối đe dọa đang treo lơ lửng trên mảnh đất này.
-Thứ ba, Startorch Academy sẽ trở thành cái nôi của những Synchronist này và là con thuyền hy vọng chung của chúng ta.
-Nghiên cứu của chúng ta đã phát hiện ra một quy luật rõ ràng. Thông qua việc đo lường Đường cong Rabelle, chúng ta có thể xác định những cá nhân có tiềm năng Resonance.
-Để bồi dưỡng những ứng viên này, nâng cao khả năng tương thích của họ và duy trì nghiên cứu liên tục, chúng ta đã thành lập Học viện này, mở cửa cho tài năng từ khắp nơi trên thế giới, quy tụ các chuyên gia từ mọi lĩnh vực. Tại đây, chúng ta sẽ hoàn thiện công nghệ Resonance Tăng Cường ổn định và phát triển các chiến lược đa dạng để đối phó với ▇▇▇ và chống chọi với mối đe dọa đang cận kề của ▇▇.
+Thứ ba, Học viện Startorch sẽ trở thành cái nôi của những Synchronist này và là con thuyền hy vọng chung của chúng ta.
+Nghiên cứu của chúng ta đã phát hiện ra một quy luật rõ ràng. Thông qua việc đo lường Đường cong Rabelle, chúng ta có thể xác định những cá nhân có tiềm năng Cộng Hưởng.
+Để bồi dưỡng những ứng viên này, nâng cao khả năng tương thích của họ và duy trì nghiên cứu liên tục, chúng ta đã thành lập Học viện này, mở cửa cho tài năng từ khắp nơi trên thế giới, quy tụ các chuyên gia từ mọi lĩnh vực. Tại đây, chúng ta sẽ hoàn thiện công nghệ Cộng Hưởng Tăng Cường ổn định và phát triển các chiến lược đa dạng để đối phó với ▇▇▇ và chống chọi với mối đe dọa đang cận kề của ▇▇.
 Tất cả những điều này sẽ không thể thực hiện được nếu không có sự đóng góp của các Roya, những người quản lý chân chính của mảnh đất này. Những món quà tính toán của các vị, kiến thức sâu rộng về Exostrider và Exoswarm, là không thể thiếu. Xin hãy tin tưởng rằng hướng đi của chúng ta song hành với các vị, và cánh cửa của Học viện này sẽ luôn rộng mở đón chào các vị.
 Gửi đến mỗi vị đại biểu có mặt tại đây hôm nay: Tôi xin kêu gọi sự tin tưởng và ủng hộ của quý vị. Mọi thành tựu được tạo ra trong những bức tường này sẽ trở về với những người đã sát cánh cùng chúng ta, tạo ra giá trị vượt xa biên giới này.
-Những người bạn Royan của tôi, các vị đã bảo vệ mảnh đất này qua bao thế hệ. Kính thưa quý đại biểu, các vị đang gánh vác tương lai của nhân loại trên đôi vai mình. Startorch Academy không đơn thuần là một cơ sở giáo dục. Nó là cầu nối giữa các nền văn minh. Nó là ngọn hải đăng chúng ta thắp lên trước màn đêm dài. Hãy cùng nhau thắp sáng Startorch này—vì bình minh của Lahai-Roi, và vì mọi sinh mạng gọi nơi đây là nhà.
+Những người bạn Royan của tôi, các vị đã bảo vệ mảnh đất này qua bao thế hệ. Kính thưa quý đại biểu, các vị đang gánh vác tương lai của nhân loại trên đôi vai mình. Học viện Startorch không đơn thuần là một cơ sở giáo dục. Nó là cầu nối giữa các nền văn minh. Nó là ngọn hải đăng chúng ta thắp lên trước màn đêm dài. Hãy cùng nhau thắp sáng Startorch này—vì bình minh của Lahai-Roi, và vì mọi sinh mạng gọi nơi đây là nhà.
 Xin cảm ơn.</t>
         </is>
       </c>
@@ -29067,7 +29067,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>Tấn Công vũ khí chính tăng {0}.</t>
+          <t>ATK vũ khí chính tăng {0}.</t>
         </is>
       </c>
     </row>
@@ -29132,7 +29132,7 @@
       </c>
       <c r="M422" t="inlineStr">
         <is>
-          <t>HP tăng thêm {0}.</t>
+          <t>Tăng HP thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -29197,7 +29197,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>Tấn Công vũ khí chính tăng {0}.</t>
+          <t>ATK vũ khí chính tăng {0}.</t>
         </is>
       </c>
     </row>
@@ -29262,7 +29262,7 @@
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t>Tấn Công của Hỗ Trợ Droid tăng {0}.</t>
+          <t>ATK của Droid Hỗ Trợ tăng {0}.</t>
         </is>
       </c>
     </row>
@@ -29327,7 +29327,7 @@
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>HP tăng thêm {0}.</t>
+          <t>Tăng HP thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -29392,7 +29392,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>Tốc Độ Tấn Công Vũ Khí Main tăng {0}.</t>
+          <t>Tốc Độ ATK Vũ Khí Chính tăng {0}.</t>
         </is>
       </c>
     </row>
@@ -29457,7 +29457,7 @@
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t>Tấn Công của Hỗ Trợ Droid tăng {0}.</t>
+          <t>ATK của Droid Hỗ Trợ tăng {0}.</t>
         </is>
       </c>
     </row>
@@ -29522,7 +29522,7 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>Sát thương nhận vào khi lao vào kẻ địch giảm {0}%.</t>
+          <t>DMG nhận vào khi lao vào kẻ địch giảm {0}%.</t>
         </is>
       </c>
     </row>
@@ -29587,7 +29587,7 @@
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>Tấn Công vũ khí chính tăng {0}.</t>
+          <t>ATK vũ khí chính tăng {0}.</t>
         </is>
       </c>
     </row>
@@ -29652,7 +29652,7 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>Tấn Công của Hỗ Trợ Droid tăng {0}.</t>
+          <t>ATK của Droid Hỗ Trợ tăng {0}.</t>
         </is>
       </c>
     </row>
@@ -29717,7 +29717,7 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>HP tăng thêm {0}.</t>
+          <t>Tăng HP thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -29782,7 +29782,7 @@
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>Tốc Độ Tấn Công Vũ Khí Main tăng {0}.</t>
+          <t>Tốc Độ ATK Vũ Khí Chính tăng {0}.</t>
         </is>
       </c>
     </row>
@@ -29847,7 +29847,7 @@
       </c>
       <c r="M433" t="inlineStr">
         <is>
-          <t>Thời Gian Cooldown của Hỗ Trợ Droid giảm {0}%.</t>
+          <t>Thời gian hồi Chiêu của Droid Hỗ Trợ giảm {0}%.</t>
         </is>
       </c>
     </row>
@@ -29912,7 +29912,7 @@
       </c>
       <c r="M434" t="inlineStr">
         <is>
-          <t>Orbital Strike Protocol - Bản Dùng Thử sẽ khả dụng khi thử thách bắt đầu. Bản Dùng Thử không thể nhận bất kỳ hiệu ứng giảm Cooldown chiêu nào và sẽ tự động hết hạn nếu mở khóa Orbital Strike Protocol chính thức.</t>
+          <t>Giao Thức Đòn Đánh Quỹ Đạo - Bản Dùng Thử sẽ khả dụng khi thử thách bắt đầu. Bản Dùng Thử không thể nhận bất kỳ hiệu ứng giảm Thời gian hồi chiêu nào và sẽ tự động hết hạn nếu mở khóa Giao Thức Đòn Đánh Quỹ Đạo chính thức.</t>
         </is>
       </c>
     </row>
@@ -29977,7 +29977,7 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>Thời Gian Cooldown của Hỗ Trợ Droid giảm {0}%.</t>
+          <t>Thời gian hồi Chiêu của Droid Hỗ Trợ giảm {0}%.</t>
         </is>
       </c>
     </row>
@@ -30042,7 +30042,7 @@
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>HP tăng thêm {0}.</t>
+          <t>Tăng HP thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -30107,7 +30107,7 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>Tốc Độ Tấn Công Vũ Khí Main tăng {0}.</t>
+          <t>Tốc Độ ATK Vũ Khí Chính tăng {0}.</t>
         </is>
       </c>
     </row>
@@ -30172,7 +30172,7 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>Thời Gian Cooldown của Hỗ Trợ Droid giảm {0}%.</t>
+          <t>Thời gian hồi Chiêu của Droid Hỗ Trợ giảm {0}%.</t>
         </is>
       </c>
     </row>
@@ -30237,7 +30237,7 @@
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>Tấn Công của Hỗ Trợ Droid tăng {0}.</t>
+          <t>ATK của Droid Hỗ Trợ tăng {0}.</t>
         </is>
       </c>
     </row>
@@ -30302,7 +30302,7 @@
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>Main Weapon ATK +{0}</t>
+          <t>ATK Vũ Khí Chính +{0}</t>
         </is>
       </c>
     </row>
@@ -30367,7 +30367,7 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>Thời gian Boost tăng thêm {0}%.</t>
+          <t>Thời gian Tăng cường tăng thêm {0}%.</t>
         </is>
       </c>
     </row>
@@ -30432,7 +30432,7 @@
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t>Tấn Công của Vũ Khí Main và Hỗ Trợ Droid tăng thêm {0}%.</t>
+          <t>ATK của Vũ Khí Chính và Droid Hỗ Trợ tăng thêm {0}%.</t>
         </is>
       </c>
     </row>
@@ -30497,7 +30497,7 @@
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t>Sát thương nhận vào khi lao vào kẻ địch giảm {0}% và lượng hồi phục nhận được tăng {0}%.</t>
+          <t>DMG nhận vào khi lao vào kẻ địch giảm {0}% và lượng hồi phục nhận được tăng {0}%.</t>
         </is>
       </c>
     </row>
@@ -30562,7 +30562,7 @@
       </c>
       <c r="M444" t="inlineStr">
         <is>
-          <t>Training Protocol Enhancement Key: Tấn Công</t>
+          <t>Chìa khóa Nâng cấp Giao thức Huấn luyện: ATK</t>
         </is>
       </c>
     </row>
@@ -30627,7 +30627,7 @@
       </c>
       <c r="M445" t="inlineStr">
         <is>
-          <t>Training Protocol Enhancement Key: Tốc Độ Tấn Công</t>
+          <t>Chìa khóa Nâng cấp Giao thức Huấn luyện: ATK SPD</t>
         </is>
       </c>
     </row>
@@ -30692,7 +30692,7 @@
       </c>
       <c r="M446" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Zap Mô-đun&lt;/color&gt; đã được nâng cấp: giờ đây nó tăng &lt;color=Highlight&gt;{0}&lt;/color&gt; Tấn Công, và cứ mỗi &lt;color=Highlight&gt;{1}&lt;/color&gt; giây, nó sẽ bắn thêm một tia laser, gây &lt;color=Highlight&gt;{2}&lt;/color&gt; Sát Thương.</t>
+          <t>&lt;color=Highlight&gt;Mô-đun Tia Điện&lt;/color&gt; đã được nâng cấp: giờ đây nó tăng &lt;color=Highlight&gt;{0}&lt;/color&gt; ATK, và cứ mỗi &lt;color=Highlight&gt;{1}&lt;/color&gt; giây, nó sẽ bắn thêm một tia laser, gây &lt;color=Highlight&gt;{2}&lt;/color&gt; Sát Thương.</t>
         </is>
       </c>
     </row>
@@ -30757,7 +30757,7 @@
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t>Kẻ địch bị trúng đòn sẽ nhận thêm &lt;color=Highlight&gt;{1}&lt;/color&gt; sát thương và gây ra ít hơn &lt;color=Highlight&gt;{2}&lt;/color&gt; sát thương trong &lt;color=Highlight&gt;{0}&lt;/color&gt; giây.</t>
+          <t>Kẻ địch bị trúng đòn sẽ nhận thêm &lt;color=Highlight&gt;{1}&lt;/color&gt; DMG và gây ra ít hơn &lt;color=Highlight&gt;{2}&lt;/color&gt; DMG trong &lt;color=Highlight&gt;{0}&lt;/color&gt; giây.</t>
         </is>
       </c>
     </row>
@@ -30887,7 +30887,7 @@
       </c>
       <c r="M449" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Orbital Strike Protocol&lt;/color&gt; được nâng cấp: &lt;color=Highlight&gt;Hỗ Trợ Droid's number cannot be further increased&lt;/color&gt;. &lt;color=Highlight&gt;For every Hỗ Trợ Droid currently deployed&lt;/color&gt; sẽ tăng Tấn Công thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;.</t>
+          <t>&lt;color=Highlight&gt;Giao Thức ATK Quỹ Đạo&lt;/color&gt; được nâng cấp: &lt;color=Highlight&gt;Không thể triển khai thêm Droid Hỗ Trợ&lt;/color&gt;. &lt;color=Highlight&gt;Mỗi Droid Hỗ Trợ đang triển khai&lt;/color&gt; sẽ tăng ATK thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -30952,7 +30952,7 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>Kẻ địch chịu &lt;color=Highlight&gt;nhiều hơn {1} sát thương&lt;/color&gt;, nhưng HP của chúng tăng thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;.</t>
+          <t>Kẻ địch chịu &lt;color=Highlight&gt;nhiều hơn {1} DMG&lt;/color&gt;, nhưng HP của chúng tăng thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -31017,7 +31017,7 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>Crit. Rate của Rover Hỗ Trợ tăng thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;.</t>
+          <t>Crit. Rate của Vận Mệnh Giả Hỗ Trợ tăng thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -31082,7 +31082,7 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Repeater Mô-đun&lt;/color&gt; được nâng cấp: Equip thêm &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; &lt;color=Highlight&gt;{Cus:Sap,S=Repeater Mô-đun P=Repeater Modules SapTag=0}&lt;/color&gt;. &lt;color=Highlight&gt;Repeater Mô-đun&lt;/color&gt; giờ đây tăng &lt;color=Highlight&gt;{1}&lt;/color&gt; Tốc Độ Tấn Công, nhưng Hệ Số Sát Thương của đạn giảm &lt;color=Highlight&gt;{2}&lt;/color&gt;.</t>
+          <t>&lt;color=Highlight&gt;Mô-đun Lặp Lại&lt;/color&gt; được nâng cấp: Trang bị thêm &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; &lt;color=Highlight&gt;{Cus:Sap,S=Mô-đun Lặp Lại P=Mô-đun Lặp Lại SapTag=0}&lt;/color&gt;. &lt;color=Highlight&gt;Mô-đun Lặp Lại&lt;/color&gt; giờ đây tăng &lt;color=Highlight&gt;{1}&lt;/color&gt; Tốc Độ ATK, nhưng Hệ Số Sát Thương của đạn giảm &lt;color=Highlight&gt;{2}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -31212,7 +31212,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>Mỗi đòn tấn công trúng mục tiêu sẽ tăng Crit. DMG thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;, tối đa &lt;color=Highlight&gt;{1}&lt;/color&gt;. Hiệu ứng này sẽ mất đi nếu không gây sát thương trong &lt;color=Highlight&gt;{2}&lt;/color&gt; giây.</t>
+          <t>Mỗi đòn tấn công trúng mục tiêu sẽ tăng Crit. DMG thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;, tối đa &lt;color=Highlight&gt;{1}&lt;/color&gt;. Hiệu ứng này sẽ mất đi nếu không gây DMG trong &lt;color=Highlight&gt;{2}&lt;/color&gt; giây.</t>
         </is>
       </c>
     </row>
@@ -31277,7 +31277,7 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Sustained Combustion Protocol&lt;/color&gt; được nâng cấp: Cooldown chiêu giảm tối đa &lt;color=Highlight&gt;{0}&lt;/color&gt;.</t>
+          <t>&lt;color=Highlight&gt;Giao Thức Đốt Cháy Liên Tục&lt;/color&gt; được nâng cấp: Thời gian hồi chiêu giảm tối đa &lt;color=Highlight&gt;{0}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -31472,7 +31472,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Shotgun Mô-đun&lt;/color&gt; được nâng cấp: số lượng đạn giờ đây tăng lên &lt;color=Highlight&gt;{0}&lt;/color&gt;, nhưng sát thương mỗi viên đạn giảm &lt;color=Highlight&gt;{1}&lt;/color&gt;.</t>
+          <t>&lt;color=Highlight&gt;Shotgun Module&lt;/color&gt; được nâng cấp: số lượng đạn giờ đây tăng lên &lt;color=Highlight&gt;{0}&lt;/color&gt;, nhưng sát thương mỗi viên đạn giảm &lt;color=Highlight&gt;{1}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -31537,7 +31537,7 @@
       </c>
       <c r="M459" t="inlineStr">
         <is>
-          <t>Mỗi &lt;color=Highlight&gt;{0}&lt;/color&gt; Crit. Rate dư thừa từ Vũ Khí Main sẽ chuyển hóa thành &lt;color=Highlight&gt;{1}&lt;/color&gt; Crit. DMG.</t>
+          <t>Mỗi &lt;color=Highlight&gt;{0}&lt;/color&gt; Crit. Rate dư thừa từ Vũ Khí Chính sẽ chuyển hóa thành &lt;color=Highlight&gt;{1}&lt;/color&gt; Crit. DMG.</t>
         </is>
       </c>
     </row>
@@ -31602,7 +31602,7 @@
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>Tấn Công và Tốc Độ Tấn Công của Vũ Khí Main được điều chỉnh ngẫu nhiên: một chỉ số tăng &lt;color=Highlight&gt;{0}&lt;/color&gt;, chỉ số còn lại giảm &lt;color=Highlight&gt;{1}&lt;/color&gt;.</t>
+          <t>ATK và Tốc Độ ATK của Vũ Khí Chính được điều chỉnh ngẫu nhiên: một chỉ số tăng &lt;color=Highlight&gt;{0}&lt;/color&gt;, chỉ số còn lại giảm &lt;color=Highlight&gt;{1}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -31667,7 +31667,7 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Guided Missile Protocol&lt;/color&gt; được nâng cấp: Sát thương của Hỗ Trợ Droid tăng thêm &lt;color=Highlight&gt;{1}&lt;/color&gt;, và Cooldown chiêu tăng thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;.</t>
+          <t>&lt;color=Highlight&gt;Giao Thức Tên Lửa Điều Khiển&lt;/color&gt; được nâng cấp: DMG của Droid Hỗ Trợ tăng thêm &lt;color=Highlight&gt;{1}&lt;/color&gt;, và Thời gian hồi chiêu tăng thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -31732,7 +31732,7 @@
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Main Weapon&lt;/color&gt; gây &lt;color=Highlight&gt;{0}&lt;/color&gt; Sát Thương nhiều hơn, nhưng Sát Thương của Hỗ Trợ Droid giảm &lt;color=Highlight&gt;{1}&lt;/color&gt;.</t>
+          <t>&lt;color=Highlight&gt;Vũ khí Chính&lt;/color&gt; gây &lt;color=Highlight&gt;{0}&lt;/color&gt; Sát Thương nhiều hơn, nhưng Sát Thương của Droid Hỗ Trợ giảm &lt;color=Highlight&gt;{1}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -31797,7 +31797,7 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>Tấn Công vũ khí chính tăng &lt;color=Highlight&gt;{0}&lt;/color&gt;.</t>
+          <t>ATK vũ khí chính tăng &lt;color=Highlight&gt;{0}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -31862,7 +31862,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>Tấn Công của Hỗ Trợ Droid tăng &lt;color=Highlight&gt;{0}&lt;/color&gt;.</t>
+          <t>ATK của Droid Hỗ Trợ tăng &lt;color=Highlight&gt;{0}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -31992,7 +31992,7 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>Crit. DMG của Rover Hỗ Trợ tăng thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;.</t>
+          <t>Crit. DMG của Vận Mệnh Giả Hỗ Trợ tăng thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -32122,7 +32122,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>Tấn Công vũ khí chính tăng &lt;color=Highlight&gt;{0}&lt;/color&gt;. Hạ gục kẻ địch bằng vũ khí chính hoặc húc sẽ tăng Tấn Công vũ khí chính thêm &lt;color=Highlight&gt;{1}&lt;/color&gt;.</t>
+          <t>ATK vũ khí chính tăng &lt;color=Highlight&gt;{0}&lt;/color&gt;. Hạ gục kẻ địch bằng vũ khí chính hoặc húc sẽ tăng ATK vũ khí chính thêm &lt;color=Highlight&gt;{1}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -32187,7 +32187,7 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>Tăng &lt;color=Highlight&gt;{0}&lt;/color&gt; Tốc Độ Tấn Công Vũ Khí Main.</t>
+          <t>Tăng &lt;color=Highlight&gt;{0}&lt;/color&gt; Tốc Độ ATK Vũ Khí Chính.</t>
         </is>
       </c>
     </row>
@@ -32252,7 +32252,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>Thời Gian Cooldown của Hỗ Trợ Droid giảm &lt;color=Highlight&gt;{0}&lt;/color&gt;.</t>
+          <t>Thời gian hồi Chiêu của Droid Hỗ Trợ giảm &lt;color=Highlight&gt;{0}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -32512,7 +32512,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>HP hiện tại được nhân đôi.</t>
+          <t>HP hiện tại đã được nhân đôi.</t>
         </is>
       </c>
     </row>
@@ -32577,7 +32577,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>Mỗi &lt;color=Highlight&gt;&lt;SapTag=0&gt;{0}&lt;/SapTag&gt;&lt;/color&gt; {Cus:Sap,S=điểm HP P=điểm HP SapTag=0} HP hiện tại sẽ tăng &lt;color=Highlight&gt;{1}&lt;/color&gt; Tấn Công cho Vũ Khí Main, tối đa &lt;color=Highlight&gt;{2}&lt;/color&gt;.</t>
+          <t>Mỗi &lt;color=Highlight&gt;&lt;SapTag=0&gt;{0}&lt;/SapTag&gt;&lt;/color&gt; {Cus:Sap,S=điểm HP P=điểm HP SapTag=0} HP hiện tại sẽ tăng &lt;color=Highlight&gt;{1}&lt;/color&gt; ATK cho Vũ Khí Chính, tối đa &lt;color=Highlight&gt;{2}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -32642,7 +32642,7 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>Nếu không chịu sát thương húc trong &lt;color=Highlight&gt;{0}&lt;/color&gt;s, Tấn Công vũ khí chính sẽ tăng &lt;color=Highlight&gt;{1}&lt;/color&gt;.</t>
+          <t>Nếu không chịu DMG húc trong &lt;color=Highlight&gt;{0}&lt;/color&gt;s, ATK vũ khí chính sẽ tăng &lt;color=Highlight&gt;{1}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -32707,7 +32707,7 @@
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>Nếu không nhận sát thương từ đâm trong &lt;color=Highlight&gt;{0}&lt;/color&gt; giây, Tấn Công của Hỗ Trợ Droid tăng &lt;color=Highlight&gt;{1}&lt;/color&gt;.</t>
+          <t>Nếu không nhận DMG từ đâm trong &lt;color=Highlight&gt;{0}&lt;/color&gt; giây, ATK của Droid Hỗ Trợ tăng &lt;color=Highlight&gt;{1}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -32772,7 +32772,7 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>Nếu không nhận Sát Thương Đâm Trong &lt;color=Highlight&gt;{0}&lt;/color&gt; giây, Tốc Độ Tấn Công Vũ Khí Main tăng &lt;color=Highlight&gt;{1}&lt;/color&gt;.</t>
+          <t>Nếu không nhận Sát Thương Đâm Trong &lt;color=Highlight&gt;{0}&lt;/color&gt; giây, Tốc Độ ATK Vũ Khí Chính tăng &lt;color=Highlight&gt;{1}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -32837,7 +32837,7 @@
       </c>
       <c r="M479" t="inlineStr">
         <is>
-          <t>Nếu không nhận sát thương từ đâm trong &lt;color=Highlight&gt;{0}&lt;/color&gt; giây, Thời Gian Cooldown của Hỗ Trợ Droid giảm &lt;color=Highlight&gt;{1}&lt;/color&gt;.</t>
+          <t>Nếu không nhận DMG từ đâm trong &lt;color=Highlight&gt;{0}&lt;/color&gt; giây, Thời gian hồi Chiêu của Droid Hỗ Trợ giảm &lt;color=Highlight&gt;{1}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -32902,7 +32902,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>Block &lt;color=Highlight&gt;&lt;SapTag=1&gt;{1}&lt;/SapTag&gt;&lt;/color&gt; {Cus:Sap,S=lượng sát thương đạn đạo,P=lượng sát thương đạn đạo SapTag=1} từ kẻ địch, kích hoạt mỗi &lt;color=Highlight&gt;{0}&lt;/color&gt; giây.</t>
+          <t>Chặn &lt;color=Highlight&gt;&lt;SapTag=1&gt;{1}&lt;/SapTag&gt;&lt;/color&gt; {Cus:Sap,S=lượng sát thương đạn đạo,P=lượng sát thương đạn đạo SapTag=1} từ kẻ địch, kích hoạt mỗi &lt;color=Highlight&gt;{0}&lt;/color&gt; giây.</t>
         </is>
       </c>
     </row>
@@ -33032,7 +33032,7 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>Tấn Công của kẻ địch giảm &lt;color=Highlight&gt;{0}&lt;/color&gt;.</t>
+          <t>ATK của kẻ địch giảm &lt;color=Highlight&gt;{0}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -33097,7 +33097,7 @@
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>Phá Shield địch gây Sát Thương bằng &lt;color=Highlight&gt;{0}&lt;/color&gt; HP tối đa của chúng.</t>
+          <t>Phá Khiên địch gây Sát Thương bằng &lt;color=Highlight&gt;{0}&lt;/color&gt; HP tối đa của chúng.</t>
         </is>
       </c>
     </row>
@@ -33162,7 +33162,7 @@
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t>Tấn Công vũ khí chính tăng &lt;color=Highlight&gt;{0}&lt;/color&gt;, Tấn Công máy hỗ trợ tăng &lt;color=Highlight&gt;{1}&lt;/color&gt;.</t>
+          <t>ATK vũ khí chính tăng &lt;color=Highlight&gt;{0}&lt;/color&gt;, ATK máy hỗ trợ tăng &lt;color=Highlight&gt;{1}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -33227,7 +33227,7 @@
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>Tấn Công vũ khí chính tăng &lt;color=Highlight&gt;{0}&lt;/color&gt;, Tốc Độ Tấn Công tăng &lt;color=Highlight&gt;{1}&lt;/color&gt;.</t>
+          <t>ATK vũ khí chính tăng &lt;color=Highlight&gt;{0}&lt;/color&gt;, Tốc Độ ATK tăng &lt;color=Highlight&gt;{1}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -33292,7 +33292,7 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>Tấn Công của Hỗ Trợ Droid tăng &lt;color=Highlight&gt;{0}&lt;/color&gt;, nhưng Thời Gian Cooldown giảm &lt;color=Highlight&gt;{1}&lt;/color&gt;.</t>
+          <t>ATK của Droid Hỗ Trợ tăng &lt;color=Highlight&gt;{0}&lt;/color&gt;, nhưng Thời gian hồi Chiêu giảm &lt;color=Highlight&gt;{1}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -33357,7 +33357,7 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>Tấn Công vũ khí chính tăng &lt;color=Highlight&gt;{0}&lt;/color&gt;, nhưng Tấn Công máy hỗ trợ giảm &lt;color=Highlight&gt;{1}&lt;/color&gt;.</t>
+          <t>ATK vũ khí chính tăng &lt;color=Highlight&gt;{0}&lt;/color&gt;, nhưng ATK máy hỗ trợ giảm &lt;color=Highlight&gt;{1}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -33422,7 +33422,7 @@
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t>Tấn Công vũ khí chính giảm &lt;color=Highlight&gt;{0}&lt;/color&gt;, nhưng Tấn Công máy hỗ trợ tăng &lt;color=Highlight&gt;{1}&lt;/color&gt;.</t>
+          <t>ATK vũ khí chính giảm &lt;color=Highlight&gt;{0}&lt;/color&gt;, nhưng ATK máy hỗ trợ tăng &lt;color=Highlight&gt;{1}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -33487,7 +33487,7 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>Tốc Độ Tấn Công Vũ Khí Main tăng &lt;color=Highlight&gt;{0}&lt;/color&gt;, nhưng Thời Gian Cooldown Hỗ Trợ Droid tăng &lt;color=Highlight&gt;{1}&lt;/color&gt;.</t>
+          <t>Tốc Độ ATK Vũ Khí Chính tăng &lt;color=Highlight&gt;{0}&lt;/color&gt;, nhưng Thời gian hồi Chiêu Droid Hỗ Trợ tăng &lt;color=Highlight&gt;{1}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -33552,7 +33552,7 @@
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t>Thời Gian Cooldown của Hỗ Trợ Droid giảm &lt;color=Highlight&gt;{1}&lt;/color&gt;, nhưng Tốc Độ Tấn Công Vũ Khí Main giảm &lt;color=Highlight&gt;{0}&lt;/color&gt;.</t>
+          <t>Thời gian hồi Chiêu của Droid Hỗ Trợ giảm &lt;color=Highlight&gt;{1}&lt;/color&gt;, nhưng Tốc Độ ATK Vũ Khí Chính giảm &lt;color=Highlight&gt;{0}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -33617,7 +33617,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>Mỗi &lt;color=Highlight&gt;{0}&lt;/color&gt; Crit. Rate hoặc &lt;color=Highlight&gt;{2}&lt;/color&gt; Crit. DMG của Vũ Khí Main sẽ tăng &lt;color=Highlight&gt;{1}&lt;/color&gt; Sát Thương cho vũ khí đó.</t>
+          <t>Mỗi &lt;color=Highlight&gt;{0}&lt;/color&gt; Crit. Rate hoặc &lt;color=Highlight&gt;{2}&lt;/color&gt; Crit. DMG của Vũ Khí Chính sẽ tăng &lt;color=Highlight&gt;{1}&lt;/color&gt; Sát Thương cho vũ khí đó.</t>
         </is>
       </c>
     </row>
@@ -33682,7 +33682,7 @@
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>Mỗi &lt;color=Highlight&gt;{0}&lt;/color&gt; Crit. Rate hoặc &lt;color=Highlight&gt;{2}&lt;/color&gt; Crit. DMG của Hỗ Trợ Droid sẽ tăng &lt;color=Highlight&gt;{1}&lt;/color&gt; Sát Thương cho nó.</t>
+          <t>Mỗi &lt;color=Highlight&gt;{0}&lt;/color&gt; Crit. Rate hoặc &lt;color=Highlight&gt;{2}&lt;/color&gt; Crit. DMG của Droid Hỗ Trợ sẽ tăng &lt;color=Highlight&gt;{1}&lt;/color&gt; Sát Thương cho nó.</t>
         </is>
       </c>
     </row>
@@ -33747,7 +33747,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>Mỗi &lt;color=Highlight&gt;{0}&lt;/color&gt; Tốc Độ Tấn Công của Vũ Khí Main (không tính cộng dồn Tốc Độ Tấn Công) sẽ tăng &lt;color=Highlight&gt;{1}&lt;/color&gt; Sát Thương cho vũ khí đó.</t>
+          <t>Mỗi &lt;color=Highlight&gt;{0}&lt;/color&gt; Tốc Độ ATK của Vũ Khí Chính (không tính cộng dồn Tốc Độ ATK) sẽ tăng &lt;color=Highlight&gt;{1}&lt;/color&gt; Sát Thương cho vũ khí đó.</t>
         </is>
       </c>
     </row>
@@ -33812,7 +33812,7 @@
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>Mỗi &lt;color=Highlight&gt;{0}&lt;/color&gt; Giảm Thời Gian Cooldown của Hỗ Trợ Droid sẽ tăng &lt;color=Highlight&gt;{1}&lt;/color&gt; Sát Thương cho nó.</t>
+          <t>Mỗi &lt;color=Highlight&gt;{0}&lt;/color&gt; Giảm Thời gian hồi Chiêu của Droid Hỗ Trợ sẽ tăng &lt;color=Highlight&gt;{1}&lt;/color&gt; Sát Thương cho nó.</t>
         </is>
       </c>
     </row>
@@ -33877,7 +33877,7 @@
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>Vũ Khí Main được lắp đặt &lt;color=Highlight&gt;Zap Mô-đun&lt;/color&gt;: Cứ mỗi &lt;color=Highlight&gt;{0}&lt;/color&gt; giây, bắn thêm một tia laser, gây &lt;color=Highlight&gt;{1}&lt;/color&gt; Sát Thương.</t>
+          <t>Vũ Khí Chính được lắp đặt &lt;color=Highlight&gt;Mô-đun Tia Điện&lt;/color&gt;: Cứ mỗi &lt;color=Highlight&gt;{0}&lt;/color&gt; giây, bắn thêm một tia laser, gây &lt;color=Highlight&gt;{1}&lt;/color&gt; Sát Thương.</t>
         </is>
       </c>
     </row>
@@ -33942,7 +33942,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>Vũ Khí Main được lắp đặt &lt;color=Highlight&gt;Repeater Mô-đun&lt;/color&gt;: Tăng &lt;color=Highlight&gt;{0}&lt;/color&gt; Tốc Độ Tấn Công.</t>
+          <t>Vũ Khí Chính được lắp đặt &lt;color=Highlight&gt;Mô-đun Lặp Lại&lt;/color&gt;: Tăng &lt;color=Highlight&gt;{0}&lt;/color&gt; Tốc Độ ATK.</t>
         </is>
       </c>
     </row>
@@ -34007,7 +34007,7 @@
       </c>
       <c r="M497" t="inlineStr">
         <is>
-          <t>Vũ Khí Main được lắp đặt &lt;color=Highlight&gt;Shotgun Mô-đun&lt;/color&gt;: Có thể bắn &lt;color=Highlight&gt;{0}&lt;/color&gt; viên đạn trong một lần tấn công, bao phủ nhiều mục tiêu trên các làn khác nhau. Nhưng sát thương đạn giảm &lt;color=Highlight&gt;{1}&lt;/color&gt;.</t>
+          <t>Vũ Khí Chính được lắp đặt &lt;color=Highlight&gt;Mô-đun Súng Ngắn&lt;/color&gt;: Có thể bắn &lt;color=Highlight&gt;{0}&lt;/color&gt; viên đạn trong một lần tấn công, bao phủ nhiều mục tiêu trên các làn khác nhau. Nhưng sát thương đạn giảm &lt;color=Highlight&gt;{1}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -34072,7 +34072,7 @@
       </c>
       <c r="M498" t="inlineStr">
         <is>
-          <t>Rover Hỗ Trợ đã kích hoạt &lt;color=Highlight&gt;Orbital Strike Protocol&lt;/color&gt;: &lt;color=Highlight&gt;Hỗ Trợ Droid's number cannot be further increased&lt;/color&gt;. &lt;color=Highlight&gt;For every Hỗ Trợ Droid currently deployed&lt;/color&gt;, Tấn Công tăng thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;. Khi kích hoạt, số lượng Rover Hỗ Trợ tăng thêm &lt;color=Highlight&gt;{1}&lt;/color&gt;.</t>
+          <t>Vận Mệnh Giả Hỗ Trợ đã kích hoạt &lt;color=Highlight&gt;Giao Thức Không Kích Tầm Nhiệt&lt;/color&gt;: &lt;color=Highlight&gt;Số lượng Vận Mệnh Giả Hỗ Trợ không thể tăng thêm&lt;/color&gt;. &lt;color=Highlight&gt;Với mỗi Vận Mệnh Giả Hỗ Trợ đang triển khai&lt;/color&gt;, ATK tăng thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;. Khi kích hoạt, số lượng Vận Mệnh Giả Hỗ Trợ tăng thêm &lt;color=Highlight&gt;{1}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -34137,7 +34137,7 @@
       </c>
       <c r="M499" t="inlineStr">
         <is>
-          <t>Rover Hỗ Trợ đã kích hoạt &lt;color=Highlight&gt;Sustained Combustion Protocol&lt;/color&gt;: Gây &lt;color=Highlight&gt;{0}&lt;/color&gt; Sát Thương khi trúng đích lần đầu. Khi trúng mục tiêu, thiêu đốt kẻ địch, gây &lt;color=Highlight&gt;{2}&lt;/color&gt; Sát Thương mỗi giây trong &lt;color=Highlight&gt;{1}&lt;/color&gt; giây. Khi kích hoạt, số lượng Rover Hỗ Trợ tăng thêm &lt;color=Highlight&gt;{3}&lt;/color&gt;.</t>
+          <t>Vận Mệnh Giả Hỗ Trợ đã kích hoạt &lt;color=Highlight&gt;Giao Thức Duy Trì Đốt Cháy&lt;/color&gt;: Gây &lt;color=Highlight&gt;{0}&lt;/color&gt; Sát Thương khi trúng đích lần đầu. Khi trúng mục tiêu, thiêu đốt kẻ địch, gây &lt;color=Highlight&gt;{2}&lt;/color&gt; Sát Thương mỗi giây trong &lt;color=Highlight&gt;{1}&lt;/color&gt; giây. Khi kích hoạt, số lượng Vận Mệnh Giả Hỗ Trợ tăng thêm &lt;color=Highlight&gt;{3}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -34202,7 +34202,7 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Zap Mô-đun&lt;/color&gt; đã được nâng cấp: giờ đây nó tăng &lt;color=Highlight&gt;{0}&lt;/color&gt; Tấn Công, và cứ mỗi &lt;color=Highlight&gt;{1}&lt;/color&gt; giây, nó sẽ bắn thêm một tia laser, gây &lt;color=Highlight&gt;{2}&lt;/color&gt; Sát Thương.</t>
+          <t>&lt;color=Highlight&gt;Mô-đun Tia Điện&lt;/color&gt; đã được nâng cấp: giờ đây nó tăng &lt;color=Highlight&gt;{0}&lt;/color&gt; ATK, và cứ mỗi &lt;color=Highlight&gt;{1}&lt;/color&gt; giây, nó sẽ bắn thêm một tia laser, gây &lt;color=Highlight&gt;{2}&lt;/color&gt; Sát Thương.</t>
         </is>
       </c>
     </row>
@@ -34267,7 +34267,7 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Repeater Mô-đun&lt;/color&gt; được nâng cấp: Equip thêm &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; &lt;color=Highlight&gt;{Cus:Sap,S=Repeater Mô-đun P=Repeater Modules SapTag=0}&lt;/color&gt;. &lt;color=Highlight&gt;Repeater Mô-đun&lt;/color&gt; giờ đây tăng &lt;color=Highlight&gt;{1}&lt;/color&gt; Tốc Độ Tấn Công, nhưng Hệ Số Sát Thương của đạn giảm &lt;color=Highlight&gt;{2}&lt;/color&gt;.</t>
+          <t>&lt;color=Highlight&gt;Mô-đun Lặp Lại&lt;/color&gt; được nâng cấp: Trang bị thêm &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; &lt;color=Highlight&gt;{Cus:Sap,S=Mô-đun Lặp Lại P=Mô-đun Lặp Lại SapTag=0}&lt;/color&gt;. &lt;color=Highlight&gt;Mô-đun Lặp Lại&lt;/color&gt; giờ đây tăng &lt;color=Highlight&gt;{1}&lt;/color&gt; Tốc Độ ATK, nhưng Hệ Số Sát Thương của đạn giảm &lt;color=Highlight&gt;{2}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
